--- a/raw/Concepthierarchy.xlsx
+++ b/raw/Concepthierarchy.xlsx
@@ -4810,6 +4810,582 @@
         <v>387</v>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" s="6">
+        <v>65</v>
+      </c>
+      <c r="C590" s="8">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="6">
+        <v>178</v>
+      </c>
+      <c r="B591" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="6">
+        <v>65</v>
+      </c>
+      <c r="C592" s="8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="6">
+        <v>68</v>
+      </c>
+      <c r="B593" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="6">
+        <v>178</v>
+      </c>
+      <c r="C594" s="8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="6">
+        <v>66</v>
+      </c>
+      <c r="B595" s="7">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="6">
+        <v>65</v>
+      </c>
+      <c r="C596" s="8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="6">
+        <v>400</v>
+      </c>
+      <c r="B597" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="6">
+        <v>65</v>
+      </c>
+      <c r="C598" s="8">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="6">
+        <v>403</v>
+      </c>
+      <c r="B599" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="6">
+        <v>65</v>
+      </c>
+      <c r="C600" s="8">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="6">
+        <v>329</v>
+      </c>
+      <c r="B601" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="6">
+        <v>260</v>
+      </c>
+      <c r="C602" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="6">
+        <v>290</v>
+      </c>
+      <c r="B603" s="7">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="6">
+        <v>128</v>
+      </c>
+      <c r="C604" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="6">
+        <v>290</v>
+      </c>
+      <c r="B605" s="7">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="6">
+        <v>195</v>
+      </c>
+      <c r="C606" s="8">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="6">
+        <v>404</v>
+      </c>
+      <c r="B607" s="7">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="6">
+        <v>302</v>
+      </c>
+      <c r="C608" s="8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="6">
+        <v>145</v>
+      </c>
+      <c r="B609" s="7">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="6">
+        <v>405</v>
+      </c>
+      <c r="C610" s="8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="6">
+        <v>145</v>
+      </c>
+      <c r="B611" s="7">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="6">
+        <v>207</v>
+      </c>
+      <c r="C612" s="8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="6">
+        <v>145</v>
+      </c>
+      <c r="B613" s="7">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="6">
+        <v>410</v>
+      </c>
+      <c r="C614" s="8">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="6">
+        <v>306</v>
+      </c>
+      <c r="B615" s="7">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="6">
+        <v>410</v>
+      </c>
+      <c r="C616" s="8">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="6">
+        <v>128</v>
+      </c>
+      <c r="B617" s="7">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="6">
+        <v>337</v>
+      </c>
+      <c r="C618" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="6">
+        <v>290</v>
+      </c>
+      <c r="B619" s="7">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="6">
+        <v>339</v>
+      </c>
+      <c r="C620" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="6">
+        <v>290</v>
+      </c>
+      <c r="B621" s="7">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="6">
+        <v>340</v>
+      </c>
+      <c r="C622" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="6">
+        <v>290</v>
+      </c>
+      <c r="B623" s="7">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="6">
+        <v>357</v>
+      </c>
+      <c r="C624" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="6">
+        <v>290</v>
+      </c>
+      <c r="B625" s="7">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="6">
+        <v>358</v>
+      </c>
+      <c r="C626" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="6">
+        <v>290</v>
+      </c>
+      <c r="B627" s="7">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="6">
+        <v>379</v>
+      </c>
+      <c r="C628" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="6">
+        <v>290</v>
+      </c>
+      <c r="B629" s="7">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="6">
+        <v>393</v>
+      </c>
+      <c r="C630" s="8">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="6">
+        <v>415</v>
+      </c>
+      <c r="B631" s="7">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="6">
+        <v>406</v>
+      </c>
+      <c r="C632" s="8">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="6">
+        <v>415</v>
+      </c>
+      <c r="B633" s="7">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="6">
+        <v>416</v>
+      </c>
+      <c r="C634" s="8">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="6">
+        <v>415</v>
+      </c>
+      <c r="B635" s="7">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="6">
+        <v>218</v>
+      </c>
+      <c r="C636" s="8">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="6">
+        <v>415</v>
+      </c>
+      <c r="B637" s="7">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="6">
+        <v>218</v>
+      </c>
+      <c r="C638" s="8">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="6">
+        <v>419</v>
+      </c>
+      <c r="B639" s="7">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="6">
+        <v>421</v>
+      </c>
+      <c r="C640" s="8">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="6">
+        <v>306</v>
+      </c>
+      <c r="B641" s="7">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="6">
+        <v>422</v>
+      </c>
+      <c r="C642" s="8">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="6">
+        <v>306</v>
+      </c>
+      <c r="B643" s="7">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="6">
+        <v>423</v>
+      </c>
+      <c r="C644" s="8">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="6">
+        <v>306</v>
+      </c>
+      <c r="B645" s="7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="6">
+        <v>424</v>
+      </c>
+      <c r="C646" s="8">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="6">
+        <v>306</v>
+      </c>
+      <c r="B647" s="7">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="6">
+        <v>424</v>
+      </c>
+      <c r="C648" s="8">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="6">
+        <v>425</v>
+      </c>
+      <c r="B649" s="7">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="6">
+        <v>423</v>
+      </c>
+      <c r="C650" s="8">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="6">
+        <v>425</v>
+      </c>
+      <c r="B651" s="7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="6">
+        <v>426</v>
+      </c>
+      <c r="C652" s="8">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="6">
+        <v>425</v>
+      </c>
+      <c r="B653" s="7">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="6">
+        <v>426</v>
+      </c>
+      <c r="C654" s="8">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="6">
+        <v>306</v>
+      </c>
+      <c r="B655" s="7">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="6">
+        <v>426</v>
+      </c>
+      <c r="C656" s="8">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="6">
+        <v>422</v>
+      </c>
+      <c r="B657" s="7">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="6">
+        <v>427</v>
+      </c>
+      <c r="C658" s="8">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="6">
+        <v>421</v>
+      </c>
+      <c r="B659" s="7">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="6">
+        <v>427</v>
+      </c>
+      <c r="C660" s="8">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="6">
+        <v>422</v>
+      </c>
+      <c r="B661" s="7">
+        <v>427</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Concepthierarchy.xlsx
+++ b/raw/Concepthierarchy.xlsx
@@ -428,71 +428,71 @@
     </row>
     <row r="42">
       <c r="A42" s="6">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="C42" s="8">
-        <v>63</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="B43" s="7">
-        <v>62</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C44" s="8">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B45" s="7">
-        <v>12</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="C46" s="8">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6">
+        <v>66</v>
+      </c>
+      <c r="B47" s="7">
         <v>2</v>
-      </c>
-      <c r="B47" s="7">
-        <v>64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="C48" s="8">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B49" s="7">
-        <v>2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C50" s="8">
         <v>65</v>
@@ -503,7 +503,7 @@
         <v>65</v>
       </c>
       <c r="B51" s="7">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52">
@@ -511,12 +511,12 @@
         <v>64</v>
       </c>
       <c r="C52" s="8">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B53" s="7">
         <v>64</v>
@@ -524,23 +524,23 @@
     </row>
     <row r="54">
       <c r="A54" s="6">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C54" s="8">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B55" s="7">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C56" s="8">
         <v>66</v>
@@ -551,30 +551,30 @@
         <v>66</v>
       </c>
       <c r="B57" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6">
         <v>70</v>
       </c>
-      <c r="C58" s="8">
-        <v>66</v>
+      <c r="B58" s="7">
+        <v>69</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6">
-        <v>66</v>
-      </c>
-      <c r="B59" s="7">
+        <v>69</v>
+      </c>
+      <c r="C59" s="8">
         <v>70</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6">
-        <v>70</v>
-      </c>
-      <c r="B60" s="7">
+        <v>71</v>
+      </c>
+      <c r="C60" s="8">
         <v>69</v>
       </c>
     </row>
@@ -582,45 +582,45 @@
       <c r="A61" s="6">
         <v>69</v>
       </c>
-      <c r="C61" s="8">
-        <v>70</v>
+      <c r="B61" s="7">
+        <v>71</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="8">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B63" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C64" s="8">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B65" s="7">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C66" s="8">
         <v>71</v>
@@ -631,7 +631,7 @@
         <v>71</v>
       </c>
       <c r="B67" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68">
@@ -639,12 +639,12 @@
         <v>75</v>
       </c>
       <c r="C68" s="8">
-        <v>71</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B69" s="7">
         <v>75</v>
@@ -652,23 +652,23 @@
     </row>
     <row r="70">
       <c r="A70" s="6">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C70" s="8">
-        <v>10</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="B71" s="7">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C72" s="8">
         <v>79</v>
@@ -679,7 +679,7 @@
         <v>79</v>
       </c>
       <c r="B73" s="7">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74">
@@ -687,12 +687,12 @@
         <v>54</v>
       </c>
       <c r="C74" s="8">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="B75" s="7">
         <v>54</v>
@@ -700,34 +700,34 @@
     </row>
     <row r="76">
       <c r="A76" s="6">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C76" s="8">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B77" s="7">
-        <v>54</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="C78" s="8">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B79" s="7">
-        <v>74</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80">
@@ -735,12 +735,12 @@
         <v>30</v>
       </c>
       <c r="C80" s="8">
-        <v>50</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="B81" s="7">
         <v>30</v>
@@ -748,34 +748,34 @@
     </row>
     <row r="82">
       <c r="A82" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C82" s="8">
-        <v>82</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="B83" s="7">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C84" s="8">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="B85" s="7">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86">
@@ -783,12 +783,12 @@
         <v>35</v>
       </c>
       <c r="C86" s="8">
-        <v>98</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B87" s="7">
         <v>35</v>
@@ -796,18 +796,18 @@
     </row>
     <row r="88">
       <c r="A88" s="6">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C88" s="8">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B89" s="7">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90">
@@ -815,12 +815,12 @@
         <v>48</v>
       </c>
       <c r="C90" s="8">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B91" s="7">
         <v>48</v>
@@ -828,18 +828,18 @@
     </row>
     <row r="92">
       <c r="A92" s="6">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C92" s="8">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B93" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94">
@@ -847,12 +847,12 @@
         <v>99</v>
       </c>
       <c r="C94" s="8">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="B95" s="7">
         <v>99</v>
@@ -863,12 +863,12 @@
         <v>99</v>
       </c>
       <c r="C96" s="8">
-        <v>47</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="B97" s="7">
         <v>99</v>
@@ -879,12 +879,12 @@
         <v>99</v>
       </c>
       <c r="C98" s="8">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B99" s="7">
         <v>99</v>
@@ -892,34 +892,34 @@
     </row>
     <row r="100">
       <c r="A100" s="6">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C100" s="8">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B101" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C102" s="8">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B103" s="7">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104">
@@ -927,12 +927,12 @@
         <v>101</v>
       </c>
       <c r="C104" s="8">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B105" s="7">
         <v>101</v>
@@ -940,34 +940,34 @@
     </row>
     <row r="106">
       <c r="A106" s="6">
+        <v>98</v>
+      </c>
+      <c r="C106" s="8">
         <v>101</v>
-      </c>
-      <c r="C106" s="8">
-        <v>79</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="B107" s="7">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="C108" s="8">
-        <v>101</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="B109" s="7">
-        <v>98</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110">
@@ -975,12 +975,12 @@
         <v>11</v>
       </c>
       <c r="C110" s="8">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B111" s="7">
         <v>11</v>
@@ -991,12 +991,12 @@
         <v>11</v>
       </c>
       <c r="C112" s="8">
-        <v>15</v>
+        <v>62</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="B113" s="7">
         <v>11</v>
@@ -1007,12 +1007,12 @@
         <v>11</v>
       </c>
       <c r="C114" s="8">
-        <v>62</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="B115" s="7">
         <v>11</v>
@@ -1020,18 +1020,18 @@
     </row>
     <row r="116">
       <c r="A116" s="6">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C116" s="8">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B117" s="7">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="118">
@@ -1039,12 +1039,12 @@
         <v>47</v>
       </c>
       <c r="C118" s="8">
-        <v>19</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="B119" s="7">
         <v>47</v>
@@ -1052,50 +1052,50 @@
     </row>
     <row r="120">
       <c r="A120" s="6">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C120" s="8">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B121" s="7">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C122" s="8">
-        <v>105</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="B123" s="7">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C124" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B125" s="7">
-        <v>69</v>
+        <v>110</v>
       </c>
     </row>
     <row r="126">
@@ -1103,12 +1103,12 @@
         <v>110</v>
       </c>
       <c r="C126" s="8">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="B127" s="7">
         <v>110</v>
@@ -1119,12 +1119,12 @@
         <v>110</v>
       </c>
       <c r="C128" s="8">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="B129" s="7">
         <v>110</v>
@@ -1135,12 +1135,12 @@
         <v>110</v>
       </c>
       <c r="C130" s="8">
-        <v>112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="B131" s="7">
         <v>110</v>
@@ -1151,12 +1151,12 @@
         <v>110</v>
       </c>
       <c r="C132" s="8">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B133" s="7">
         <v>110</v>
@@ -1167,12 +1167,12 @@
         <v>110</v>
       </c>
       <c r="C134" s="8">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B135" s="7">
         <v>110</v>
@@ -1180,18 +1180,18 @@
     </row>
     <row r="136">
       <c r="A136" s="6">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C136" s="8">
-        <v>48</v>
+        <v>114</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="B137" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="138">
@@ -1199,12 +1199,12 @@
         <v>113</v>
       </c>
       <c r="C138" s="8">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="B139" s="7">
         <v>113</v>
@@ -1215,12 +1215,12 @@
         <v>113</v>
       </c>
       <c r="C140" s="8">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B141" s="7">
         <v>113</v>
@@ -1231,12 +1231,12 @@
         <v>113</v>
       </c>
       <c r="C142" s="8">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B143" s="7">
         <v>113</v>
@@ -1244,18 +1244,18 @@
     </row>
     <row r="144">
       <c r="A144" s="6">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="C144" s="8">
-        <v>116</v>
+        <v>66</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="B145" s="7">
-        <v>113</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146">
@@ -1263,12 +1263,12 @@
         <v>27</v>
       </c>
       <c r="C146" s="8">
-        <v>66</v>
+        <v>117</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="B147" s="7">
         <v>27</v>
@@ -1279,12 +1279,12 @@
         <v>27</v>
       </c>
       <c r="C148" s="8">
-        <v>117</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="B149" s="7">
         <v>27</v>
@@ -1292,18 +1292,18 @@
     </row>
     <row r="150">
       <c r="A150" s="6">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="C150" s="8">
-        <v>65</v>
+        <v>119</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="B151" s="7">
-        <v>27</v>
+        <v>118</v>
       </c>
     </row>
     <row r="152">
@@ -1311,12 +1311,12 @@
         <v>118</v>
       </c>
       <c r="C152" s="8">
-        <v>119</v>
+        <v>59</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B153" s="7">
         <v>118</v>
@@ -1327,12 +1327,12 @@
         <v>118</v>
       </c>
       <c r="C154" s="8">
-        <v>59</v>
+        <v>90</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="B155" s="7">
         <v>118</v>
@@ -1340,39 +1340,39 @@
     </row>
     <row r="156">
       <c r="A156" s="6">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C156" s="8">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B157" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="6">
+        <v>121</v>
+      </c>
+      <c r="C158" s="8">
         <v>120</v>
-      </c>
-      <c r="C158" s="8">
-        <v>65</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="B159" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C160" s="8">
         <v>120</v>
@@ -1383,23 +1383,23 @@
         <v>120</v>
       </c>
       <c r="B161" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C162" s="8">
-        <v>120</v>
+        <v>58</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="B163" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="164">
@@ -1407,12 +1407,12 @@
         <v>123</v>
       </c>
       <c r="C164" s="8">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="B165" s="7">
         <v>123</v>
@@ -1423,12 +1423,12 @@
         <v>123</v>
       </c>
       <c r="C166" s="8">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B167" s="7">
         <v>123</v>
@@ -1439,12 +1439,12 @@
         <v>123</v>
       </c>
       <c r="C168" s="8">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B169" s="7">
         <v>123</v>
@@ -1452,87 +1452,87 @@
     </row>
     <row r="170">
       <c r="A170" s="6">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C170" s="8">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="6">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B171" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="6">
+        <v>123</v>
+      </c>
+      <c r="C172" s="8">
         <v>125</v>
-      </c>
-      <c r="C172" s="8">
-        <v>58</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="B173" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="6">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C174" s="8">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B175" s="7">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="6">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C176" s="8">
-        <v>128</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="B177" s="7">
-        <v>106</v>
+        <v>129</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C178" s="8">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="B179" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C180" s="8">
         <v>48</v>
@@ -1543,39 +1543,39 @@
         <v>48</v>
       </c>
       <c r="B181" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="6">
+        <v>132</v>
+      </c>
+      <c r="C182" s="8">
         <v>131</v>
-      </c>
-      <c r="C182" s="8">
-        <v>48</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="B183" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="6">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C184" s="8">
-        <v>131</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="B185" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="186">
@@ -1583,12 +1583,12 @@
         <v>134</v>
       </c>
       <c r="C186" s="8">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B187" s="7">
         <v>134</v>
@@ -1599,12 +1599,12 @@
         <v>134</v>
       </c>
       <c r="C188" s="8">
-        <v>59</v>
+        <v>135</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="B189" s="7">
         <v>134</v>
@@ -1615,12 +1615,12 @@
         <v>134</v>
       </c>
       <c r="C190" s="8">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B191" s="7">
         <v>134</v>
@@ -1628,18 +1628,18 @@
     </row>
     <row r="192">
       <c r="A192" s="6">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C192" s="8">
-        <v>136</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="B193" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="194">
@@ -1647,12 +1647,12 @@
         <v>133</v>
       </c>
       <c r="C194" s="8">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B195" s="7">
         <v>133</v>
@@ -1663,12 +1663,12 @@
         <v>133</v>
       </c>
       <c r="C196" s="8">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="B197" s="7">
         <v>133</v>
@@ -1676,18 +1676,18 @@
     </row>
     <row r="198">
       <c r="A198" s="6">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C198" s="8">
-        <v>135</v>
+        <v>79</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6">
+        <v>79</v>
+      </c>
+      <c r="B199" s="7">
         <v>135</v>
-      </c>
-      <c r="B199" s="7">
-        <v>133</v>
       </c>
     </row>
     <row r="200">
@@ -1695,12 +1695,12 @@
         <v>135</v>
       </c>
       <c r="C200" s="8">
-        <v>79</v>
+        <v>125</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="B201" s="7">
         <v>135</v>
@@ -1711,12 +1711,12 @@
         <v>135</v>
       </c>
       <c r="C202" s="8">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B203" s="7">
         <v>135</v>
@@ -1727,12 +1727,12 @@
         <v>135</v>
       </c>
       <c r="C204" s="8">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="B205" s="7">
         <v>135</v>
@@ -1743,12 +1743,12 @@
         <v>135</v>
       </c>
       <c r="C206" s="8">
-        <v>106</v>
+        <v>48</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="B207" s="7">
         <v>135</v>
@@ -1756,18 +1756,18 @@
     </row>
     <row r="208">
       <c r="A208" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C208" s="8">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B209" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="210">
@@ -1775,12 +1775,12 @@
         <v>136</v>
       </c>
       <c r="C210" s="8">
-        <v>79</v>
+        <v>49</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="B211" s="7">
         <v>136</v>
@@ -1791,12 +1791,12 @@
         <v>136</v>
       </c>
       <c r="C212" s="8">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="B213" s="7">
         <v>136</v>
@@ -1807,12 +1807,12 @@
         <v>136</v>
       </c>
       <c r="C214" s="8">
-        <v>113</v>
+        <v>138</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="B215" s="7">
         <v>136</v>
@@ -1823,12 +1823,12 @@
         <v>136</v>
       </c>
       <c r="C216" s="8">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B217" s="7">
         <v>136</v>
@@ -1836,18 +1836,18 @@
     </row>
     <row r="218">
       <c r="A218" s="6">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C218" s="8">
-        <v>137</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="B219" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="220">
@@ -1855,12 +1855,12 @@
         <v>139</v>
       </c>
       <c r="C220" s="8">
-        <v>2</v>
+        <v>135</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="B221" s="7">
         <v>139</v>
@@ -1871,12 +1871,12 @@
         <v>139</v>
       </c>
       <c r="C222" s="8">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B223" s="7">
         <v>139</v>
@@ -1887,12 +1887,12 @@
         <v>139</v>
       </c>
       <c r="C224" s="8">
-        <v>136</v>
+        <v>59</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="B225" s="7">
         <v>139</v>
@@ -1900,34 +1900,34 @@
     </row>
     <row r="226">
       <c r="A226" s="6">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C226" s="8">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B227" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="6">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="C228" s="8">
-        <v>66</v>
+        <v>10</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="B229" s="7">
-        <v>141</v>
+        <v>43</v>
       </c>
     </row>
     <row r="230">
@@ -1935,12 +1935,12 @@
         <v>43</v>
       </c>
       <c r="C230" s="8">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B231" s="7">
         <v>43</v>
@@ -1948,50 +1948,50 @@
     </row>
     <row r="232">
       <c r="A232" s="6">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="C232" s="8">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B233" s="7">
-        <v>43</v>
+        <v>143</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="6">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C234" s="8">
-        <v>47</v>
+        <v>145</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="B235" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="6">
+        <v>143</v>
+      </c>
+      <c r="C236" s="8">
         <v>144</v>
-      </c>
-      <c r="C236" s="8">
-        <v>145</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B237" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="238">
@@ -1999,12 +1999,12 @@
         <v>143</v>
       </c>
       <c r="C238" s="8">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="B239" s="7">
         <v>143</v>
@@ -2015,12 +2015,12 @@
         <v>143</v>
       </c>
       <c r="C240" s="8">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B241" s="7">
         <v>143</v>
@@ -2028,18 +2028,18 @@
     </row>
     <row r="242">
       <c r="A242" s="6">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C242" s="8">
-        <v>49</v>
+        <v>112</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B243" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="244">
@@ -2047,12 +2047,12 @@
         <v>146</v>
       </c>
       <c r="C244" s="8">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B245" s="7">
         <v>146</v>
@@ -2063,12 +2063,12 @@
         <v>146</v>
       </c>
       <c r="C246" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B247" s="7">
         <v>146</v>
@@ -2076,18 +2076,18 @@
     </row>
     <row r="248">
       <c r="A248" s="6">
+        <v>148</v>
+      </c>
+      <c r="C248" s="8">
         <v>146</v>
-      </c>
-      <c r="C248" s="8">
-        <v>132</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="6">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B249" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="250">
@@ -2095,12 +2095,12 @@
         <v>148</v>
       </c>
       <c r="C250" s="8">
-        <v>146</v>
+        <v>106</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B251" s="7">
         <v>148</v>
@@ -2111,12 +2111,12 @@
         <v>148</v>
       </c>
       <c r="C252" s="8">
-        <v>106</v>
+        <v>125</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="6">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B253" s="7">
         <v>148</v>
@@ -2127,12 +2127,12 @@
         <v>148</v>
       </c>
       <c r="C254" s="8">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B255" s="7">
         <v>148</v>
@@ -2143,12 +2143,12 @@
         <v>148</v>
       </c>
       <c r="C256" s="8">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B257" s="7">
         <v>148</v>
@@ -2156,18 +2156,18 @@
     </row>
     <row r="258">
       <c r="A258" s="6">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C258" s="8">
-        <v>130</v>
+        <v>49</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="B259" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="260">
@@ -2175,12 +2175,12 @@
         <v>149</v>
       </c>
       <c r="C260" s="8">
-        <v>49</v>
+        <v>125</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="B261" s="7">
         <v>149</v>
@@ -2191,12 +2191,12 @@
         <v>149</v>
       </c>
       <c r="C262" s="8">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B263" s="7">
         <v>149</v>
@@ -2207,12 +2207,12 @@
         <v>149</v>
       </c>
       <c r="C264" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B265" s="7">
         <v>149</v>
@@ -2220,18 +2220,18 @@
     </row>
     <row r="266">
       <c r="A266" s="6">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C266" s="8">
-        <v>132</v>
+        <v>19</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="B267" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="268">
@@ -2239,12 +2239,12 @@
         <v>150</v>
       </c>
       <c r="C268" s="8">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="B269" s="7">
         <v>150</v>
@@ -2255,12 +2255,12 @@
         <v>150</v>
       </c>
       <c r="C270" s="8">
-        <v>106</v>
+        <v>47</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="6">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B271" s="7">
         <v>150</v>
@@ -2268,18 +2268,18 @@
     </row>
     <row r="272">
       <c r="A272" s="6">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C272" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="6">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B273" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="274">
@@ -2287,12 +2287,12 @@
         <v>152</v>
       </c>
       <c r="C274" s="8">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="6">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B275" s="7">
         <v>152</v>
@@ -2300,18 +2300,18 @@
     </row>
     <row r="276">
       <c r="A276" s="6">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C276" s="8">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="6">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B277" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="278">
@@ -2319,12 +2319,12 @@
         <v>153</v>
       </c>
       <c r="C278" s="8">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="6">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B279" s="7">
         <v>153</v>
@@ -2335,12 +2335,12 @@
         <v>153</v>
       </c>
       <c r="C280" s="8">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="6">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="B281" s="7">
         <v>153</v>
@@ -2348,18 +2348,18 @@
     </row>
     <row r="282">
       <c r="A282" s="6">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C282" s="8">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="6">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B283" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="284">
@@ -2367,12 +2367,12 @@
         <v>155</v>
       </c>
       <c r="C284" s="8">
-        <v>57</v>
+        <v>135</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="B285" s="7">
         <v>155</v>
@@ -2380,66 +2380,66 @@
     </row>
     <row r="286">
       <c r="A286" s="6">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C286" s="8">
-        <v>135</v>
+        <v>79</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="B287" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="6">
-        <v>156</v>
-      </c>
-      <c r="C288" s="8">
-        <v>79</v>
+        <v>165</v>
+      </c>
+      <c r="B288" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6">
-        <v>79</v>
-      </c>
-      <c r="B289" s="7">
-        <v>156</v>
+        <v>1</v>
+      </c>
+      <c r="C289" s="8">
+        <v>165</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6">
-        <v>165</v>
-      </c>
-      <c r="B290" s="7">
-        <v>1</v>
+        <v>171</v>
+      </c>
+      <c r="C290" s="8">
+        <v>79</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6">
-        <v>1</v>
-      </c>
-      <c r="C291" s="8">
-        <v>165</v>
+        <v>79</v>
+      </c>
+      <c r="B291" s="7">
+        <v>171</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C292" s="8">
-        <v>79</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="B293" s="7">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="294">
@@ -2447,12 +2447,12 @@
         <v>179</v>
       </c>
       <c r="C294" s="8">
-        <v>2</v>
+        <v>178</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6">
-        <v>2</v>
+        <v>178</v>
       </c>
       <c r="B295" s="7">
         <v>179</v>
@@ -2463,12 +2463,12 @@
         <v>179</v>
       </c>
       <c r="C296" s="8">
-        <v>178</v>
+        <v>64</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="B297" s="7">
         <v>179</v>
@@ -2476,18 +2476,18 @@
     </row>
     <row r="298">
       <c r="A298" s="6">
+        <v>180</v>
+      </c>
+      <c r="C298" s="8">
         <v>179</v>
-      </c>
-      <c r="C298" s="8">
-        <v>64</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6">
-        <v>64</v>
+        <v>179</v>
       </c>
       <c r="B299" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="300">
@@ -2495,12 +2495,12 @@
         <v>180</v>
       </c>
       <c r="C300" s="8">
-        <v>179</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="6">
-        <v>179</v>
+        <v>3</v>
       </c>
       <c r="B301" s="7">
         <v>180</v>
@@ -2508,18 +2508,18 @@
     </row>
     <row r="302">
       <c r="A302" s="6">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C302" s="8">
-        <v>3</v>
+        <v>179</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="6">
-        <v>3</v>
+        <v>179</v>
       </c>
       <c r="B303" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="304">
@@ -2527,12 +2527,12 @@
         <v>181</v>
       </c>
       <c r="C304" s="8">
-        <v>179</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="6">
-        <v>179</v>
+        <v>3</v>
       </c>
       <c r="B305" s="7">
         <v>181</v>
@@ -2540,18 +2540,18 @@
     </row>
     <row r="306">
       <c r="A306" s="6">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C306" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B307" s="7">
-        <v>181</v>
+        <v>199</v>
       </c>
     </row>
     <row r="308">
@@ -2559,12 +2559,12 @@
         <v>199</v>
       </c>
       <c r="C308" s="8">
-        <v>1</v>
+        <v>177</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="6">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="B309" s="7">
         <v>199</v>
@@ -2572,34 +2572,34 @@
     </row>
     <row r="310">
       <c r="A310" s="6">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C310" s="8">
-        <v>177</v>
+        <v>202</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="6">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="B311" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="6">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="C312" s="8">
-        <v>202</v>
+        <v>64</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="6">
-        <v>202</v>
+        <v>64</v>
       </c>
       <c r="B313" s="7">
-        <v>201</v>
+        <v>182</v>
       </c>
     </row>
     <row r="314">
@@ -2607,12 +2607,12 @@
         <v>182</v>
       </c>
       <c r="C314" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B315" s="7">
         <v>182</v>
@@ -2620,66 +2620,66 @@
     </row>
     <row r="316">
       <c r="A316" s="6">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C316" s="8">
-        <v>65</v>
+        <v>104</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="6">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B317" s="7">
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="6">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C318" s="8">
-        <v>104</v>
+        <v>145</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="6">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="B319" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="6">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C320" s="8">
-        <v>145</v>
+        <v>199</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="6">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="B321" s="7">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="6">
-        <v>195</v>
+        <v>73</v>
       </c>
       <c r="C322" s="8">
-        <v>199</v>
+        <v>157</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="6">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="B323" s="7">
-        <v>195</v>
+        <v>73</v>
       </c>
     </row>
     <row r="324">
@@ -2687,12 +2687,12 @@
         <v>73</v>
       </c>
       <c r="C324" s="8">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="6">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B325" s="7">
         <v>73</v>
@@ -2703,12 +2703,12 @@
         <v>73</v>
       </c>
       <c r="C326" s="8">
-        <v>173</v>
+        <v>211</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="6">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="B327" s="7">
         <v>73</v>
@@ -2716,18 +2716,18 @@
     </row>
     <row r="328">
       <c r="A328" s="6">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C328" s="8">
-        <v>211</v>
+        <v>34</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="6">
-        <v>211</v>
+        <v>34</v>
       </c>
       <c r="B329" s="7">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="330">
@@ -2735,12 +2735,12 @@
         <v>88</v>
       </c>
       <c r="C330" s="8">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="6">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B331" s="7">
         <v>88</v>
@@ -2748,34 +2748,34 @@
     </row>
     <row r="332">
       <c r="A332" s="6">
-        <v>88</v>
+        <v>226</v>
       </c>
       <c r="C332" s="8">
-        <v>47</v>
+        <v>227</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="6">
-        <v>47</v>
+        <v>227</v>
       </c>
       <c r="B333" s="7">
-        <v>88</v>
+        <v>226</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="6">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C334" s="8">
-        <v>227</v>
+        <v>47</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="6">
+        <v>47</v>
+      </c>
+      <c r="B335" s="7">
         <v>227</v>
-      </c>
-      <c r="B335" s="7">
-        <v>226</v>
       </c>
     </row>
     <row r="336">
@@ -2783,12 +2783,12 @@
         <v>227</v>
       </c>
       <c r="C336" s="8">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="6">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B337" s="7">
         <v>227</v>
@@ -2796,66 +2796,66 @@
     </row>
     <row r="338">
       <c r="A338" s="6">
-        <v>227</v>
+        <v>50</v>
       </c>
       <c r="C338" s="8">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B339" s="7">
-        <v>227</v>
+        <v>50</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="6">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C340" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="6">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B341" s="7">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="6">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="C342" s="8">
-        <v>68</v>
+        <v>227</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="6">
-        <v>68</v>
+        <v>227</v>
       </c>
       <c r="B343" s="7">
-        <v>20</v>
+        <v>234</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="6">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C344" s="8">
-        <v>227</v>
+        <v>95</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="6">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="B345" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="346">
@@ -2863,12 +2863,12 @@
         <v>235</v>
       </c>
       <c r="C346" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="6">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B347" s="7">
         <v>235</v>
@@ -2876,34 +2876,34 @@
     </row>
     <row r="348">
       <c r="A348" s="6">
-        <v>235</v>
+        <v>144</v>
       </c>
       <c r="C348" s="8">
-        <v>96</v>
+        <v>66</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="6">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="B349" s="7">
-        <v>235</v>
+        <v>144</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="6">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="C350" s="8">
-        <v>66</v>
+        <v>98</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="6">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="B351" s="7">
-        <v>144</v>
+        <v>241</v>
       </c>
     </row>
     <row r="352">
@@ -2911,12 +2911,12 @@
         <v>241</v>
       </c>
       <c r="C352" s="8">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="6">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B353" s="7">
         <v>241</v>
@@ -2927,12 +2927,12 @@
         <v>241</v>
       </c>
       <c r="C354" s="8">
-        <v>104</v>
+        <v>53</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="6">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="B355" s="7">
         <v>241</v>
@@ -2943,12 +2943,12 @@
         <v>241</v>
       </c>
       <c r="C356" s="8">
-        <v>53</v>
+        <v>143</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="6">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="B357" s="7">
         <v>241</v>
@@ -2959,12 +2959,12 @@
         <v>241</v>
       </c>
       <c r="C358" s="8">
-        <v>143</v>
+        <v>242</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="6">
-        <v>143</v>
+        <v>242</v>
       </c>
       <c r="B359" s="7">
         <v>241</v>
@@ -2972,18 +2972,18 @@
     </row>
     <row r="360">
       <c r="A360" s="6">
-        <v>241</v>
+        <v>97</v>
       </c>
       <c r="C360" s="8">
-        <v>242</v>
+        <v>64</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="6">
-        <v>242</v>
+        <v>64</v>
       </c>
       <c r="B361" s="7">
-        <v>241</v>
+        <v>97</v>
       </c>
     </row>
     <row r="362">
@@ -2991,12 +2991,12 @@
         <v>97</v>
       </c>
       <c r="C362" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B363" s="7">
         <v>97</v>
@@ -3004,39 +3004,39 @@
     </row>
     <row r="364">
       <c r="A364" s="6">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="C364" s="8">
-        <v>65</v>
+        <v>251</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="6">
-        <v>65</v>
+        <v>251</v>
       </c>
       <c r="B365" s="7">
-        <v>97</v>
+        <v>250</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="6">
+        <v>162</v>
+      </c>
+      <c r="C366" s="8">
         <v>250</v>
-      </c>
-      <c r="C366" s="8">
-        <v>251</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="6">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B367" s="7">
-        <v>250</v>
+        <v>162</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="6">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C368" s="8">
         <v>250</v>
@@ -3047,39 +3047,39 @@
         <v>250</v>
       </c>
       <c r="B369" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="6">
-        <v>161</v>
+        <v>252</v>
       </c>
       <c r="C370" s="8">
-        <v>250</v>
+        <v>209</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="6">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="B371" s="7">
-        <v>161</v>
+        <v>252</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="6">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C372" s="8">
-        <v>209</v>
+        <v>79</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="6">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="B373" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="374">
@@ -3087,12 +3087,12 @@
         <v>259</v>
       </c>
       <c r="C374" s="8">
-        <v>79</v>
+        <v>260</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="6">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="B375" s="7">
         <v>259</v>
@@ -3103,12 +3103,12 @@
         <v>259</v>
       </c>
       <c r="C376" s="8">
-        <v>260</v>
+        <v>19</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="6">
-        <v>260</v>
+        <v>19</v>
       </c>
       <c r="B377" s="7">
         <v>259</v>
@@ -3119,12 +3119,12 @@
         <v>259</v>
       </c>
       <c r="C378" s="8">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="6">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="B379" s="7">
         <v>259</v>
@@ -3135,12 +3135,12 @@
         <v>259</v>
       </c>
       <c r="C380" s="8">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="6">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="B381" s="7">
         <v>259</v>
@@ -3151,12 +3151,12 @@
         <v>259</v>
       </c>
       <c r="C382" s="8">
-        <v>25</v>
+        <v>261</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="6">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="B383" s="7">
         <v>259</v>
@@ -3164,18 +3164,18 @@
     </row>
     <row r="384">
       <c r="A384" s="6">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C384" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="6">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B385" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="386">
@@ -3183,12 +3183,12 @@
         <v>262</v>
       </c>
       <c r="C386" s="8">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="6">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B387" s="7">
         <v>262</v>
@@ -3196,18 +3196,18 @@
     </row>
     <row r="388">
       <c r="A388" s="6">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C388" s="8">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="6">
+        <v>261</v>
+      </c>
+      <c r="B389" s="7">
         <v>264</v>
-      </c>
-      <c r="B389" s="7">
-        <v>262</v>
       </c>
     </row>
     <row r="390">
@@ -3215,12 +3215,12 @@
         <v>264</v>
       </c>
       <c r="C390" s="8">
-        <v>261</v>
+        <v>25</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="6">
-        <v>261</v>
+        <v>25</v>
       </c>
       <c r="B391" s="7">
         <v>264</v>
@@ -3231,12 +3231,12 @@
         <v>264</v>
       </c>
       <c r="C392" s="8">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="6">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B393" s="7">
         <v>264</v>
@@ -3244,18 +3244,18 @@
     </row>
     <row r="394">
       <c r="A394" s="6">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C394" s="8">
-        <v>78</v>
+        <v>266</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="6">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="B395" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="396">
@@ -3263,12 +3263,12 @@
         <v>265</v>
       </c>
       <c r="C396" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="6">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B397" s="7">
         <v>265</v>
@@ -3279,12 +3279,12 @@
         <v>265</v>
       </c>
       <c r="C398" s="8">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="6">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B399" s="7">
         <v>265</v>
@@ -3295,12 +3295,12 @@
         <v>265</v>
       </c>
       <c r="C400" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="6">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B401" s="7">
         <v>265</v>
@@ -3308,18 +3308,18 @@
     </row>
     <row r="402">
       <c r="A402" s="6">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C402" s="8">
-        <v>269</v>
+        <v>25</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="6">
-        <v>269</v>
+        <v>25</v>
       </c>
       <c r="B403" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="404">
@@ -3327,12 +3327,12 @@
         <v>270</v>
       </c>
       <c r="C404" s="8">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B405" s="7">
         <v>270</v>
@@ -3343,12 +3343,12 @@
         <v>270</v>
       </c>
       <c r="C406" s="8">
-        <v>19</v>
+        <v>263</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="6">
-        <v>19</v>
+        <v>263</v>
       </c>
       <c r="B407" s="7">
         <v>270</v>
@@ -3356,18 +3356,18 @@
     </row>
     <row r="408">
       <c r="A408" s="6">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C408" s="8">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="6">
+        <v>271</v>
+      </c>
+      <c r="B409" s="7">
         <v>263</v>
-      </c>
-      <c r="B409" s="7">
-        <v>270</v>
       </c>
     </row>
     <row r="410">
@@ -3375,12 +3375,12 @@
         <v>263</v>
       </c>
       <c r="C410" s="8">
-        <v>271</v>
+        <v>261</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="6">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B411" s="7">
         <v>263</v>
@@ -3391,12 +3391,12 @@
         <v>263</v>
       </c>
       <c r="C412" s="8">
-        <v>261</v>
+        <v>82</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="6">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="B413" s="7">
         <v>263</v>
@@ -3407,12 +3407,12 @@
         <v>263</v>
       </c>
       <c r="C414" s="8">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="6">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="B415" s="7">
         <v>263</v>
@@ -3423,12 +3423,12 @@
         <v>263</v>
       </c>
       <c r="C416" s="8">
-        <v>25</v>
+        <v>272</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="6">
-        <v>25</v>
+        <v>272</v>
       </c>
       <c r="B417" s="7">
         <v>263</v>
@@ -3436,23 +3436,23 @@
     </row>
     <row r="418">
       <c r="A418" s="6">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C418" s="8">
-        <v>272</v>
+        <v>179</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="6">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="B419" s="7">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="6">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C420" s="8">
         <v>179</v>
@@ -3463,39 +3463,39 @@
         <v>179</v>
       </c>
       <c r="B421" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="6">
-        <v>276</v>
-      </c>
-      <c r="C422" s="8">
-        <v>179</v>
+        <v>277</v>
+      </c>
+      <c r="B422" s="7">
+        <v>241</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="6">
-        <v>179</v>
-      </c>
-      <c r="B423" s="7">
-        <v>276</v>
+        <v>241</v>
+      </c>
+      <c r="C423" s="8">
+        <v>277</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="6">
+        <v>278</v>
+      </c>
+      <c r="C424" s="8">
         <v>277</v>
-      </c>
-      <c r="B424" s="7">
-        <v>241</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="6">
-        <v>241</v>
-      </c>
-      <c r="C425" s="8">
         <v>277</v>
+      </c>
+      <c r="B425" s="7">
+        <v>278</v>
       </c>
     </row>
     <row r="426">
@@ -3503,12 +3503,12 @@
         <v>278</v>
       </c>
       <c r="C426" s="8">
-        <v>277</v>
+        <v>79</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="6">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="B427" s="7">
         <v>278</v>
@@ -3516,34 +3516,34 @@
     </row>
     <row r="428">
       <c r="A428" s="6">
+        <v>279</v>
+      </c>
+      <c r="C428" s="8">
         <v>278</v>
-      </c>
-      <c r="C428" s="8">
-        <v>79</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="6">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="B429" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="6">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C430" s="8">
-        <v>278</v>
+        <v>79</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="6">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="B431" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="432">
@@ -3551,12 +3551,12 @@
         <v>280</v>
       </c>
       <c r="C432" s="8">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="6">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B433" s="7">
         <v>280</v>
@@ -3567,12 +3567,12 @@
         <v>280</v>
       </c>
       <c r="C434" s="8">
-        <v>28</v>
+        <v>119</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="6">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="B435" s="7">
         <v>280</v>
@@ -3583,12 +3583,12 @@
         <v>280</v>
       </c>
       <c r="C436" s="8">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="6">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B437" s="7">
         <v>280</v>
@@ -3596,18 +3596,18 @@
     </row>
     <row r="438">
       <c r="A438" s="6">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C438" s="8">
-        <v>117</v>
+        <v>57</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="6">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="B439" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="440">
@@ -3615,12 +3615,12 @@
         <v>281</v>
       </c>
       <c r="C440" s="8">
-        <v>57</v>
+        <v>90</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="6">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B441" s="7">
         <v>281</v>
@@ -3631,12 +3631,12 @@
         <v>281</v>
       </c>
       <c r="C442" s="8">
-        <v>90</v>
+        <v>145</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="6">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="B443" s="7">
         <v>281</v>
@@ -3647,12 +3647,12 @@
         <v>281</v>
       </c>
       <c r="C444" s="8">
-        <v>145</v>
+        <v>69</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="6">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="B445" s="7">
         <v>281</v>
@@ -3663,12 +3663,12 @@
         <v>281</v>
       </c>
       <c r="C446" s="8">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="6">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B447" s="7">
         <v>281</v>
@@ -3676,82 +3676,82 @@
     </row>
     <row r="448">
       <c r="A448" s="6">
+        <v>232</v>
+      </c>
+      <c r="C448" s="8">
         <v>281</v>
-      </c>
-      <c r="C448" s="8">
-        <v>64</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="6">
-        <v>64</v>
+        <v>281</v>
       </c>
       <c r="B449" s="7">
-        <v>281</v>
+        <v>232</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="6">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="C450" s="8">
-        <v>281</v>
+        <v>66</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="6">
-        <v>281</v>
+        <v>66</v>
       </c>
       <c r="B451" s="7">
-        <v>232</v>
+        <v>282</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="6">
+        <v>283</v>
+      </c>
+      <c r="C452" s="8">
         <v>282</v>
-      </c>
-      <c r="C452" s="8">
-        <v>66</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="6">
-        <v>66</v>
+        <v>282</v>
       </c>
       <c r="B453" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="6">
+        <v>282</v>
+      </c>
+      <c r="C454" s="8">
         <v>283</v>
-      </c>
-      <c r="C454" s="8">
-        <v>282</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="6">
+        <v>283</v>
+      </c>
+      <c r="B455" s="7">
         <v>282</v>
-      </c>
-      <c r="B455" s="7">
-        <v>283</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="6">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C456" s="8">
-        <v>283</v>
+        <v>178</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="6">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="B457" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="458">
@@ -3759,12 +3759,12 @@
         <v>284</v>
       </c>
       <c r="C458" s="8">
-        <v>178</v>
+        <v>68</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="6">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="B459" s="7">
         <v>284</v>
@@ -3775,12 +3775,12 @@
         <v>284</v>
       </c>
       <c r="C460" s="8">
-        <v>68</v>
+        <v>179</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="6">
-        <v>68</v>
+        <v>179</v>
       </c>
       <c r="B461" s="7">
         <v>284</v>
@@ -3791,12 +3791,12 @@
         <v>284</v>
       </c>
       <c r="C462" s="8">
-        <v>179</v>
+        <v>65</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="6">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="B463" s="7">
         <v>284</v>
@@ -3807,12 +3807,12 @@
         <v>284</v>
       </c>
       <c r="C464" s="8">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="6">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B465" s="7">
         <v>284</v>
@@ -3820,34 +3820,34 @@
     </row>
     <row r="466">
       <c r="A466" s="6">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C466" s="8">
-        <v>64</v>
+        <v>286</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="6">
-        <v>64</v>
+        <v>286</v>
       </c>
       <c r="B467" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="6">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C468" s="8">
-        <v>286</v>
+        <v>65</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="6">
+        <v>65</v>
+      </c>
+      <c r="B469" s="7">
         <v>286</v>
-      </c>
-      <c r="B469" s="7">
-        <v>285</v>
       </c>
     </row>
     <row r="470">
@@ -3855,12 +3855,12 @@
         <v>286</v>
       </c>
       <c r="C470" s="8">
-        <v>65</v>
+        <v>22</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="6">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="B471" s="7">
         <v>286</v>
@@ -3871,12 +3871,12 @@
         <v>286</v>
       </c>
       <c r="C472" s="8">
-        <v>22</v>
+        <v>287</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="6">
-        <v>22</v>
+        <v>287</v>
       </c>
       <c r="B473" s="7">
         <v>286</v>
@@ -3887,12 +3887,12 @@
         <v>286</v>
       </c>
       <c r="C474" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="6">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B475" s="7">
         <v>286</v>
@@ -3900,23 +3900,23 @@
     </row>
     <row r="476">
       <c r="A476" s="6">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C476" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="6">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B477" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="6">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="C478" s="8">
         <v>290</v>
@@ -3927,12 +3927,12 @@
         <v>290</v>
       </c>
       <c r="B479" s="7">
-        <v>289</v>
+        <v>116</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="6">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C480" s="8">
         <v>290</v>
@@ -3943,12 +3943,12 @@
         <v>290</v>
       </c>
       <c r="B481" s="7">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="6">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C482" s="8">
         <v>290</v>
@@ -3959,12 +3959,12 @@
         <v>290</v>
       </c>
       <c r="B483" s="7">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="6">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="C484" s="8">
         <v>290</v>
@@ -3975,12 +3975,12 @@
         <v>290</v>
       </c>
       <c r="B485" s="7">
-        <v>111</v>
+        <v>47</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="6">
-        <v>47</v>
+        <v>295</v>
       </c>
       <c r="C486" s="8">
         <v>290</v>
@@ -3991,55 +3991,55 @@
         <v>290</v>
       </c>
       <c r="B487" s="7">
-        <v>47</v>
+        <v>295</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="6">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C488" s="8">
-        <v>290</v>
+        <v>178</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="6">
-        <v>290</v>
+        <v>178</v>
       </c>
       <c r="B489" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="6">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C490" s="8">
-        <v>178</v>
+        <v>302</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="6">
-        <v>178</v>
+        <v>302</v>
       </c>
       <c r="B491" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="6">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C492" s="8">
-        <v>302</v>
+        <v>62</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="6">
-        <v>302</v>
+        <v>62</v>
       </c>
       <c r="B493" s="7">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="494">
@@ -4047,12 +4047,12 @@
         <v>311</v>
       </c>
       <c r="C494" s="8">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="6">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B495" s="7">
         <v>311</v>
@@ -4060,18 +4060,18 @@
     </row>
     <row r="496">
       <c r="A496" s="6">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="C496" s="8">
-        <v>53</v>
+        <v>106</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="6">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B497" s="7">
-        <v>311</v>
+        <v>84</v>
       </c>
     </row>
     <row r="498">
@@ -4079,12 +4079,12 @@
         <v>84</v>
       </c>
       <c r="C498" s="8">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="6">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B499" s="7">
         <v>84</v>
@@ -4095,12 +4095,12 @@
         <v>84</v>
       </c>
       <c r="C500" s="8">
-        <v>49</v>
+        <v>125</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="6">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="B501" s="7">
         <v>84</v>
@@ -4111,12 +4111,12 @@
         <v>84</v>
       </c>
       <c r="C502" s="8">
-        <v>125</v>
+        <v>47</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="6">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="B503" s="7">
         <v>84</v>
@@ -4124,18 +4124,18 @@
     </row>
     <row r="504">
       <c r="A504" s="6">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="C504" s="8">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="6">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B505" s="7">
-        <v>84</v>
+        <v>312</v>
       </c>
     </row>
     <row r="506">
@@ -4143,12 +4143,12 @@
         <v>312</v>
       </c>
       <c r="C506" s="8">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="6">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B507" s="7">
         <v>312</v>
@@ -4156,34 +4156,34 @@
     </row>
     <row r="508">
       <c r="A508" s="6">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="C508" s="8">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="6">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B509" s="7">
-        <v>312</v>
+        <v>118</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="6">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C510" s="8">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B511" s="7">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="512">
@@ -4191,12 +4191,12 @@
         <v>97</v>
       </c>
       <c r="C512" s="8">
-        <v>70</v>
+        <v>322</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="6">
-        <v>70</v>
+        <v>322</v>
       </c>
       <c r="B513" s="7">
         <v>97</v>
@@ -4204,34 +4204,34 @@
     </row>
     <row r="514">
       <c r="A514" s="6">
-        <v>97</v>
+        <v>325</v>
       </c>
       <c r="C514" s="8">
-        <v>322</v>
+        <v>163</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="6">
-        <v>322</v>
+        <v>163</v>
       </c>
       <c r="B515" s="7">
-        <v>97</v>
+        <v>325</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="6">
-        <v>325</v>
+        <v>14</v>
       </c>
       <c r="C516" s="8">
-        <v>163</v>
+        <v>24</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="6">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="B517" s="7">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="518">
@@ -4239,12 +4239,12 @@
         <v>14</v>
       </c>
       <c r="C518" s="8">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="6">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="B519" s="7">
         <v>14</v>
@@ -4255,12 +4255,12 @@
         <v>14</v>
       </c>
       <c r="C520" s="8">
-        <v>63</v>
+        <v>260</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="6">
-        <v>63</v>
+        <v>260</v>
       </c>
       <c r="B521" s="7">
         <v>14</v>
@@ -4268,18 +4268,18 @@
     </row>
     <row r="522">
       <c r="A522" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C522" s="8">
-        <v>260</v>
+        <v>66</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="6">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="B523" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="524">
@@ -4287,12 +4287,12 @@
         <v>19</v>
       </c>
       <c r="C524" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="6">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B525" s="7">
         <v>19</v>
@@ -4300,39 +4300,39 @@
     </row>
     <row r="526">
       <c r="A526" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C526" s="8">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="6">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B527" s="7">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="6">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="C528" s="8">
-        <v>65</v>
+        <v>329</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="6">
-        <v>65</v>
+        <v>329</v>
       </c>
       <c r="B529" s="7">
-        <v>22</v>
+        <v>78</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="6">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="C530" s="8">
         <v>329</v>
@@ -4343,23 +4343,23 @@
         <v>329</v>
       </c>
       <c r="B531" s="7">
-        <v>78</v>
+        <v>22</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="6">
-        <v>22</v>
+        <v>223</v>
       </c>
       <c r="C532" s="8">
-        <v>329</v>
+        <v>59</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="6">
-        <v>329</v>
+        <v>59</v>
       </c>
       <c r="B533" s="7">
-        <v>22</v>
+        <v>223</v>
       </c>
     </row>
     <row r="534">
@@ -4367,12 +4367,12 @@
         <v>223</v>
       </c>
       <c r="C534" s="8">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="6">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="B535" s="7">
         <v>223</v>
@@ -4383,12 +4383,12 @@
         <v>223</v>
       </c>
       <c r="C536" s="8">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="6">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B537" s="7">
         <v>223</v>
@@ -4396,18 +4396,18 @@
     </row>
     <row r="538">
       <c r="A538" s="6">
-        <v>223</v>
+        <v>352</v>
       </c>
       <c r="C538" s="8">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="6">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B539" s="7">
-        <v>223</v>
+        <v>352</v>
       </c>
     </row>
     <row r="540">
@@ -4415,12 +4415,12 @@
         <v>352</v>
       </c>
       <c r="C540" s="8">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="6">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B541" s="7">
         <v>352</v>
@@ -4428,18 +4428,18 @@
     </row>
     <row r="542">
       <c r="A542" s="6">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C542" s="8">
-        <v>64</v>
+        <v>341</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="6">
-        <v>64</v>
+        <v>341</v>
       </c>
       <c r="B543" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="544">
@@ -4447,12 +4447,12 @@
         <v>354</v>
       </c>
       <c r="C544" s="8">
-        <v>341</v>
+        <v>19</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="6">
-        <v>341</v>
+        <v>19</v>
       </c>
       <c r="B545" s="7">
         <v>354</v>
@@ -4463,12 +4463,12 @@
         <v>354</v>
       </c>
       <c r="C546" s="8">
-        <v>19</v>
+        <v>355</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="6">
-        <v>19</v>
+        <v>355</v>
       </c>
       <c r="B547" s="7">
         <v>354</v>
@@ -4479,12 +4479,12 @@
         <v>354</v>
       </c>
       <c r="C548" s="8">
-        <v>355</v>
+        <v>135</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="6">
-        <v>355</v>
+        <v>135</v>
       </c>
       <c r="B549" s="7">
         <v>354</v>
@@ -4495,12 +4495,12 @@
         <v>354</v>
       </c>
       <c r="C550" s="8">
-        <v>135</v>
+        <v>164</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="6">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="B551" s="7">
         <v>354</v>
@@ -4508,34 +4508,34 @@
     </row>
     <row r="552">
       <c r="A552" s="6">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="C552" s="8">
-        <v>164</v>
+        <v>355</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="6">
-        <v>164</v>
+        <v>355</v>
       </c>
       <c r="B553" s="7">
-        <v>354</v>
+        <v>308</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="6">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="C554" s="8">
-        <v>355</v>
+        <v>164</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="6">
-        <v>355</v>
+        <v>164</v>
       </c>
       <c r="B555" s="7">
-        <v>308</v>
+        <v>166</v>
       </c>
     </row>
     <row r="556">
@@ -4543,12 +4543,12 @@
         <v>166</v>
       </c>
       <c r="C556" s="8">
-        <v>164</v>
+        <v>356</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="6">
-        <v>164</v>
+        <v>356</v>
       </c>
       <c r="B557" s="7">
         <v>166</v>
@@ -4559,12 +4559,12 @@
         <v>166</v>
       </c>
       <c r="C558" s="8">
-        <v>356</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="6">
-        <v>356</v>
+        <v>1</v>
       </c>
       <c r="B559" s="7">
         <v>166</v>
@@ -4572,18 +4572,18 @@
     </row>
     <row r="560">
       <c r="A560" s="6">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C560" s="8">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="6">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="B561" s="7">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="562">
@@ -4591,12 +4591,12 @@
         <v>137</v>
       </c>
       <c r="C562" s="8">
-        <v>79</v>
+        <v>128</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="6">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="B563" s="7">
         <v>137</v>
@@ -4607,12 +4607,12 @@
         <v>137</v>
       </c>
       <c r="C564" s="8">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="6">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B565" s="7">
         <v>137</v>
@@ -4623,12 +4623,12 @@
         <v>137</v>
       </c>
       <c r="C566" s="8">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="6">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B567" s="7">
         <v>137</v>
@@ -4639,12 +4639,12 @@
         <v>137</v>
       </c>
       <c r="C568" s="8">
-        <v>115</v>
+        <v>58</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="6">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="B569" s="7">
         <v>137</v>
@@ -4655,12 +4655,12 @@
         <v>137</v>
       </c>
       <c r="C570" s="8">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="6">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="B571" s="7">
         <v>137</v>
@@ -4671,12 +4671,12 @@
         <v>137</v>
       </c>
       <c r="C572" s="8">
-        <v>99</v>
+        <v>357</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="6">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="B573" s="7">
         <v>137</v>
@@ -4684,23 +4684,23 @@
     </row>
     <row r="574">
       <c r="A574" s="6">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="C574" s="8">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="6">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B575" s="7">
-        <v>137</v>
+        <v>55</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="6">
-        <v>55</v>
+        <v>363</v>
       </c>
       <c r="C576" s="8">
         <v>362</v>
@@ -4711,12 +4711,12 @@
         <v>362</v>
       </c>
       <c r="B577" s="7">
-        <v>55</v>
+        <v>363</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="6">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C578" s="8">
         <v>362</v>
@@ -4727,23 +4727,23 @@
         <v>362</v>
       </c>
       <c r="B579" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="6">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C580" s="8">
-        <v>362</v>
+        <v>133</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="6">
-        <v>362</v>
+        <v>133</v>
       </c>
       <c r="B581" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="582">
@@ -4751,12 +4751,12 @@
         <v>367</v>
       </c>
       <c r="C582" s="8">
-        <v>133</v>
+        <v>368</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="6">
-        <v>133</v>
+        <v>368</v>
       </c>
       <c r="B583" s="7">
         <v>367</v>
@@ -4764,50 +4764,50 @@
     </row>
     <row r="584">
       <c r="A584" s="6">
-        <v>367</v>
+        <v>180</v>
       </c>
       <c r="C584" s="8">
-        <v>368</v>
+        <v>68</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="6">
-        <v>368</v>
+        <v>68</v>
       </c>
       <c r="B585" s="7">
-        <v>367</v>
+        <v>180</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="6">
-        <v>180</v>
+        <v>387</v>
       </c>
       <c r="C586" s="8">
-        <v>68</v>
+        <v>369</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="6">
-        <v>68</v>
+        <v>369</v>
       </c>
       <c r="B587" s="7">
-        <v>180</v>
+        <v>387</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="6">
-        <v>387</v>
+        <v>65</v>
       </c>
       <c r="C588" s="8">
-        <v>369</v>
+        <v>178</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="6">
-        <v>369</v>
+        <v>178</v>
       </c>
       <c r="B589" s="7">
-        <v>387</v>
+        <v>65</v>
       </c>
     </row>
     <row r="590">
@@ -4815,12 +4815,12 @@
         <v>65</v>
       </c>
       <c r="C590" s="8">
-        <v>178</v>
+        <v>68</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="6">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="B591" s="7">
         <v>65</v>
@@ -4828,34 +4828,34 @@
     </row>
     <row r="592">
       <c r="A592" s="6">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="C592" s="8">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="6">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B593" s="7">
-        <v>65</v>
+        <v>178</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="6">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="C594" s="8">
-        <v>66</v>
+        <v>400</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="6">
-        <v>66</v>
+        <v>400</v>
       </c>
       <c r="B595" s="7">
-        <v>178</v>
+        <v>65</v>
       </c>
     </row>
     <row r="596">
@@ -4863,12 +4863,12 @@
         <v>65</v>
       </c>
       <c r="C596" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="6">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B597" s="7">
         <v>65</v>
@@ -4879,12 +4879,12 @@
         <v>65</v>
       </c>
       <c r="C598" s="8">
-        <v>403</v>
+        <v>329</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="6">
-        <v>403</v>
+        <v>329</v>
       </c>
       <c r="B599" s="7">
         <v>65</v>
@@ -4892,23 +4892,23 @@
     </row>
     <row r="600">
       <c r="A600" s="6">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="C600" s="8">
-        <v>329</v>
+        <v>290</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="6">
-        <v>329</v>
+        <v>290</v>
       </c>
       <c r="B601" s="7">
-        <v>65</v>
+        <v>260</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="6">
-        <v>260</v>
+        <v>128</v>
       </c>
       <c r="C602" s="8">
         <v>290</v>
@@ -4919,44 +4919,44 @@
         <v>290</v>
       </c>
       <c r="B603" s="7">
-        <v>260</v>
+        <v>128</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="6">
-        <v>128</v>
+        <v>195</v>
       </c>
       <c r="C604" s="8">
-        <v>290</v>
+        <v>404</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="6">
-        <v>290</v>
+        <v>404</v>
       </c>
       <c r="B605" s="7">
-        <v>128</v>
+        <v>195</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="6">
-        <v>195</v>
+        <v>302</v>
       </c>
       <c r="C606" s="8">
-        <v>404</v>
+        <v>145</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="6">
-        <v>404</v>
+        <v>145</v>
       </c>
       <c r="B607" s="7">
-        <v>195</v>
+        <v>302</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="6">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="C608" s="8">
         <v>145</v>
@@ -4967,12 +4967,12 @@
         <v>145</v>
       </c>
       <c r="B609" s="7">
-        <v>302</v>
+        <v>405</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="6">
-        <v>405</v>
+        <v>207</v>
       </c>
       <c r="C610" s="8">
         <v>145</v>
@@ -4983,23 +4983,23 @@
         <v>145</v>
       </c>
       <c r="B611" s="7">
-        <v>405</v>
+        <v>207</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="6">
-        <v>207</v>
+        <v>410</v>
       </c>
       <c r="C612" s="8">
-        <v>145</v>
+        <v>306</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="6">
-        <v>145</v>
+        <v>306</v>
       </c>
       <c r="B613" s="7">
-        <v>207</v>
+        <v>410</v>
       </c>
     </row>
     <row r="614">
@@ -5007,12 +5007,12 @@
         <v>410</v>
       </c>
       <c r="C614" s="8">
-        <v>306</v>
+        <v>128</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="6">
-        <v>306</v>
+        <v>128</v>
       </c>
       <c r="B615" s="7">
         <v>410</v>
@@ -5020,23 +5020,23 @@
     </row>
     <row r="616">
       <c r="A616" s="6">
-        <v>410</v>
+        <v>337</v>
       </c>
       <c r="C616" s="8">
-        <v>128</v>
+        <v>290</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="6">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="B617" s="7">
-        <v>410</v>
+        <v>337</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="6">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C618" s="8">
         <v>290</v>
@@ -5047,12 +5047,12 @@
         <v>290</v>
       </c>
       <c r="B619" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="6">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C620" s="8">
         <v>290</v>
@@ -5063,12 +5063,12 @@
         <v>290</v>
       </c>
       <c r="B621" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="6">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="C622" s="8">
         <v>290</v>
@@ -5079,12 +5079,12 @@
         <v>290</v>
       </c>
       <c r="B623" s="7">
-        <v>340</v>
+        <v>357</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="6">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C624" s="8">
         <v>290</v>
@@ -5095,12 +5095,12 @@
         <v>290</v>
       </c>
       <c r="B625" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="6">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C626" s="8">
         <v>290</v>
@@ -5111,28 +5111,28 @@
         <v>290</v>
       </c>
       <c r="B627" s="7">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="6">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C628" s="8">
-        <v>290</v>
+        <v>415</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="6">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="B629" s="7">
-        <v>379</v>
+        <v>393</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="6">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="C630" s="8">
         <v>415</v>
@@ -5143,12 +5143,12 @@
         <v>415</v>
       </c>
       <c r="B631" s="7">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="6">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C632" s="8">
         <v>415</v>
@@ -5159,12 +5159,12 @@
         <v>415</v>
       </c>
       <c r="B633" s="7">
-        <v>406</v>
+        <v>416</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="6">
-        <v>416</v>
+        <v>218</v>
       </c>
       <c r="C634" s="8">
         <v>415</v>
@@ -5175,7 +5175,7 @@
         <v>415</v>
       </c>
       <c r="B635" s="7">
-        <v>416</v>
+        <v>218</v>
       </c>
     </row>
     <row r="636">
@@ -5183,12 +5183,12 @@
         <v>218</v>
       </c>
       <c r="C636" s="8">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="6">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B637" s="7">
         <v>218</v>
@@ -5196,23 +5196,23 @@
     </row>
     <row r="638">
       <c r="A638" s="6">
-        <v>218</v>
+        <v>421</v>
       </c>
       <c r="C638" s="8">
-        <v>419</v>
+        <v>306</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="6">
-        <v>419</v>
+        <v>306</v>
       </c>
       <c r="B639" s="7">
-        <v>218</v>
+        <v>421</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="6">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C640" s="8">
         <v>306</v>
@@ -5223,12 +5223,12 @@
         <v>306</v>
       </c>
       <c r="B641" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="6">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C642" s="8">
         <v>306</v>
@@ -5239,12 +5239,12 @@
         <v>306</v>
       </c>
       <c r="B643" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="6">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C644" s="8">
         <v>306</v>
@@ -5255,7 +5255,7 @@
         <v>306</v>
       </c>
       <c r="B645" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="646">
@@ -5263,12 +5263,12 @@
         <v>424</v>
       </c>
       <c r="C646" s="8">
-        <v>306</v>
+        <v>425</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="6">
-        <v>306</v>
+        <v>425</v>
       </c>
       <c r="B647" s="7">
         <v>424</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="648">
       <c r="A648" s="6">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C648" s="8">
         <v>425</v>
@@ -5287,12 +5287,12 @@
         <v>425</v>
       </c>
       <c r="B649" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="6">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C650" s="8">
         <v>425</v>
@@ -5303,7 +5303,7 @@
         <v>425</v>
       </c>
       <c r="B651" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="652">
@@ -5311,12 +5311,12 @@
         <v>426</v>
       </c>
       <c r="C652" s="8">
-        <v>425</v>
+        <v>306</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="6">
-        <v>425</v>
+        <v>306</v>
       </c>
       <c r="B653" s="7">
         <v>426</v>
@@ -5327,12 +5327,12 @@
         <v>426</v>
       </c>
       <c r="C654" s="8">
-        <v>306</v>
+        <v>422</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="6">
-        <v>306</v>
+        <v>422</v>
       </c>
       <c r="B655" s="7">
         <v>426</v>
@@ -5340,18 +5340,18 @@
     </row>
     <row r="656">
       <c r="A656" s="6">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C656" s="8">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="6">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B657" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="658">
@@ -5359,12 +5359,12 @@
         <v>427</v>
       </c>
       <c r="C658" s="8">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="6">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B659" s="7">
         <v>427</v>
@@ -5372,18 +5372,178 @@
     </row>
     <row r="660">
       <c r="A660" s="6">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C660" s="8">
-        <v>422</v>
+        <v>224</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="6">
-        <v>422</v>
+        <v>224</v>
       </c>
       <c r="B661" s="7">
-        <v>427</v>
+        <v>429</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="6">
+        <v>429</v>
+      </c>
+      <c r="C662" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="6">
+        <v>17</v>
+      </c>
+      <c r="B663" s="7">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="6">
+        <v>430</v>
+      </c>
+      <c r="C664" s="8">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="6">
+        <v>135</v>
+      </c>
+      <c r="B665" s="7">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="6">
+        <v>63</v>
+      </c>
+      <c r="C666" s="8">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="6">
+        <v>437</v>
+      </c>
+      <c r="B667" s="7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="6">
+        <v>63</v>
+      </c>
+      <c r="C668" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="6">
+        <v>438</v>
+      </c>
+      <c r="B669" s="7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="6">
+        <v>63</v>
+      </c>
+      <c r="C670" s="8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="6">
+        <v>62</v>
+      </c>
+      <c r="B671" s="7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="6">
+        <v>425</v>
+      </c>
+      <c r="C672" s="8">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="6">
+        <v>306</v>
+      </c>
+      <c r="B673" s="7">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="6">
+        <v>444</v>
+      </c>
+      <c r="C674" s="8">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="6">
+        <v>392</v>
+      </c>
+      <c r="B675" s="7">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="6">
+        <v>444</v>
+      </c>
+      <c r="C676" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="6">
+        <v>64</v>
+      </c>
+      <c r="B677" s="7">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="6">
+        <v>59</v>
+      </c>
+      <c r="C678" s="8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="6">
+        <v>65</v>
+      </c>
+      <c r="B679" s="7">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="6">
+        <v>59</v>
+      </c>
+      <c r="C680" s="8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="6">
+        <v>400</v>
+      </c>
+      <c r="B681" s="7">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Concepthierarchy.xlsx
+++ b/raw/Concepthierarchy.xlsx
@@ -5546,6 +5546,262 @@
         <v>59</v>
       </c>
     </row>
+    <row r="682">
+      <c r="A682" s="6">
+        <v>450</v>
+      </c>
+      <c r="C682" s="8">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="6">
+        <v>69</v>
+      </c>
+      <c r="B683" s="7">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="6">
+        <v>388</v>
+      </c>
+      <c r="C684" s="8">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="6">
+        <v>363</v>
+      </c>
+      <c r="B685" s="7">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="6">
+        <v>201</v>
+      </c>
+      <c r="C686" s="8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="6">
+        <v>65</v>
+      </c>
+      <c r="B687" s="7">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="6">
+        <v>96</v>
+      </c>
+      <c r="C688" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="6">
+        <v>1</v>
+      </c>
+      <c r="B689" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="6">
+        <v>96</v>
+      </c>
+      <c r="C690" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="6">
+        <v>79</v>
+      </c>
+      <c r="B691" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="6">
+        <v>96</v>
+      </c>
+      <c r="C692" s="8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="6">
+        <v>90</v>
+      </c>
+      <c r="B693" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="6">
+        <v>95</v>
+      </c>
+      <c r="C694" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="6">
+        <v>1</v>
+      </c>
+      <c r="B695" s="7">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="6">
+        <v>457</v>
+      </c>
+      <c r="C696" s="8">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="6">
+        <v>355</v>
+      </c>
+      <c r="B697" s="7">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="6">
+        <v>457</v>
+      </c>
+      <c r="C698" s="8">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="6">
+        <v>209</v>
+      </c>
+      <c r="B699" s="7">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="6">
+        <v>394</v>
+      </c>
+      <c r="C700" s="8">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="6">
+        <v>63</v>
+      </c>
+      <c r="B701" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="6">
+        <v>394</v>
+      </c>
+      <c r="C702" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="6">
+        <v>438</v>
+      </c>
+      <c r="B703" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="6">
+        <v>394</v>
+      </c>
+      <c r="C704" s="8">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="6">
+        <v>458</v>
+      </c>
+      <c r="B705" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="6">
+        <v>286</v>
+      </c>
+      <c r="C706" s="8">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="6">
+        <v>458</v>
+      </c>
+      <c r="B707" s="7">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="6">
+        <v>466</v>
+      </c>
+      <c r="C708" s="8">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="6">
+        <v>467</v>
+      </c>
+      <c r="B709" s="7">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="6">
+        <v>467</v>
+      </c>
+      <c r="C710" s="8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="6">
+        <v>55</v>
+      </c>
+      <c r="B711" s="7">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="6">
+        <v>466</v>
+      </c>
+      <c r="C712" s="8">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="6">
+        <v>178</v>
+      </c>
+      <c r="B713" s="7">
+        <v>466</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Concepthierarchy.xlsx
+++ b/raw/Concepthierarchy.xlsx
@@ -3676,66 +3676,66 @@
     </row>
     <row r="448">
       <c r="A448" s="6">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="C448" s="8">
-        <v>281</v>
+        <v>66</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="6">
-        <v>281</v>
+        <v>66</v>
       </c>
       <c r="B449" s="7">
-        <v>232</v>
+        <v>282</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="6">
+        <v>283</v>
+      </c>
+      <c r="C450" s="8">
         <v>282</v>
-      </c>
-      <c r="C450" s="8">
-        <v>66</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="6">
-        <v>66</v>
+        <v>282</v>
       </c>
       <c r="B451" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="6">
+        <v>282</v>
+      </c>
+      <c r="C452" s="8">
         <v>283</v>
-      </c>
-      <c r="C452" s="8">
-        <v>282</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="6">
+        <v>283</v>
+      </c>
+      <c r="B453" s="7">
         <v>282</v>
-      </c>
-      <c r="B453" s="7">
-        <v>283</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="6">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C454" s="8">
-        <v>283</v>
+        <v>178</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="6">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="B455" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="456">
@@ -3743,12 +3743,12 @@
         <v>284</v>
       </c>
       <c r="C456" s="8">
-        <v>178</v>
+        <v>68</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="6">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="B457" s="7">
         <v>284</v>
@@ -3759,12 +3759,12 @@
         <v>284</v>
       </c>
       <c r="C458" s="8">
-        <v>68</v>
+        <v>179</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="6">
-        <v>68</v>
+        <v>179</v>
       </c>
       <c r="B459" s="7">
         <v>284</v>
@@ -3775,12 +3775,12 @@
         <v>284</v>
       </c>
       <c r="C460" s="8">
-        <v>179</v>
+        <v>65</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="6">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="B461" s="7">
         <v>284</v>
@@ -3791,12 +3791,12 @@
         <v>284</v>
       </c>
       <c r="C462" s="8">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="6">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B463" s="7">
         <v>284</v>
@@ -3804,34 +3804,34 @@
     </row>
     <row r="464">
       <c r="A464" s="6">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C464" s="8">
-        <v>64</v>
+        <v>286</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="6">
-        <v>64</v>
+        <v>286</v>
       </c>
       <c r="B465" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="6">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C466" s="8">
-        <v>286</v>
+        <v>65</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="6">
+        <v>65</v>
+      </c>
+      <c r="B467" s="7">
         <v>286</v>
-      </c>
-      <c r="B467" s="7">
-        <v>285</v>
       </c>
     </row>
     <row r="468">
@@ -3839,12 +3839,12 @@
         <v>286</v>
       </c>
       <c r="C468" s="8">
-        <v>65</v>
+        <v>22</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="6">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="B469" s="7">
         <v>286</v>
@@ -3855,12 +3855,12 @@
         <v>286</v>
       </c>
       <c r="C470" s="8">
-        <v>22</v>
+        <v>287</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="6">
-        <v>22</v>
+        <v>287</v>
       </c>
       <c r="B471" s="7">
         <v>286</v>
@@ -3871,12 +3871,12 @@
         <v>286</v>
       </c>
       <c r="C472" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="6">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B473" s="7">
         <v>286</v>
@@ -3884,23 +3884,23 @@
     </row>
     <row r="474">
       <c r="A474" s="6">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C474" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="6">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B475" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="6">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="C476" s="8">
         <v>290</v>
@@ -3911,12 +3911,12 @@
         <v>290</v>
       </c>
       <c r="B477" s="7">
-        <v>289</v>
+        <v>116</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="6">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C478" s="8">
         <v>290</v>
@@ -3927,12 +3927,12 @@
         <v>290</v>
       </c>
       <c r="B479" s="7">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="6">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C480" s="8">
         <v>290</v>
@@ -3943,12 +3943,12 @@
         <v>290</v>
       </c>
       <c r="B481" s="7">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="6">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="C482" s="8">
         <v>290</v>
@@ -3959,12 +3959,12 @@
         <v>290</v>
       </c>
       <c r="B483" s="7">
-        <v>111</v>
+        <v>47</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="6">
-        <v>47</v>
+        <v>295</v>
       </c>
       <c r="C484" s="8">
         <v>290</v>
@@ -3975,55 +3975,55 @@
         <v>290</v>
       </c>
       <c r="B485" s="7">
-        <v>47</v>
+        <v>295</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="6">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C486" s="8">
-        <v>290</v>
+        <v>178</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="6">
-        <v>290</v>
+        <v>178</v>
       </c>
       <c r="B487" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="6">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C488" s="8">
-        <v>178</v>
+        <v>302</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="6">
-        <v>178</v>
+        <v>302</v>
       </c>
       <c r="B489" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="6">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C490" s="8">
-        <v>302</v>
+        <v>62</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="6">
-        <v>302</v>
+        <v>62</v>
       </c>
       <c r="B491" s="7">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="492">
@@ -4031,12 +4031,12 @@
         <v>311</v>
       </c>
       <c r="C492" s="8">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="6">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B493" s="7">
         <v>311</v>
@@ -4044,18 +4044,18 @@
     </row>
     <row r="494">
       <c r="A494" s="6">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="C494" s="8">
-        <v>53</v>
+        <v>106</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="6">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B495" s="7">
-        <v>311</v>
+        <v>84</v>
       </c>
     </row>
     <row r="496">
@@ -4063,12 +4063,12 @@
         <v>84</v>
       </c>
       <c r="C496" s="8">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="6">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B497" s="7">
         <v>84</v>
@@ -4079,12 +4079,12 @@
         <v>84</v>
       </c>
       <c r="C498" s="8">
-        <v>49</v>
+        <v>125</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="6">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="B499" s="7">
         <v>84</v>
@@ -4095,12 +4095,12 @@
         <v>84</v>
       </c>
       <c r="C500" s="8">
-        <v>125</v>
+        <v>47</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="6">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="B501" s="7">
         <v>84</v>
@@ -4108,18 +4108,18 @@
     </row>
     <row r="502">
       <c r="A502" s="6">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="C502" s="8">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="6">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B503" s="7">
-        <v>84</v>
+        <v>312</v>
       </c>
     </row>
     <row r="504">
@@ -4127,12 +4127,12 @@
         <v>312</v>
       </c>
       <c r="C504" s="8">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="6">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B505" s="7">
         <v>312</v>
@@ -4140,34 +4140,34 @@
     </row>
     <row r="506">
       <c r="A506" s="6">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="C506" s="8">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="6">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B507" s="7">
-        <v>312</v>
+        <v>118</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="6">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C508" s="8">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B509" s="7">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="510">
@@ -4175,12 +4175,12 @@
         <v>97</v>
       </c>
       <c r="C510" s="8">
-        <v>70</v>
+        <v>322</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="6">
-        <v>70</v>
+        <v>322</v>
       </c>
       <c r="B511" s="7">
         <v>97</v>
@@ -4188,34 +4188,34 @@
     </row>
     <row r="512">
       <c r="A512" s="6">
-        <v>97</v>
+        <v>325</v>
       </c>
       <c r="C512" s="8">
-        <v>322</v>
+        <v>163</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="6">
-        <v>322</v>
+        <v>163</v>
       </c>
       <c r="B513" s="7">
-        <v>97</v>
+        <v>325</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="6">
-        <v>325</v>
+        <v>14</v>
       </c>
       <c r="C514" s="8">
-        <v>163</v>
+        <v>24</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="6">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="B515" s="7">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="516">
@@ -4223,12 +4223,12 @@
         <v>14</v>
       </c>
       <c r="C516" s="8">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="6">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="B517" s="7">
         <v>14</v>
@@ -4239,12 +4239,12 @@
         <v>14</v>
       </c>
       <c r="C518" s="8">
-        <v>63</v>
+        <v>260</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="6">
-        <v>63</v>
+        <v>260</v>
       </c>
       <c r="B519" s="7">
         <v>14</v>
@@ -4252,18 +4252,18 @@
     </row>
     <row r="520">
       <c r="A520" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C520" s="8">
-        <v>260</v>
+        <v>66</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="6">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="B521" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="522">
@@ -4271,12 +4271,12 @@
         <v>19</v>
       </c>
       <c r="C522" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="6">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B523" s="7">
         <v>19</v>
@@ -4284,39 +4284,39 @@
     </row>
     <row r="524">
       <c r="A524" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C524" s="8">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="6">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B525" s="7">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="6">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="C526" s="8">
-        <v>65</v>
+        <v>329</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="6">
-        <v>65</v>
+        <v>329</v>
       </c>
       <c r="B527" s="7">
-        <v>22</v>
+        <v>78</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="6">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="C528" s="8">
         <v>329</v>
@@ -4327,23 +4327,23 @@
         <v>329</v>
       </c>
       <c r="B529" s="7">
-        <v>78</v>
+        <v>22</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="6">
-        <v>22</v>
+        <v>223</v>
       </c>
       <c r="C530" s="8">
-        <v>329</v>
+        <v>59</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="6">
-        <v>329</v>
+        <v>59</v>
       </c>
       <c r="B531" s="7">
-        <v>22</v>
+        <v>223</v>
       </c>
     </row>
     <row r="532">
@@ -4351,12 +4351,12 @@
         <v>223</v>
       </c>
       <c r="C532" s="8">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="6">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="B533" s="7">
         <v>223</v>
@@ -4367,12 +4367,12 @@
         <v>223</v>
       </c>
       <c r="C534" s="8">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="6">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B535" s="7">
         <v>223</v>
@@ -4380,18 +4380,18 @@
     </row>
     <row r="536">
       <c r="A536" s="6">
-        <v>223</v>
+        <v>352</v>
       </c>
       <c r="C536" s="8">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="6">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B537" s="7">
-        <v>223</v>
+        <v>352</v>
       </c>
     </row>
     <row r="538">
@@ -4399,12 +4399,12 @@
         <v>352</v>
       </c>
       <c r="C538" s="8">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="6">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B539" s="7">
         <v>352</v>
@@ -4412,18 +4412,18 @@
     </row>
     <row r="540">
       <c r="A540" s="6">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C540" s="8">
-        <v>64</v>
+        <v>341</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="6">
-        <v>64</v>
+        <v>341</v>
       </c>
       <c r="B541" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="542">
@@ -4431,12 +4431,12 @@
         <v>354</v>
       </c>
       <c r="C542" s="8">
-        <v>341</v>
+        <v>19</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="6">
-        <v>341</v>
+        <v>19</v>
       </c>
       <c r="B543" s="7">
         <v>354</v>
@@ -4447,12 +4447,12 @@
         <v>354</v>
       </c>
       <c r="C544" s="8">
-        <v>19</v>
+        <v>355</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="6">
-        <v>19</v>
+        <v>355</v>
       </c>
       <c r="B545" s="7">
         <v>354</v>
@@ -4463,12 +4463,12 @@
         <v>354</v>
       </c>
       <c r="C546" s="8">
-        <v>355</v>
+        <v>135</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="6">
-        <v>355</v>
+        <v>135</v>
       </c>
       <c r="B547" s="7">
         <v>354</v>
@@ -4479,12 +4479,12 @@
         <v>354</v>
       </c>
       <c r="C548" s="8">
-        <v>135</v>
+        <v>164</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="6">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="B549" s="7">
         <v>354</v>
@@ -4492,34 +4492,34 @@
     </row>
     <row r="550">
       <c r="A550" s="6">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="C550" s="8">
-        <v>164</v>
+        <v>355</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="6">
-        <v>164</v>
+        <v>355</v>
       </c>
       <c r="B551" s="7">
-        <v>354</v>
+        <v>308</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="6">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="C552" s="8">
-        <v>355</v>
+        <v>164</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="6">
-        <v>355</v>
+        <v>164</v>
       </c>
       <c r="B553" s="7">
-        <v>308</v>
+        <v>166</v>
       </c>
     </row>
     <row r="554">
@@ -4527,12 +4527,12 @@
         <v>166</v>
       </c>
       <c r="C554" s="8">
-        <v>164</v>
+        <v>356</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="6">
-        <v>164</v>
+        <v>356</v>
       </c>
       <c r="B555" s="7">
         <v>166</v>
@@ -4543,12 +4543,12 @@
         <v>166</v>
       </c>
       <c r="C556" s="8">
-        <v>356</v>
+        <v>1</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="6">
-        <v>356</v>
+        <v>1</v>
       </c>
       <c r="B557" s="7">
         <v>166</v>
@@ -4556,18 +4556,18 @@
     </row>
     <row r="558">
       <c r="A558" s="6">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C558" s="8">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="6">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="B559" s="7">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="560">
@@ -4575,12 +4575,12 @@
         <v>137</v>
       </c>
       <c r="C560" s="8">
-        <v>79</v>
+        <v>128</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="6">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="B561" s="7">
         <v>137</v>
@@ -4591,12 +4591,12 @@
         <v>137</v>
       </c>
       <c r="C562" s="8">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="6">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B563" s="7">
         <v>137</v>
@@ -4607,12 +4607,12 @@
         <v>137</v>
       </c>
       <c r="C564" s="8">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="6">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B565" s="7">
         <v>137</v>
@@ -4623,12 +4623,12 @@
         <v>137</v>
       </c>
       <c r="C566" s="8">
-        <v>115</v>
+        <v>58</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="6">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="B567" s="7">
         <v>137</v>
@@ -4639,12 +4639,12 @@
         <v>137</v>
       </c>
       <c r="C568" s="8">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="6">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="B569" s="7">
         <v>137</v>
@@ -4655,12 +4655,12 @@
         <v>137</v>
       </c>
       <c r="C570" s="8">
-        <v>99</v>
+        <v>357</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="6">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="B571" s="7">
         <v>137</v>
@@ -4668,23 +4668,23 @@
     </row>
     <row r="572">
       <c r="A572" s="6">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="C572" s="8">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="6">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B573" s="7">
-        <v>137</v>
+        <v>55</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="6">
-        <v>55</v>
+        <v>363</v>
       </c>
       <c r="C574" s="8">
         <v>362</v>
@@ -4695,12 +4695,12 @@
         <v>362</v>
       </c>
       <c r="B575" s="7">
-        <v>55</v>
+        <v>363</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="6">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C576" s="8">
         <v>362</v>
@@ -4711,23 +4711,23 @@
         <v>362</v>
       </c>
       <c r="B577" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="6">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C578" s="8">
-        <v>362</v>
+        <v>133</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="6">
-        <v>362</v>
+        <v>133</v>
       </c>
       <c r="B579" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="580">
@@ -4735,12 +4735,12 @@
         <v>367</v>
       </c>
       <c r="C580" s="8">
-        <v>133</v>
+        <v>368</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="6">
-        <v>133</v>
+        <v>368</v>
       </c>
       <c r="B581" s="7">
         <v>367</v>
@@ -4748,50 +4748,50 @@
     </row>
     <row r="582">
       <c r="A582" s="6">
-        <v>367</v>
+        <v>180</v>
       </c>
       <c r="C582" s="8">
-        <v>368</v>
+        <v>68</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="6">
-        <v>368</v>
+        <v>68</v>
       </c>
       <c r="B583" s="7">
-        <v>367</v>
+        <v>180</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="6">
-        <v>180</v>
+        <v>387</v>
       </c>
       <c r="C584" s="8">
-        <v>68</v>
+        <v>369</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="6">
-        <v>68</v>
+        <v>369</v>
       </c>
       <c r="B585" s="7">
-        <v>180</v>
+        <v>387</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="6">
-        <v>387</v>
+        <v>65</v>
       </c>
       <c r="C586" s="8">
-        <v>369</v>
+        <v>178</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="6">
-        <v>369</v>
+        <v>178</v>
       </c>
       <c r="B587" s="7">
-        <v>387</v>
+        <v>65</v>
       </c>
     </row>
     <row r="588">
@@ -4799,12 +4799,12 @@
         <v>65</v>
       </c>
       <c r="C588" s="8">
-        <v>178</v>
+        <v>68</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="6">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="B589" s="7">
         <v>65</v>
@@ -4812,34 +4812,34 @@
     </row>
     <row r="590">
       <c r="A590" s="6">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="C590" s="8">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="6">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B591" s="7">
-        <v>65</v>
+        <v>178</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="6">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="C592" s="8">
-        <v>66</v>
+        <v>400</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="6">
-        <v>66</v>
+        <v>400</v>
       </c>
       <c r="B593" s="7">
-        <v>178</v>
+        <v>65</v>
       </c>
     </row>
     <row r="594">
@@ -4847,12 +4847,12 @@
         <v>65</v>
       </c>
       <c r="C594" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="6">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B595" s="7">
         <v>65</v>
@@ -4863,12 +4863,12 @@
         <v>65</v>
       </c>
       <c r="C596" s="8">
-        <v>403</v>
+        <v>329</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="6">
-        <v>403</v>
+        <v>329</v>
       </c>
       <c r="B597" s="7">
         <v>65</v>
@@ -4876,23 +4876,23 @@
     </row>
     <row r="598">
       <c r="A598" s="6">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="C598" s="8">
-        <v>329</v>
+        <v>290</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="6">
-        <v>329</v>
+        <v>290</v>
       </c>
       <c r="B599" s="7">
-        <v>65</v>
+        <v>260</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="6">
-        <v>260</v>
+        <v>128</v>
       </c>
       <c r="C600" s="8">
         <v>290</v>
@@ -4903,44 +4903,44 @@
         <v>290</v>
       </c>
       <c r="B601" s="7">
-        <v>260</v>
+        <v>128</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="6">
-        <v>128</v>
+        <v>195</v>
       </c>
       <c r="C602" s="8">
-        <v>290</v>
+        <v>404</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="6">
-        <v>290</v>
+        <v>404</v>
       </c>
       <c r="B603" s="7">
-        <v>128</v>
+        <v>195</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="6">
-        <v>195</v>
+        <v>302</v>
       </c>
       <c r="C604" s="8">
-        <v>404</v>
+        <v>145</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="6">
-        <v>404</v>
+        <v>145</v>
       </c>
       <c r="B605" s="7">
-        <v>195</v>
+        <v>302</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="6">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="C606" s="8">
         <v>145</v>
@@ -4951,12 +4951,12 @@
         <v>145</v>
       </c>
       <c r="B607" s="7">
-        <v>302</v>
+        <v>405</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="6">
-        <v>405</v>
+        <v>207</v>
       </c>
       <c r="C608" s="8">
         <v>145</v>
@@ -4967,23 +4967,23 @@
         <v>145</v>
       </c>
       <c r="B609" s="7">
-        <v>405</v>
+        <v>207</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="6">
-        <v>207</v>
+        <v>410</v>
       </c>
       <c r="C610" s="8">
-        <v>145</v>
+        <v>306</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="6">
-        <v>145</v>
+        <v>306</v>
       </c>
       <c r="B611" s="7">
-        <v>207</v>
+        <v>410</v>
       </c>
     </row>
     <row r="612">
@@ -4991,12 +4991,12 @@
         <v>410</v>
       </c>
       <c r="C612" s="8">
-        <v>306</v>
+        <v>128</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="6">
-        <v>306</v>
+        <v>128</v>
       </c>
       <c r="B613" s="7">
         <v>410</v>
@@ -5004,23 +5004,23 @@
     </row>
     <row r="614">
       <c r="A614" s="6">
-        <v>410</v>
+        <v>337</v>
       </c>
       <c r="C614" s="8">
-        <v>128</v>
+        <v>290</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="6">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="B615" s="7">
-        <v>410</v>
+        <v>337</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="6">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C616" s="8">
         <v>290</v>
@@ -5031,12 +5031,12 @@
         <v>290</v>
       </c>
       <c r="B617" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="6">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C618" s="8">
         <v>290</v>
@@ -5047,12 +5047,12 @@
         <v>290</v>
       </c>
       <c r="B619" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="6">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="C620" s="8">
         <v>290</v>
@@ -5063,12 +5063,12 @@
         <v>290</v>
       </c>
       <c r="B621" s="7">
-        <v>340</v>
+        <v>357</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="6">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C622" s="8">
         <v>290</v>
@@ -5079,12 +5079,12 @@
         <v>290</v>
       </c>
       <c r="B623" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="6">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C624" s="8">
         <v>290</v>
@@ -5095,28 +5095,28 @@
         <v>290</v>
       </c>
       <c r="B625" s="7">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="6">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C626" s="8">
-        <v>290</v>
+        <v>415</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="6">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="B627" s="7">
-        <v>379</v>
+        <v>393</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="6">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="C628" s="8">
         <v>415</v>
@@ -5127,12 +5127,12 @@
         <v>415</v>
       </c>
       <c r="B629" s="7">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="6">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C630" s="8">
         <v>415</v>
@@ -5143,12 +5143,12 @@
         <v>415</v>
       </c>
       <c r="B631" s="7">
-        <v>406</v>
+        <v>416</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="6">
-        <v>416</v>
+        <v>218</v>
       </c>
       <c r="C632" s="8">
         <v>415</v>
@@ -5159,7 +5159,7 @@
         <v>415</v>
       </c>
       <c r="B633" s="7">
-        <v>416</v>
+        <v>218</v>
       </c>
     </row>
     <row r="634">
@@ -5167,12 +5167,12 @@
         <v>218</v>
       </c>
       <c r="C634" s="8">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="6">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B635" s="7">
         <v>218</v>
@@ -5180,23 +5180,23 @@
     </row>
     <row r="636">
       <c r="A636" s="6">
-        <v>218</v>
+        <v>421</v>
       </c>
       <c r="C636" s="8">
-        <v>419</v>
+        <v>306</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="6">
-        <v>419</v>
+        <v>306</v>
       </c>
       <c r="B637" s="7">
-        <v>218</v>
+        <v>421</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="6">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C638" s="8">
         <v>306</v>
@@ -5207,12 +5207,12 @@
         <v>306</v>
       </c>
       <c r="B639" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="6">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C640" s="8">
         <v>306</v>
@@ -5223,12 +5223,12 @@
         <v>306</v>
       </c>
       <c r="B641" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="6">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C642" s="8">
         <v>306</v>
@@ -5239,7 +5239,7 @@
         <v>306</v>
       </c>
       <c r="B643" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="644">
@@ -5247,12 +5247,12 @@
         <v>424</v>
       </c>
       <c r="C644" s="8">
-        <v>306</v>
+        <v>425</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" s="6">
-        <v>306</v>
+        <v>425</v>
       </c>
       <c r="B645" s="7">
         <v>424</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="646">
       <c r="A646" s="6">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C646" s="8">
         <v>425</v>
@@ -5271,12 +5271,12 @@
         <v>425</v>
       </c>
       <c r="B647" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="6">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C648" s="8">
         <v>425</v>
@@ -5287,7 +5287,7 @@
         <v>425</v>
       </c>
       <c r="B649" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="650">
@@ -5295,12 +5295,12 @@
         <v>426</v>
       </c>
       <c r="C650" s="8">
-        <v>425</v>
+        <v>306</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="6">
-        <v>425</v>
+        <v>306</v>
       </c>
       <c r="B651" s="7">
         <v>426</v>
@@ -5311,12 +5311,12 @@
         <v>426</v>
       </c>
       <c r="C652" s="8">
-        <v>306</v>
+        <v>422</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="6">
-        <v>306</v>
+        <v>422</v>
       </c>
       <c r="B653" s="7">
         <v>426</v>
@@ -5324,18 +5324,18 @@
     </row>
     <row r="654">
       <c r="A654" s="6">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C654" s="8">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="6">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B655" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="656">
@@ -5343,12 +5343,12 @@
         <v>427</v>
       </c>
       <c r="C656" s="8">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="6">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B657" s="7">
         <v>427</v>
@@ -5356,18 +5356,18 @@
     </row>
     <row r="658">
       <c r="A658" s="6">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C658" s="8">
-        <v>422</v>
+        <v>224</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="6">
-        <v>422</v>
+        <v>224</v>
       </c>
       <c r="B659" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="660">
@@ -5375,12 +5375,12 @@
         <v>429</v>
       </c>
       <c r="C660" s="8">
-        <v>224</v>
+        <v>17</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="6">
-        <v>224</v>
+        <v>17</v>
       </c>
       <c r="B661" s="7">
         <v>429</v>
@@ -5388,34 +5388,34 @@
     </row>
     <row r="662">
       <c r="A662" s="6">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C662" s="8">
-        <v>17</v>
+        <v>135</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" s="6">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="B663" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" s="6">
-        <v>430</v>
+        <v>63</v>
       </c>
       <c r="C664" s="8">
-        <v>135</v>
+        <v>437</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="6">
-        <v>135</v>
+        <v>437</v>
       </c>
       <c r="B665" s="7">
-        <v>430</v>
+        <v>63</v>
       </c>
     </row>
     <row r="666">
@@ -5423,12 +5423,12 @@
         <v>63</v>
       </c>
       <c r="C666" s="8">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" s="6">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B667" s="7">
         <v>63</v>
@@ -5439,12 +5439,12 @@
         <v>63</v>
       </c>
       <c r="C668" s="8">
-        <v>438</v>
+        <v>62</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" s="6">
-        <v>438</v>
+        <v>62</v>
       </c>
       <c r="B669" s="7">
         <v>63</v>
@@ -5452,34 +5452,34 @@
     </row>
     <row r="670">
       <c r="A670" s="6">
-        <v>63</v>
+        <v>425</v>
       </c>
       <c r="C670" s="8">
-        <v>62</v>
+        <v>306</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="6">
-        <v>62</v>
+        <v>306</v>
       </c>
       <c r="B671" s="7">
-        <v>63</v>
+        <v>425</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="6">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="C672" s="8">
-        <v>306</v>
+        <v>392</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" s="6">
-        <v>306</v>
+        <v>392</v>
       </c>
       <c r="B673" s="7">
-        <v>425</v>
+        <v>444</v>
       </c>
     </row>
     <row r="674">
@@ -5487,12 +5487,12 @@
         <v>444</v>
       </c>
       <c r="C674" s="8">
-        <v>392</v>
+        <v>64</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" s="6">
-        <v>392</v>
+        <v>64</v>
       </c>
       <c r="B675" s="7">
         <v>444</v>
@@ -5500,18 +5500,18 @@
     </row>
     <row r="676">
       <c r="A676" s="6">
-        <v>444</v>
+        <v>59</v>
       </c>
       <c r="C676" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B677" s="7">
-        <v>444</v>
+        <v>59</v>
       </c>
     </row>
     <row r="678">
@@ -5519,12 +5519,12 @@
         <v>59</v>
       </c>
       <c r="C678" s="8">
-        <v>65</v>
+        <v>400</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" s="6">
-        <v>65</v>
+        <v>400</v>
       </c>
       <c r="B679" s="7">
         <v>59</v>
@@ -5532,66 +5532,66 @@
     </row>
     <row r="680">
       <c r="A680" s="6">
-        <v>59</v>
+        <v>450</v>
       </c>
       <c r="C680" s="8">
-        <v>400</v>
+        <v>69</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" s="6">
-        <v>400</v>
+        <v>69</v>
       </c>
       <c r="B681" s="7">
-        <v>59</v>
+        <v>450</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="6">
-        <v>450</v>
+        <v>388</v>
       </c>
       <c r="C682" s="8">
-        <v>69</v>
+        <v>363</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" s="6">
-        <v>69</v>
+        <v>363</v>
       </c>
       <c r="B683" s="7">
-        <v>450</v>
+        <v>388</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="6">
-        <v>388</v>
+        <v>201</v>
       </c>
       <c r="C684" s="8">
-        <v>363</v>
+        <v>65</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" s="6">
-        <v>363</v>
+        <v>65</v>
       </c>
       <c r="B685" s="7">
-        <v>388</v>
+        <v>201</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="6">
-        <v>201</v>
+        <v>96</v>
       </c>
       <c r="C686" s="8">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="6">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="B687" s="7">
-        <v>201</v>
+        <v>96</v>
       </c>
     </row>
     <row r="688">
@@ -5599,12 +5599,12 @@
         <v>96</v>
       </c>
       <c r="C688" s="8">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="6">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="B689" s="7">
         <v>96</v>
@@ -5615,12 +5615,12 @@
         <v>96</v>
       </c>
       <c r="C690" s="8">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" s="6">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B691" s="7">
         <v>96</v>
@@ -5628,34 +5628,34 @@
     </row>
     <row r="692">
       <c r="A692" s="6">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C692" s="8">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" s="6">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="B693" s="7">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" s="6">
-        <v>95</v>
+        <v>457</v>
       </c>
       <c r="C694" s="8">
-        <v>1</v>
+        <v>355</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" s="6">
-        <v>1</v>
+        <v>355</v>
       </c>
       <c r="B695" s="7">
-        <v>95</v>
+        <v>457</v>
       </c>
     </row>
     <row r="696">
@@ -5663,12 +5663,12 @@
         <v>457</v>
       </c>
       <c r="C696" s="8">
-        <v>355</v>
+        <v>209</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" s="6">
-        <v>355</v>
+        <v>209</v>
       </c>
       <c r="B697" s="7">
         <v>457</v>
@@ -5676,18 +5676,18 @@
     </row>
     <row r="698">
       <c r="A698" s="6">
-        <v>457</v>
+        <v>394</v>
       </c>
       <c r="C698" s="8">
-        <v>209</v>
+        <v>63</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" s="6">
-        <v>209</v>
+        <v>63</v>
       </c>
       <c r="B699" s="7">
-        <v>457</v>
+        <v>394</v>
       </c>
     </row>
     <row r="700">
@@ -5695,12 +5695,12 @@
         <v>394</v>
       </c>
       <c r="C700" s="8">
-        <v>63</v>
+        <v>438</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" s="6">
-        <v>63</v>
+        <v>438</v>
       </c>
       <c r="B701" s="7">
         <v>394</v>
@@ -5711,12 +5711,12 @@
         <v>394</v>
       </c>
       <c r="C702" s="8">
-        <v>438</v>
+        <v>458</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" s="6">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="B703" s="7">
         <v>394</v>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="704">
       <c r="A704" s="6">
-        <v>394</v>
+        <v>286</v>
       </c>
       <c r="C704" s="8">
         <v>458</v>
@@ -5735,71 +5735,519 @@
         <v>458</v>
       </c>
       <c r="B705" s="7">
-        <v>394</v>
+        <v>286</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" s="6">
-        <v>286</v>
+        <v>466</v>
       </c>
       <c r="C706" s="8">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="6">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B707" s="7">
-        <v>286</v>
+        <v>466</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" s="6">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C708" s="8">
-        <v>467</v>
+        <v>55</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" s="6">
+        <v>55</v>
+      </c>
+      <c r="B709" s="7">
         <v>467</v>
-      </c>
-      <c r="B709" s="7">
-        <v>466</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" s="6">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C710" s="8">
-        <v>55</v>
+        <v>178</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" s="6">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="B711" s="7">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" s="6">
-        <v>466</v>
+        <v>140</v>
       </c>
       <c r="C712" s="8">
-        <v>178</v>
+        <v>79</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" s="6">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="B713" s="7">
-        <v>466</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="6">
+        <v>140</v>
+      </c>
+      <c r="C714" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="6">
+        <v>59</v>
+      </c>
+      <c r="B715" s="7">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="6">
+        <v>140</v>
+      </c>
+      <c r="C716" s="8">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="6">
+        <v>334</v>
+      </c>
+      <c r="B717" s="7">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="6">
+        <v>232</v>
+      </c>
+      <c r="C718" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="6">
+        <v>59</v>
+      </c>
+      <c r="B719" s="7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="6">
+        <v>232</v>
+      </c>
+      <c r="C720" s="8">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="6">
+        <v>352</v>
+      </c>
+      <c r="B721" s="7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="6">
+        <v>232</v>
+      </c>
+      <c r="C722" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="6">
+        <v>64</v>
+      </c>
+      <c r="B723" s="7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="6">
+        <v>232</v>
+      </c>
+      <c r="C724" s="8">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="6">
+        <v>313</v>
+      </c>
+      <c r="B725" s="7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="6">
+        <v>232</v>
+      </c>
+      <c r="C726" s="8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="6">
+        <v>90</v>
+      </c>
+      <c r="B727" s="7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="6">
+        <v>232</v>
+      </c>
+      <c r="C728" s="8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="6">
+        <v>145</v>
+      </c>
+      <c r="B729" s="7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="6">
+        <v>232</v>
+      </c>
+      <c r="C730" s="8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="6">
+        <v>57</v>
+      </c>
+      <c r="B731" s="7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="6">
+        <v>472</v>
+      </c>
+      <c r="C732" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="6">
+        <v>79</v>
+      </c>
+      <c r="B733" s="7">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="6">
+        <v>472</v>
+      </c>
+      <c r="C734" s="8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="6">
+        <v>117</v>
+      </c>
+      <c r="B735" s="7">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="6">
+        <v>231</v>
+      </c>
+      <c r="C736" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="6">
+        <v>2</v>
+      </c>
+      <c r="B737" s="7">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="6">
+        <v>231</v>
+      </c>
+      <c r="C738" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="6">
+        <v>64</v>
+      </c>
+      <c r="B739" s="7">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="6">
+        <v>231</v>
+      </c>
+      <c r="C740" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="6">
+        <v>59</v>
+      </c>
+      <c r="B741" s="7">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="6">
+        <v>231</v>
+      </c>
+      <c r="C742" s="8">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="6">
+        <v>126</v>
+      </c>
+      <c r="B743" s="7">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="6">
+        <v>231</v>
+      </c>
+      <c r="C744" s="8">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="6">
+        <v>127</v>
+      </c>
+      <c r="B745" s="7">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="6">
+        <v>231</v>
+      </c>
+      <c r="C746" s="8">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="6">
+        <v>313</v>
+      </c>
+      <c r="B747" s="7">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="6">
+        <v>231</v>
+      </c>
+      <c r="C748" s="8">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="6">
+        <v>135</v>
+      </c>
+      <c r="B749" s="7">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="6">
+        <v>221</v>
+      </c>
+      <c r="C750" s="8">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="6">
+        <v>473</v>
+      </c>
+      <c r="B751" s="7">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="6">
+        <v>473</v>
+      </c>
+      <c r="C752" s="8">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="6">
+        <v>474</v>
+      </c>
+      <c r="B753" s="7">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="6">
+        <v>60</v>
+      </c>
+      <c r="C754" s="8">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="6">
+        <v>119</v>
+      </c>
+      <c r="B755" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="6">
+        <v>60</v>
+      </c>
+      <c r="C756" s="8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="6">
+        <v>90</v>
+      </c>
+      <c r="B757" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="6">
+        <v>60</v>
+      </c>
+      <c r="C758" s="8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="6">
+        <v>117</v>
+      </c>
+      <c r="B759" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="6">
+        <v>60</v>
+      </c>
+      <c r="C760" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="6">
+        <v>59</v>
+      </c>
+      <c r="B761" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="6">
+        <v>90</v>
+      </c>
+      <c r="C762" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="6">
+        <v>79</v>
+      </c>
+      <c r="B763" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="6">
+        <v>90</v>
+      </c>
+      <c r="C764" s="8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="6">
+        <v>145</v>
+      </c>
+      <c r="B765" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="6">
+        <v>90</v>
+      </c>
+      <c r="C766" s="8">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="6">
+        <v>389</v>
+      </c>
+      <c r="B767" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="6">
+        <v>90</v>
+      </c>
+      <c r="C768" s="8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="6">
+        <v>57</v>
+      </c>
+      <c r="B769" s="7">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Concepthierarchy.xlsx
+++ b/raw/Concepthierarchy.xlsx
@@ -124,7 +124,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="8">
         <v>2</v>
@@ -135,311 +135,311 @@
         <v>2</v>
       </c>
       <c r="B5" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C6" s="8">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B7" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C8" s="8">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B9" s="7">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C10" s="8">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="B11" s="7">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C12" s="8">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B13" s="7">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C14" s="8">
-        <v>14</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B15" s="7">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C16" s="8">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B17" s="7">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C18" s="8">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="B19" s="7">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C20" s="8">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B21" s="7">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C22" s="8">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B23" s="7">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C24" s="8">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B25" s="7">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C26" s="8">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B27" s="7">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C28" s="8">
-        <v>58</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="B29" s="7">
-        <v>49</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C30" s="8">
-        <v>58</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="B31" s="7">
-        <v>57</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C32" s="8">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B33" s="7">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C34" s="8">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B35" s="7">
-        <v>61</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C36" s="8">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B37" s="7">
-        <v>16</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C38" s="8">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="B39" s="7">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C40" s="8">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="B41" s="7">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C42" s="8">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="B43" s="7">
-        <v>12</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44">
@@ -447,12 +447,12 @@
         <v>64</v>
       </c>
       <c r="C44" s="8">
-        <v>2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="B45" s="7">
         <v>64</v>
@@ -460,7 +460,7 @@
     </row>
     <row r="46">
       <c r="A46" s="6">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C46" s="8">
         <v>66</v>
@@ -471,615 +471,615 @@
         <v>66</v>
       </c>
       <c r="B47" s="7">
-        <v>2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C48" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B49" s="7">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6">
-        <v>64</v>
-      </c>
-      <c r="C50" s="8">
-        <v>65</v>
+        <v>70</v>
+      </c>
+      <c r="B50" s="7">
+        <v>69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6">
-        <v>65</v>
-      </c>
-      <c r="B51" s="7">
-        <v>64</v>
+        <v>69</v>
+      </c>
+      <c r="C51" s="8">
+        <v>70</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C52" s="8">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B53" s="7">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C54" s="8">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B55" s="7">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C56" s="8">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B57" s="7">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6">
-        <v>70</v>
-      </c>
-      <c r="B58" s="7">
-        <v>69</v>
+        <v>75</v>
+      </c>
+      <c r="C58" s="8">
+        <v>71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6">
-        <v>69</v>
-      </c>
-      <c r="C59" s="8">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="B59" s="7">
+        <v>75</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C60" s="8">
-        <v>69</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="B61" s="7">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C62" s="8">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B63" s="7">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C64" s="8">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B65" s="7">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C66" s="8">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B67" s="7">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C68" s="8">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B69" s="7">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="C70" s="8">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="B71" s="7">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C72" s="8">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B73" s="7">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C74" s="8">
-        <v>57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="B75" s="7">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="C76" s="8">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="B77" s="7">
-        <v>74</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C78" s="8">
-        <v>50</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B79" s="7">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C80" s="8">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B81" s="7">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C82" s="8">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="B83" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C84" s="8">
-        <v>98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B85" s="7">
-        <v>35</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C86" s="8">
-        <v>68</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="B87" s="7">
-        <v>35</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C88" s="8">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B89" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C90" s="8">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B91" s="7">
-        <v>48</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C92" s="8">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B93" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C94" s="8">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B95" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C96" s="8">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="B97" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C98" s="8">
-        <v>59</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="B99" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="C100" s="8">
-        <v>70</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="B101" s="7">
-        <v>98</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="C102" s="8">
-        <v>69</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="B103" s="7">
-        <v>101</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="C104" s="8">
-        <v>79</v>
+        <v>62</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B105" s="7">
-        <v>101</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="C106" s="8">
-        <v>101</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="B107" s="7">
-        <v>98</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C108" s="8">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B109" s="7">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C110" s="8">
-        <v>15</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="B111" s="7">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="C112" s="8">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="B113" s="7">
-        <v>11</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="C114" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B115" s="7">
-        <v>11</v>
+        <v>69</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="C116" s="8">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B117" s="7">
-        <v>47</v>
+        <v>110</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="C118" s="8">
-        <v>102</v>
+        <v>59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="B119" s="7">
-        <v>47</v>
+        <v>110</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C120" s="8">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B121" s="7">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C122" s="8">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="B123" s="7">
-        <v>69</v>
+        <v>110</v>
       </c>
     </row>
     <row r="124">
@@ -1087,12 +1087,12 @@
         <v>110</v>
       </c>
       <c r="C124" s="8">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="B125" s="7">
         <v>110</v>
@@ -1103,12 +1103,12 @@
         <v>110</v>
       </c>
       <c r="C126" s="8">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B127" s="7">
         <v>110</v>
@@ -1116,167 +1116,167 @@
     </row>
     <row r="128">
       <c r="A128" s="6">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C128" s="8">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B129" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="6">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C130" s="8">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="B131" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C132" s="8">
-        <v>49</v>
+        <v>115</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="B133" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C134" s="8">
-        <v>48</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="B135" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="C136" s="8">
-        <v>114</v>
+        <v>66</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="B137" s="7">
-        <v>113</v>
+        <v>27</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="C138" s="8">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B139" s="7">
-        <v>113</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="C140" s="8">
-        <v>115</v>
+        <v>65</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="B141" s="7">
-        <v>113</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C142" s="8">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B143" s="7">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="C144" s="8">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B145" s="7">
-        <v>27</v>
+        <v>118</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="C146" s="8">
-        <v>117</v>
+        <v>90</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="B147" s="7">
-        <v>27</v>
+        <v>118</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="C148" s="8">
         <v>65</v>
@@ -1287,108 +1287,108 @@
         <v>65</v>
       </c>
       <c r="B149" s="7">
-        <v>27</v>
+        <v>120</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C150" s="8">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B151" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C152" s="8">
-        <v>59</v>
+        <v>120</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="B153" s="7">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="6">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C154" s="8">
-        <v>90</v>
+        <v>58</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="B155" s="7">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="6">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C156" s="8">
-        <v>65</v>
+        <v>99</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="B157" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="6">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C158" s="8">
-        <v>120</v>
+        <v>106</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="B159" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C160" s="8">
-        <v>120</v>
+        <v>49</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="B161" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C162" s="8">
         <v>58</v>
@@ -1399,7 +1399,7 @@
         <v>58</v>
       </c>
       <c r="B163" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="164">
@@ -1407,12 +1407,12 @@
         <v>123</v>
       </c>
       <c r="C164" s="8">
-        <v>99</v>
+        <v>125</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="B165" s="7">
         <v>123</v>
@@ -1420,183 +1420,183 @@
     </row>
     <row r="166">
       <c r="A166" s="6">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C166" s="8">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6">
+        <v>128</v>
+      </c>
+      <c r="B167" s="7">
         <v>106</v>
-      </c>
-      <c r="B167" s="7">
-        <v>123</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="6">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C168" s="8">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="B169" s="7">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="6">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C170" s="8">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="6">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B171" s="7">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="6">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C172" s="8">
-        <v>125</v>
+        <v>48</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="B173" s="7">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="6">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C174" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B175" s="7">
-        <v>106</v>
+        <v>132</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="6">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C176" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B177" s="7">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C178" s="8">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B179" s="7">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C180" s="8">
-        <v>48</v>
+        <v>135</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="B181" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="6">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C182" s="8">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B183" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="6">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C184" s="8">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B185" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="6">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C186" s="8">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B187" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="6">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C188" s="8">
         <v>135</v>
@@ -1607,71 +1607,71 @@
         <v>135</v>
       </c>
       <c r="B189" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C190" s="8">
-        <v>136</v>
+        <v>79</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="B191" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C192" s="8">
-        <v>19</v>
+        <v>125</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="B193" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C194" s="8">
-        <v>47</v>
+        <v>131</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="B195" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C196" s="8">
-        <v>135</v>
+        <v>106</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6">
+        <v>106</v>
+      </c>
+      <c r="B197" s="7">
         <v>135</v>
-      </c>
-      <c r="B197" s="7">
-        <v>133</v>
       </c>
     </row>
     <row r="198">
@@ -1679,12 +1679,12 @@
         <v>135</v>
       </c>
       <c r="C198" s="8">
-        <v>79</v>
+        <v>48</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="B199" s="7">
         <v>135</v>
@@ -1692,66 +1692,66 @@
     </row>
     <row r="200">
       <c r="A200" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C200" s="8">
-        <v>125</v>
+        <v>79</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="B201" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C202" s="8">
-        <v>131</v>
+        <v>49</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="B203" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C204" s="8">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B205" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C206" s="8">
-        <v>48</v>
+        <v>138</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="B207" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="208">
@@ -1759,12 +1759,12 @@
         <v>136</v>
       </c>
       <c r="C208" s="8">
-        <v>79</v>
+        <v>137</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="B209" s="7">
         <v>136</v>
@@ -1772,178 +1772,178 @@
     </row>
     <row r="210">
       <c r="A210" s="6">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C210" s="8">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B211" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="6">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C212" s="8">
-        <v>113</v>
+        <v>135</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B213" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="6">
+        <v>139</v>
+      </c>
+      <c r="C214" s="8">
         <v>136</v>
-      </c>
-      <c r="C214" s="8">
-        <v>138</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B215" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="6">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C216" s="8">
-        <v>137</v>
+        <v>59</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="B217" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="6">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C218" s="8">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="B219" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="6">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C220" s="8">
-        <v>135</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6">
-        <v>135</v>
+        <v>10</v>
       </c>
       <c r="B221" s="7">
-        <v>139</v>
+        <v>43</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="6">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C222" s="8">
-        <v>136</v>
+        <v>19</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="B223" s="7">
-        <v>139</v>
+        <v>43</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="6">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C224" s="8">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B225" s="7">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="6">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C226" s="8">
-        <v>66</v>
+        <v>145</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6">
-        <v>66</v>
+        <v>145</v>
       </c>
       <c r="B227" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="6">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="C228" s="8">
-        <v>10</v>
+        <v>144</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="B229" s="7">
-        <v>43</v>
+        <v>143</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="6">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="C230" s="8">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="B231" s="7">
-        <v>43</v>
+        <v>143</v>
       </c>
     </row>
     <row r="232">
@@ -1951,12 +1951,12 @@
         <v>143</v>
       </c>
       <c r="C232" s="8">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B233" s="7">
         <v>143</v>
@@ -1964,103 +1964,103 @@
     </row>
     <row r="234">
       <c r="A234" s="6">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C234" s="8">
-        <v>145</v>
+        <v>112</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="B235" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="6">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C236" s="8">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B237" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="6">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C238" s="8">
-        <v>106</v>
+        <v>132</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="B239" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="6">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C240" s="8">
-        <v>49</v>
+        <v>146</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="B241" s="7">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="6">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C242" s="8">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B243" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="6">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C244" s="8">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B245" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="6">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C246" s="8">
         <v>132</v>
@@ -2071,7 +2071,7 @@
         <v>132</v>
       </c>
       <c r="B247" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="248">
@@ -2079,12 +2079,12 @@
         <v>148</v>
       </c>
       <c r="C248" s="8">
-        <v>146</v>
+        <v>130</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="6">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B249" s="7">
         <v>148</v>
@@ -2092,23 +2092,23 @@
     </row>
     <row r="250">
       <c r="A250" s="6">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C250" s="8">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B251" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="6">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C252" s="8">
         <v>125</v>
@@ -2119,172 +2119,172 @@
         <v>125</v>
       </c>
       <c r="B253" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="6">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C254" s="8">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B255" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="6">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C256" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B257" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="6">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C258" s="8">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B259" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="6">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C260" s="8">
-        <v>125</v>
+        <v>106</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B261" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="6">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C262" s="8">
-        <v>130</v>
+        <v>47</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="B263" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="6">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C264" s="8">
-        <v>132</v>
+        <v>59</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="B265" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="6">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C266" s="8">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B267" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="6">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C268" s="8">
-        <v>106</v>
+        <v>50</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="B269" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="6">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C270" s="8">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="6">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B271" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="6">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C272" s="8">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="6">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B273" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="6">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C274" s="8">
         <v>57</v>
@@ -2295,460 +2295,460 @@
         <v>57</v>
       </c>
       <c r="B275" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="6">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C276" s="8">
-        <v>50</v>
+        <v>135</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="6">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="B277" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="6">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C278" s="8">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="6">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="B279" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="6">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C280" s="8">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="6">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B281" s="7">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="6">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C282" s="8">
-        <v>57</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="6">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="B283" s="7">
-        <v>155</v>
+        <v>179</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="6">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C284" s="8">
-        <v>135</v>
+        <v>178</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="B285" s="7">
-        <v>155</v>
+        <v>179</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="6">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C286" s="8">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B287" s="7">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="6">
-        <v>165</v>
-      </c>
-      <c r="B288" s="7">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C288" s="8">
+        <v>179</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6">
-        <v>1</v>
-      </c>
-      <c r="C289" s="8">
-        <v>165</v>
+        <v>179</v>
+      </c>
+      <c r="B289" s="7">
+        <v>180</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C290" s="8">
-        <v>79</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="B291" s="7">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6">
+        <v>181</v>
+      </c>
+      <c r="C292" s="8">
         <v>179</v>
-      </c>
-      <c r="C292" s="8">
-        <v>2</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="B293" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="6">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C294" s="8">
-        <v>178</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6">
-        <v>178</v>
+        <v>3</v>
       </c>
       <c r="B295" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="6">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C296" s="8">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="B297" s="7">
-        <v>179</v>
+        <v>199</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="6">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C298" s="8">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B299" s="7">
-        <v>180</v>
+        <v>199</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="6">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C300" s="8">
-        <v>3</v>
+        <v>202</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="6">
-        <v>3</v>
+        <v>202</v>
       </c>
       <c r="B301" s="7">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="6">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C302" s="8">
-        <v>179</v>
+        <v>64</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="6">
-        <v>179</v>
+        <v>64</v>
       </c>
       <c r="B303" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="6">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C304" s="8">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="6">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="B305" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="6">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C306" s="8">
-        <v>1</v>
+        <v>104</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="6">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="B307" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="6">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C308" s="8">
-        <v>177</v>
+        <v>145</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="6">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="B309" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="6">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C310" s="8">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="6">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B311" s="7">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="6">
-        <v>182</v>
+        <v>73</v>
       </c>
       <c r="C312" s="8">
-        <v>64</v>
+        <v>157</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="6">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="B313" s="7">
-        <v>182</v>
+        <v>73</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="6">
-        <v>182</v>
+        <v>73</v>
       </c>
       <c r="C314" s="8">
-        <v>65</v>
+        <v>173</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="6">
-        <v>65</v>
+        <v>173</v>
       </c>
       <c r="B315" s="7">
-        <v>182</v>
+        <v>73</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="6">
-        <v>204</v>
+        <v>73</v>
       </c>
       <c r="C316" s="8">
-        <v>104</v>
+        <v>211</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="6">
-        <v>104</v>
+        <v>211</v>
       </c>
       <c r="B317" s="7">
-        <v>204</v>
+        <v>73</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="6">
-        <v>205</v>
+        <v>88</v>
       </c>
       <c r="C318" s="8">
-        <v>145</v>
+        <v>34</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="6">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="B319" s="7">
-        <v>205</v>
+        <v>88</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="6">
-        <v>195</v>
+        <v>88</v>
       </c>
       <c r="C320" s="8">
-        <v>199</v>
+        <v>47</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="6">
-        <v>199</v>
+        <v>47</v>
       </c>
       <c r="B321" s="7">
-        <v>195</v>
+        <v>88</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="6">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="C322" s="8">
-        <v>157</v>
+        <v>227</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="6">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="B323" s="7">
-        <v>73</v>
+        <v>226</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="6">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="C324" s="8">
-        <v>173</v>
+        <v>47</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="6">
-        <v>173</v>
+        <v>47</v>
       </c>
       <c r="B325" s="7">
-        <v>73</v>
+        <v>227</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="6">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="C326" s="8">
-        <v>211</v>
+        <v>64</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="6">
-        <v>211</v>
+        <v>64</v>
       </c>
       <c r="B327" s="7">
-        <v>73</v>
+        <v>227</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="6">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C328" s="8">
-        <v>34</v>
+        <v>66</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="6">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="B329" s="7">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="6">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="C330" s="8">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="6">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B331" s="7">
-        <v>88</v>
+        <v>20</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="6">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="C332" s="8">
         <v>227</v>
@@ -2759,44 +2759,44 @@
         <v>227</v>
       </c>
       <c r="B333" s="7">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="6">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C334" s="8">
-        <v>47</v>
+        <v>95</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="6">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="B335" s="7">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="6">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C336" s="8">
-        <v>64</v>
+        <v>96</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="6">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="B337" s="7">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="6">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="C338" s="8">
         <v>66</v>
@@ -2807,263 +2807,263 @@
         <v>66</v>
       </c>
       <c r="B339" s="7">
-        <v>50</v>
+        <v>144</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="6">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="C340" s="8">
-        <v>68</v>
+        <v>98</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="6">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="B341" s="7">
-        <v>20</v>
+        <v>241</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="6">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C342" s="8">
-        <v>227</v>
+        <v>104</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="6">
-        <v>227</v>
+        <v>104</v>
       </c>
       <c r="B343" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="6">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C344" s="8">
-        <v>95</v>
+        <v>53</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="6">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="B345" s="7">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="6">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C346" s="8">
-        <v>96</v>
+        <v>143</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="6">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="B347" s="7">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="6">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="C348" s="8">
-        <v>66</v>
+        <v>242</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="6">
-        <v>66</v>
+        <v>242</v>
       </c>
       <c r="B349" s="7">
-        <v>144</v>
+        <v>241</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="6">
-        <v>241</v>
+        <v>97</v>
       </c>
       <c r="C350" s="8">
-        <v>98</v>
+        <v>64</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="6">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="B351" s="7">
-        <v>241</v>
+        <v>97</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="6">
-        <v>241</v>
+        <v>97</v>
       </c>
       <c r="C352" s="8">
-        <v>104</v>
+        <v>65</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="6">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="B353" s="7">
-        <v>241</v>
+        <v>97</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="6">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C354" s="8">
-        <v>53</v>
+        <v>251</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="6">
-        <v>53</v>
+        <v>251</v>
       </c>
       <c r="B355" s="7">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="6">
-        <v>241</v>
+        <v>162</v>
       </c>
       <c r="C356" s="8">
-        <v>143</v>
+        <v>250</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="6">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="B357" s="7">
-        <v>241</v>
+        <v>162</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="6">
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="C358" s="8">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="6">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B359" s="7">
-        <v>241</v>
+        <v>161</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="6">
-        <v>97</v>
+        <v>252</v>
       </c>
       <c r="C360" s="8">
-        <v>64</v>
+        <v>209</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="6">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="B361" s="7">
-        <v>97</v>
+        <v>252</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="6">
-        <v>97</v>
+        <v>259</v>
       </c>
       <c r="C362" s="8">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="6">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B363" s="7">
-        <v>97</v>
+        <v>259</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="6">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C364" s="8">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="6">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B365" s="7">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="6">
-        <v>162</v>
+        <v>259</v>
       </c>
       <c r="C366" s="8">
-        <v>250</v>
+        <v>19</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="6">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="B367" s="7">
-        <v>162</v>
+        <v>259</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="6">
-        <v>161</v>
+        <v>259</v>
       </c>
       <c r="C368" s="8">
-        <v>250</v>
+        <v>82</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="6">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="B369" s="7">
-        <v>161</v>
+        <v>259</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="6">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C370" s="8">
-        <v>209</v>
+        <v>25</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="6">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="B371" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="372">
@@ -3071,12 +3071,12 @@
         <v>259</v>
       </c>
       <c r="C372" s="8">
-        <v>79</v>
+        <v>261</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="6">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="B373" s="7">
         <v>259</v>
@@ -3084,55 +3084,55 @@
     </row>
     <row r="374">
       <c r="A374" s="6">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C374" s="8">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="6">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B375" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="6">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C376" s="8">
-        <v>19</v>
+        <v>264</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="6">
-        <v>19</v>
+        <v>264</v>
       </c>
       <c r="B377" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="6">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C378" s="8">
-        <v>82</v>
+        <v>261</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="6">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="B379" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="6">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C380" s="8">
         <v>25</v>
@@ -3143,748 +3143,748 @@
         <v>25</v>
       </c>
       <c r="B381" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="6">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C382" s="8">
-        <v>261</v>
+        <v>78</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="6">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="B383" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="6">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C384" s="8">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="6">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B385" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="6">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C386" s="8">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="6">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B387" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="6">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C388" s="8">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="6">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B389" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="6">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C390" s="8">
-        <v>25</v>
+        <v>269</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="6">
-        <v>25</v>
+        <v>269</v>
       </c>
       <c r="B391" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="6">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C392" s="8">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="6">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="B393" s="7">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="6">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C394" s="8">
-        <v>266</v>
+        <v>19</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="6">
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="B395" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="6">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C396" s="8">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="6">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B397" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="6">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C398" s="8">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="6">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B399" s="7">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="6">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C400" s="8">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="6">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B401" s="7">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="6">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C402" s="8">
-        <v>25</v>
+        <v>82</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="6">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="B403" s="7">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="6">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C404" s="8">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="6">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B405" s="7">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="6">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C406" s="8">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="6">
+        <v>272</v>
+      </c>
+      <c r="B407" s="7">
         <v>263</v>
-      </c>
-      <c r="B407" s="7">
-        <v>270</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="6">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C408" s="8">
-        <v>271</v>
+        <v>179</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="6">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="B409" s="7">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="6">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C410" s="8">
-        <v>261</v>
+        <v>179</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="6">
-        <v>261</v>
+        <v>179</v>
       </c>
       <c r="B411" s="7">
-        <v>263</v>
+        <v>276</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="6">
-        <v>263</v>
-      </c>
-      <c r="C412" s="8">
-        <v>82</v>
+        <v>277</v>
+      </c>
+      <c r="B412" s="7">
+        <v>241</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="6">
-        <v>82</v>
-      </c>
-      <c r="B413" s="7">
-        <v>263</v>
+        <v>241</v>
+      </c>
+      <c r="C413" s="8">
+        <v>277</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="6">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C414" s="8">
-        <v>25</v>
+        <v>277</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="6">
-        <v>25</v>
+        <v>277</v>
       </c>
       <c r="B415" s="7">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="6">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C416" s="8">
-        <v>272</v>
+        <v>79</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="6">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="B417" s="7">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="6">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C418" s="8">
-        <v>179</v>
+        <v>278</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="6">
-        <v>179</v>
+        <v>278</v>
       </c>
       <c r="B419" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="6">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C420" s="8">
-        <v>179</v>
+        <v>79</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="6">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="B421" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="6">
-        <v>277</v>
-      </c>
-      <c r="B422" s="7">
-        <v>241</v>
+        <v>280</v>
+      </c>
+      <c r="C422" s="8">
+        <v>28</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="6">
-        <v>241</v>
-      </c>
-      <c r="C423" s="8">
-        <v>277</v>
+        <v>28</v>
+      </c>
+      <c r="B423" s="7">
+        <v>280</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="6">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C424" s="8">
-        <v>277</v>
+        <v>119</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="6">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B425" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="6">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C426" s="8">
-        <v>79</v>
+        <v>117</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="6">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="B427" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="6">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C428" s="8">
-        <v>278</v>
+        <v>57</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="6">
-        <v>278</v>
+        <v>57</v>
       </c>
       <c r="B429" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="6">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C430" s="8">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="6">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B431" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="6">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C432" s="8">
-        <v>28</v>
+        <v>145</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="6">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="B433" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="6">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C434" s="8">
-        <v>119</v>
+        <v>69</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="6">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="B435" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="6">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C436" s="8">
-        <v>117</v>
+        <v>64</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="6">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="B437" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="6">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C438" s="8">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="6">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B439" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="6">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C440" s="8">
-        <v>90</v>
+        <v>282</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="6">
-        <v>90</v>
+        <v>282</v>
       </c>
       <c r="B441" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="6">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C442" s="8">
-        <v>145</v>
+        <v>283</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="6">
-        <v>145</v>
+        <v>283</v>
       </c>
       <c r="B443" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="6">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C444" s="8">
-        <v>69</v>
+        <v>178</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="6">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="B445" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="6">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C446" s="8">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="6">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B447" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="6">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C448" s="8">
-        <v>66</v>
+        <v>179</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="6">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="B449" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="6">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C450" s="8">
-        <v>282</v>
+        <v>65</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="6">
-        <v>282</v>
+        <v>65</v>
       </c>
       <c r="B451" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="6">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C452" s="8">
-        <v>283</v>
+        <v>64</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="6">
-        <v>283</v>
+        <v>64</v>
       </c>
       <c r="B453" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="6">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C454" s="8">
-        <v>178</v>
+        <v>286</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="6">
-        <v>178</v>
+        <v>286</v>
       </c>
       <c r="B455" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="6">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C456" s="8">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="6">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B457" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="6">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C458" s="8">
-        <v>179</v>
+        <v>22</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="6">
-        <v>179</v>
+        <v>22</v>
       </c>
       <c r="B459" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="6">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C460" s="8">
-        <v>65</v>
+        <v>287</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="6">
-        <v>65</v>
+        <v>287</v>
       </c>
       <c r="B461" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="6">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C462" s="8">
-        <v>64</v>
+        <v>288</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="6">
-        <v>64</v>
+        <v>288</v>
       </c>
       <c r="B463" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="6">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C464" s="8">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="6">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B465" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="6">
-        <v>286</v>
+        <v>116</v>
       </c>
       <c r="C466" s="8">
-        <v>65</v>
+        <v>290</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="6">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="B467" s="7">
-        <v>286</v>
+        <v>116</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="6">
-        <v>286</v>
+        <v>115</v>
       </c>
       <c r="C468" s="8">
-        <v>22</v>
+        <v>290</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="6">
-        <v>22</v>
+        <v>290</v>
       </c>
       <c r="B469" s="7">
-        <v>286</v>
+        <v>115</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="6">
-        <v>286</v>
+        <v>111</v>
       </c>
       <c r="C470" s="8">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="6">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B471" s="7">
-        <v>286</v>
+        <v>111</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="6">
-        <v>286</v>
+        <v>47</v>
       </c>
       <c r="C472" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="6">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B473" s="7">
-        <v>286</v>
+        <v>47</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="6">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C474" s="8">
         <v>290</v>
@@ -3895,663 +3895,663 @@
         <v>290</v>
       </c>
       <c r="B475" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="6">
-        <v>116</v>
+        <v>297</v>
       </c>
       <c r="C476" s="8">
-        <v>290</v>
+        <v>178</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="6">
-        <v>290</v>
+        <v>178</v>
       </c>
       <c r="B477" s="7">
-        <v>116</v>
+        <v>297</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="6">
-        <v>115</v>
+        <v>303</v>
       </c>
       <c r="C478" s="8">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="6">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B479" s="7">
-        <v>115</v>
+        <v>303</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="6">
-        <v>111</v>
+        <v>311</v>
       </c>
       <c r="C480" s="8">
-        <v>290</v>
+        <v>62</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="6">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="B481" s="7">
-        <v>111</v>
+        <v>311</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="6">
-        <v>47</v>
+        <v>311</v>
       </c>
       <c r="C482" s="8">
-        <v>290</v>
+        <v>53</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="6">
-        <v>290</v>
+        <v>53</v>
       </c>
       <c r="B483" s="7">
-        <v>47</v>
+        <v>311</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="6">
-        <v>295</v>
+        <v>84</v>
       </c>
       <c r="C484" s="8">
-        <v>290</v>
+        <v>106</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="6">
-        <v>290</v>
+        <v>106</v>
       </c>
       <c r="B485" s="7">
-        <v>295</v>
+        <v>84</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="6">
-        <v>297</v>
+        <v>84</v>
       </c>
       <c r="C486" s="8">
-        <v>178</v>
+        <v>49</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="6">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="B487" s="7">
-        <v>297</v>
+        <v>84</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="6">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="C488" s="8">
-        <v>302</v>
+        <v>125</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="6">
-        <v>302</v>
+        <v>125</v>
       </c>
       <c r="B489" s="7">
-        <v>303</v>
+        <v>84</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="6">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="C490" s="8">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="6">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B491" s="7">
-        <v>311</v>
+        <v>84</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="6">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C492" s="8">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="6">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B493" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="6">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="C494" s="8">
-        <v>106</v>
+        <v>47</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="6">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B495" s="7">
-        <v>84</v>
+        <v>312</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="6">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="C496" s="8">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="6">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B497" s="7">
-        <v>84</v>
+        <v>118</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="6">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C498" s="8">
-        <v>125</v>
+        <v>70</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="6">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="B499" s="7">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="6">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C500" s="8">
-        <v>47</v>
+        <v>322</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="6">
-        <v>47</v>
+        <v>322</v>
       </c>
       <c r="B501" s="7">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="6">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="C502" s="8">
-        <v>64</v>
+        <v>163</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="6">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="B503" s="7">
-        <v>312</v>
+        <v>325</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="6">
-        <v>312</v>
+        <v>14</v>
       </c>
       <c r="C504" s="8">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="6">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B505" s="7">
-        <v>312</v>
+        <v>14</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="6">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="C506" s="8">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="6">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B507" s="7">
-        <v>118</v>
+        <v>14</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="6">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="C508" s="8">
-        <v>70</v>
+        <v>260</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="6">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="B509" s="7">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="6">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="C510" s="8">
-        <v>322</v>
+        <v>66</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="6">
-        <v>322</v>
+        <v>66</v>
       </c>
       <c r="B511" s="7">
-        <v>97</v>
+        <v>19</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="6">
-        <v>325</v>
+        <v>19</v>
       </c>
       <c r="C512" s="8">
-        <v>163</v>
+        <v>68</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="6">
-        <v>163</v>
+        <v>68</v>
       </c>
       <c r="B513" s="7">
-        <v>325</v>
+        <v>19</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C514" s="8">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="6">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="B515" s="7">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="6">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="C516" s="8">
-        <v>63</v>
+        <v>329</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="6">
-        <v>63</v>
+        <v>329</v>
       </c>
       <c r="B517" s="7">
-        <v>14</v>
+        <v>78</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C518" s="8">
-        <v>260</v>
+        <v>329</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="6">
-        <v>260</v>
+        <v>329</v>
       </c>
       <c r="B519" s="7">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="6">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="C520" s="8">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="6">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B521" s="7">
-        <v>19</v>
+        <v>223</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="6">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="C522" s="8">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="6">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B523" s="7">
-        <v>19</v>
+        <v>223</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="6">
-        <v>22</v>
+        <v>223</v>
       </c>
       <c r="C524" s="8">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="6">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B525" s="7">
-        <v>22</v>
+        <v>223</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="6">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="C526" s="8">
-        <v>329</v>
+        <v>65</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="6">
-        <v>329</v>
+        <v>65</v>
       </c>
       <c r="B527" s="7">
-        <v>78</v>
+        <v>352</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="6">
-        <v>22</v>
+        <v>352</v>
       </c>
       <c r="C528" s="8">
-        <v>329</v>
+        <v>64</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="6">
-        <v>329</v>
+        <v>64</v>
       </c>
       <c r="B529" s="7">
-        <v>22</v>
+        <v>352</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="6">
-        <v>223</v>
+        <v>354</v>
       </c>
       <c r="C530" s="8">
-        <v>59</v>
+        <v>341</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="6">
-        <v>59</v>
+        <v>341</v>
       </c>
       <c r="B531" s="7">
-        <v>223</v>
+        <v>354</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="6">
-        <v>223</v>
+        <v>354</v>
       </c>
       <c r="C532" s="8">
-        <v>79</v>
+        <v>19</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="6">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B533" s="7">
-        <v>223</v>
+        <v>354</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="6">
-        <v>223</v>
+        <v>354</v>
       </c>
       <c r="C534" s="8">
-        <v>90</v>
+        <v>355</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="6">
-        <v>90</v>
+        <v>355</v>
       </c>
       <c r="B535" s="7">
-        <v>223</v>
+        <v>354</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="6">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C536" s="8">
-        <v>65</v>
+        <v>135</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="6">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="B537" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="6">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C538" s="8">
-        <v>64</v>
+        <v>164</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="6">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="B539" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="6">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="C540" s="8">
-        <v>341</v>
+        <v>355</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="6">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B541" s="7">
-        <v>354</v>
+        <v>308</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="6">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="C542" s="8">
-        <v>19</v>
+        <v>164</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="6">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="B543" s="7">
-        <v>354</v>
+        <v>166</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="6">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="C544" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="6">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B545" s="7">
-        <v>354</v>
+        <v>166</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="6">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="C546" s="8">
-        <v>135</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="6">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="B547" s="7">
-        <v>354</v>
+        <v>166</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="6">
-        <v>354</v>
+        <v>137</v>
       </c>
       <c r="C548" s="8">
-        <v>164</v>
+        <v>79</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="6">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="B549" s="7">
-        <v>354</v>
+        <v>137</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="6">
-        <v>308</v>
+        <v>137</v>
       </c>
       <c r="C550" s="8">
-        <v>355</v>
+        <v>128</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="6">
-        <v>355</v>
+        <v>128</v>
       </c>
       <c r="B551" s="7">
-        <v>308</v>
+        <v>137</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="6">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C552" s="8">
-        <v>164</v>
+        <v>116</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="6">
-        <v>164</v>
+        <v>116</v>
       </c>
       <c r="B553" s="7">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="6">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C554" s="8">
-        <v>356</v>
+        <v>115</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="6">
-        <v>356</v>
+        <v>115</v>
       </c>
       <c r="B555" s="7">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="6">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C556" s="8">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="6">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="B557" s="7">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="558">
@@ -4559,12 +4559,12 @@
         <v>137</v>
       </c>
       <c r="C558" s="8">
-        <v>79</v>
+        <v>99</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="6">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B559" s="7">
         <v>137</v>
@@ -4575,12 +4575,12 @@
         <v>137</v>
       </c>
       <c r="C560" s="8">
-        <v>128</v>
+        <v>357</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="6">
-        <v>128</v>
+        <v>357</v>
       </c>
       <c r="B561" s="7">
         <v>137</v>
@@ -4588,194 +4588,194 @@
     </row>
     <row r="562">
       <c r="A562" s="6">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="C562" s="8">
-        <v>116</v>
+        <v>362</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="6">
-        <v>116</v>
+        <v>362</v>
       </c>
       <c r="B563" s="7">
-        <v>137</v>
+        <v>55</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="6">
-        <v>137</v>
+        <v>363</v>
       </c>
       <c r="C564" s="8">
-        <v>115</v>
+        <v>362</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="6">
-        <v>115</v>
+        <v>362</v>
       </c>
       <c r="B565" s="7">
-        <v>137</v>
+        <v>363</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="6">
-        <v>137</v>
+        <v>364</v>
       </c>
       <c r="C566" s="8">
-        <v>58</v>
+        <v>362</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="6">
-        <v>58</v>
+        <v>362</v>
       </c>
       <c r="B567" s="7">
-        <v>137</v>
+        <v>364</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="6">
-        <v>137</v>
+        <v>367</v>
       </c>
       <c r="C568" s="8">
-        <v>99</v>
+        <v>133</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="6">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="B569" s="7">
-        <v>137</v>
+        <v>367</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="6">
-        <v>137</v>
+        <v>367</v>
       </c>
       <c r="C570" s="8">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="6">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B571" s="7">
-        <v>137</v>
+        <v>367</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="6">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="C572" s="8">
-        <v>362</v>
+        <v>68</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="6">
-        <v>362</v>
+        <v>68</v>
       </c>
       <c r="B573" s="7">
-        <v>55</v>
+        <v>180</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="6">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="C574" s="8">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="6">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B575" s="7">
-        <v>363</v>
+        <v>387</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="6">
-        <v>364</v>
+        <v>65</v>
       </c>
       <c r="C576" s="8">
-        <v>362</v>
+        <v>178</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="6">
-        <v>362</v>
+        <v>178</v>
       </c>
       <c r="B577" s="7">
-        <v>364</v>
+        <v>65</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="6">
-        <v>367</v>
+        <v>65</v>
       </c>
       <c r="C578" s="8">
-        <v>133</v>
+        <v>68</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="6">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="B579" s="7">
-        <v>367</v>
+        <v>65</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="6">
-        <v>367</v>
+        <v>178</v>
       </c>
       <c r="C580" s="8">
-        <v>368</v>
+        <v>66</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="6">
-        <v>368</v>
+        <v>66</v>
       </c>
       <c r="B581" s="7">
-        <v>367</v>
+        <v>178</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="6">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="C582" s="8">
-        <v>68</v>
+        <v>400</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="6">
-        <v>68</v>
+        <v>400</v>
       </c>
       <c r="B583" s="7">
-        <v>180</v>
+        <v>65</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="6">
-        <v>387</v>
+        <v>65</v>
       </c>
       <c r="C584" s="8">
-        <v>369</v>
+        <v>403</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="6">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="B585" s="7">
-        <v>387</v>
+        <v>65</v>
       </c>
     </row>
     <row r="586">
@@ -4783,12 +4783,12 @@
         <v>65</v>
       </c>
       <c r="C586" s="8">
-        <v>178</v>
+        <v>329</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="6">
-        <v>178</v>
+        <v>329</v>
       </c>
       <c r="B587" s="7">
         <v>65</v>
@@ -4796,215 +4796,215 @@
     </row>
     <row r="588">
       <c r="A588" s="6">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="C588" s="8">
-        <v>68</v>
+        <v>290</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="6">
-        <v>68</v>
+        <v>290</v>
       </c>
       <c r="B589" s="7">
-        <v>65</v>
+        <v>260</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="6">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="C590" s="8">
-        <v>66</v>
+        <v>290</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="6">
-        <v>66</v>
+        <v>290</v>
       </c>
       <c r="B591" s="7">
-        <v>178</v>
+        <v>128</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="6">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="C592" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="6">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B593" s="7">
-        <v>65</v>
+        <v>195</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="6">
-        <v>65</v>
+        <v>302</v>
       </c>
       <c r="C594" s="8">
-        <v>403</v>
+        <v>145</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="6">
-        <v>403</v>
+        <v>145</v>
       </c>
       <c r="B595" s="7">
-        <v>65</v>
+        <v>302</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="6">
-        <v>65</v>
+        <v>405</v>
       </c>
       <c r="C596" s="8">
-        <v>329</v>
+        <v>145</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="6">
-        <v>329</v>
+        <v>145</v>
       </c>
       <c r="B597" s="7">
-        <v>65</v>
+        <v>405</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="6">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="C598" s="8">
-        <v>290</v>
+        <v>145</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="6">
-        <v>290</v>
+        <v>145</v>
       </c>
       <c r="B599" s="7">
-        <v>260</v>
+        <v>207</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="6">
-        <v>128</v>
+        <v>410</v>
       </c>
       <c r="C600" s="8">
-        <v>290</v>
+        <v>306</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="6">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B601" s="7">
-        <v>128</v>
+        <v>410</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="6">
-        <v>195</v>
+        <v>410</v>
       </c>
       <c r="C602" s="8">
-        <v>404</v>
+        <v>128</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="6">
-        <v>404</v>
+        <v>128</v>
       </c>
       <c r="B603" s="7">
-        <v>195</v>
+        <v>410</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="6">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="C604" s="8">
-        <v>145</v>
+        <v>290</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="6">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="B605" s="7">
-        <v>302</v>
+        <v>337</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="6">
-        <v>405</v>
+        <v>339</v>
       </c>
       <c r="C606" s="8">
-        <v>145</v>
+        <v>290</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="6">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="B607" s="7">
-        <v>405</v>
+        <v>339</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="6">
-        <v>207</v>
+        <v>340</v>
       </c>
       <c r="C608" s="8">
-        <v>145</v>
+        <v>290</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="6">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="B609" s="7">
-        <v>207</v>
+        <v>340</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="6">
-        <v>410</v>
+        <v>357</v>
       </c>
       <c r="C610" s="8">
-        <v>306</v>
+        <v>290</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="6">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="B611" s="7">
-        <v>410</v>
+        <v>357</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="6">
-        <v>410</v>
+        <v>358</v>
       </c>
       <c r="C612" s="8">
-        <v>128</v>
+        <v>290</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="6">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="B613" s="7">
-        <v>410</v>
+        <v>358</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="6">
-        <v>337</v>
+        <v>379</v>
       </c>
       <c r="C614" s="8">
         <v>290</v>
@@ -5015,204 +5015,204 @@
         <v>290</v>
       </c>
       <c r="B615" s="7">
-        <v>337</v>
+        <v>379</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="6">
-        <v>339</v>
+        <v>393</v>
       </c>
       <c r="C616" s="8">
-        <v>290</v>
+        <v>415</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="6">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="B617" s="7">
-        <v>339</v>
+        <v>393</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="6">
-        <v>340</v>
+        <v>406</v>
       </c>
       <c r="C618" s="8">
-        <v>290</v>
+        <v>415</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="6">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="B619" s="7">
-        <v>340</v>
+        <v>406</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="6">
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="C620" s="8">
-        <v>290</v>
+        <v>415</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="6">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="B621" s="7">
-        <v>357</v>
+        <v>416</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="6">
-        <v>358</v>
+        <v>218</v>
       </c>
       <c r="C622" s="8">
-        <v>290</v>
+        <v>415</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="6">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="B623" s="7">
-        <v>358</v>
+        <v>218</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="6">
-        <v>379</v>
+        <v>218</v>
       </c>
       <c r="C624" s="8">
-        <v>290</v>
+        <v>419</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="6">
-        <v>290</v>
+        <v>419</v>
       </c>
       <c r="B625" s="7">
-        <v>379</v>
+        <v>218</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="6">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="C626" s="8">
-        <v>415</v>
+        <v>306</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="6">
-        <v>415</v>
+        <v>306</v>
       </c>
       <c r="B627" s="7">
-        <v>393</v>
+        <v>421</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="6">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="C628" s="8">
-        <v>415</v>
+        <v>306</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="6">
-        <v>415</v>
+        <v>306</v>
       </c>
       <c r="B629" s="7">
-        <v>406</v>
+        <v>422</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="6">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C630" s="8">
-        <v>415</v>
+        <v>306</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="6">
-        <v>415</v>
+        <v>306</v>
       </c>
       <c r="B631" s="7">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="6">
-        <v>218</v>
+        <v>424</v>
       </c>
       <c r="C632" s="8">
-        <v>415</v>
+        <v>306</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="6">
-        <v>415</v>
+        <v>306</v>
       </c>
       <c r="B633" s="7">
-        <v>218</v>
+        <v>424</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="6">
-        <v>218</v>
+        <v>424</v>
       </c>
       <c r="C634" s="8">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="6">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B635" s="7">
-        <v>218</v>
+        <v>424</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="6">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C636" s="8">
-        <v>306</v>
+        <v>425</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="6">
-        <v>306</v>
+        <v>425</v>
       </c>
       <c r="B637" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="6">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C638" s="8">
-        <v>306</v>
+        <v>425</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="6">
-        <v>306</v>
+        <v>425</v>
       </c>
       <c r="B639" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="6">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C640" s="8">
         <v>306</v>
@@ -5223,615 +5223,615 @@
         <v>306</v>
       </c>
       <c r="B641" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="6">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C642" s="8">
-        <v>306</v>
+        <v>422</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="6">
-        <v>306</v>
+        <v>422</v>
       </c>
       <c r="B643" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="6">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C644" s="8">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" s="6">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B645" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" s="6">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C646" s="8">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="6">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B647" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="6">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C648" s="8">
-        <v>425</v>
+        <v>224</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" s="6">
-        <v>425</v>
+        <v>224</v>
       </c>
       <c r="B649" s="7">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="6">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C650" s="8">
-        <v>306</v>
+        <v>17</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="6">
-        <v>306</v>
+        <v>17</v>
       </c>
       <c r="B651" s="7">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="6">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C652" s="8">
-        <v>422</v>
+        <v>135</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="6">
-        <v>422</v>
+        <v>135</v>
       </c>
       <c r="B653" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="6">
-        <v>427</v>
+        <v>63</v>
       </c>
       <c r="C654" s="8">
-        <v>421</v>
+        <v>437</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="6">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="B655" s="7">
-        <v>427</v>
+        <v>63</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" s="6">
-        <v>427</v>
+        <v>63</v>
       </c>
       <c r="C656" s="8">
-        <v>422</v>
+        <v>438</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="6">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="B657" s="7">
-        <v>427</v>
+        <v>63</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="6">
-        <v>429</v>
+        <v>63</v>
       </c>
       <c r="C658" s="8">
-        <v>224</v>
+        <v>62</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="6">
-        <v>224</v>
+        <v>62</v>
       </c>
       <c r="B659" s="7">
-        <v>429</v>
+        <v>63</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="6">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C660" s="8">
-        <v>17</v>
+        <v>306</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="6">
-        <v>17</v>
+        <v>306</v>
       </c>
       <c r="B661" s="7">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" s="6">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="C662" s="8">
-        <v>135</v>
+        <v>392</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" s="6">
-        <v>135</v>
+        <v>392</v>
       </c>
       <c r="B663" s="7">
-        <v>430</v>
+        <v>444</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" s="6">
-        <v>63</v>
+        <v>444</v>
       </c>
       <c r="C664" s="8">
-        <v>437</v>
+        <v>64</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="6">
-        <v>437</v>
+        <v>64</v>
       </c>
       <c r="B665" s="7">
-        <v>63</v>
+        <v>444</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" s="6">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C666" s="8">
-        <v>438</v>
+        <v>65</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" s="6">
-        <v>438</v>
+        <v>65</v>
       </c>
       <c r="B667" s="7">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" s="6">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C668" s="8">
-        <v>62</v>
+        <v>400</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" s="6">
-        <v>62</v>
+        <v>400</v>
       </c>
       <c r="B669" s="7">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" s="6">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="C670" s="8">
-        <v>306</v>
+        <v>69</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="6">
-        <v>306</v>
+        <v>69</v>
       </c>
       <c r="B671" s="7">
-        <v>425</v>
+        <v>450</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="6">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="C672" s="8">
-        <v>392</v>
+        <v>363</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" s="6">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="B673" s="7">
-        <v>444</v>
+        <v>388</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" s="6">
-        <v>444</v>
+        <v>201</v>
       </c>
       <c r="C674" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" s="6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B675" s="7">
-        <v>444</v>
+        <v>201</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" s="6">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="C676" s="8">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="6">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="B677" s="7">
-        <v>59</v>
+        <v>96</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" s="6">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="C678" s="8">
-        <v>400</v>
+        <v>79</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" s="6">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="B679" s="7">
-        <v>59</v>
+        <v>96</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="6">
-        <v>450</v>
+        <v>96</v>
       </c>
       <c r="C680" s="8">
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" s="6">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="B681" s="7">
-        <v>450</v>
+        <v>96</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="6">
-        <v>388</v>
+        <v>95</v>
       </c>
       <c r="C682" s="8">
-        <v>363</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" s="6">
-        <v>363</v>
+        <v>1</v>
       </c>
       <c r="B683" s="7">
-        <v>388</v>
+        <v>95</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="6">
-        <v>201</v>
+        <v>457</v>
       </c>
       <c r="C684" s="8">
-        <v>65</v>
+        <v>355</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" s="6">
-        <v>65</v>
+        <v>355</v>
       </c>
       <c r="B685" s="7">
-        <v>201</v>
+        <v>457</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="6">
-        <v>96</v>
+        <v>457</v>
       </c>
       <c r="C686" s="8">
-        <v>1</v>
+        <v>209</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="6">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="B687" s="7">
-        <v>96</v>
+        <v>457</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" s="6">
-        <v>96</v>
+        <v>394</v>
       </c>
       <c r="C688" s="8">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="6">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B689" s="7">
-        <v>96</v>
+        <v>394</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" s="6">
-        <v>96</v>
+        <v>394</v>
       </c>
       <c r="C690" s="8">
-        <v>90</v>
+        <v>438</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" s="6">
-        <v>90</v>
+        <v>438</v>
       </c>
       <c r="B691" s="7">
-        <v>96</v>
+        <v>394</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="6">
-        <v>95</v>
+        <v>394</v>
       </c>
       <c r="C692" s="8">
-        <v>1</v>
+        <v>458</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" s="6">
-        <v>1</v>
+        <v>458</v>
       </c>
       <c r="B693" s="7">
-        <v>95</v>
+        <v>394</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" s="6">
-        <v>457</v>
+        <v>286</v>
       </c>
       <c r="C694" s="8">
-        <v>355</v>
+        <v>458</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" s="6">
-        <v>355</v>
+        <v>458</v>
       </c>
       <c r="B695" s="7">
-        <v>457</v>
+        <v>286</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" s="6">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="C696" s="8">
-        <v>209</v>
+        <v>467</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" s="6">
-        <v>209</v>
+        <v>467</v>
       </c>
       <c r="B697" s="7">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" s="6">
-        <v>394</v>
+        <v>467</v>
       </c>
       <c r="C698" s="8">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" s="6">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B699" s="7">
-        <v>394</v>
+        <v>467</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" s="6">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="C700" s="8">
-        <v>438</v>
+        <v>178</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" s="6">
-        <v>438</v>
+        <v>178</v>
       </c>
       <c r="B701" s="7">
-        <v>394</v>
+        <v>466</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" s="6">
-        <v>394</v>
+        <v>140</v>
       </c>
       <c r="C702" s="8">
-        <v>458</v>
+        <v>79</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" s="6">
-        <v>458</v>
+        <v>79</v>
       </c>
       <c r="B703" s="7">
-        <v>394</v>
+        <v>140</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" s="6">
-        <v>286</v>
+        <v>140</v>
       </c>
       <c r="C704" s="8">
-        <v>458</v>
+        <v>59</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" s="6">
-        <v>458</v>
+        <v>59</v>
       </c>
       <c r="B705" s="7">
-        <v>286</v>
+        <v>140</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" s="6">
-        <v>466</v>
+        <v>140</v>
       </c>
       <c r="C706" s="8">
-        <v>467</v>
+        <v>334</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="6">
-        <v>467</v>
+        <v>334</v>
       </c>
       <c r="B707" s="7">
-        <v>466</v>
+        <v>140</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" s="6">
-        <v>467</v>
+        <v>232</v>
       </c>
       <c r="C708" s="8">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" s="6">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B709" s="7">
-        <v>467</v>
+        <v>232</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" s="6">
-        <v>466</v>
+        <v>232</v>
       </c>
       <c r="C710" s="8">
-        <v>178</v>
+        <v>352</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" s="6">
-        <v>178</v>
+        <v>352</v>
       </c>
       <c r="B711" s="7">
-        <v>466</v>
+        <v>232</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" s="6">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="C712" s="8">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" s="6">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B713" s="7">
-        <v>140</v>
+        <v>232</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" s="6">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="C714" s="8">
-        <v>59</v>
+        <v>313</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" s="6">
-        <v>59</v>
+        <v>313</v>
       </c>
       <c r="B715" s="7">
-        <v>140</v>
+        <v>232</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" s="6">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="C716" s="8">
-        <v>334</v>
+        <v>90</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" s="6">
-        <v>334</v>
+        <v>90</v>
       </c>
       <c r="B717" s="7">
-        <v>140</v>
+        <v>232</v>
       </c>
     </row>
     <row r="718">
@@ -5839,12 +5839,12 @@
         <v>232</v>
       </c>
       <c r="C718" s="8">
-        <v>59</v>
+        <v>145</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" s="6">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="B719" s="7">
         <v>232</v>
@@ -5855,12 +5855,12 @@
         <v>232</v>
       </c>
       <c r="C720" s="8">
-        <v>352</v>
+        <v>57</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" s="6">
-        <v>352</v>
+        <v>57</v>
       </c>
       <c r="B721" s="7">
         <v>232</v>
@@ -5868,114 +5868,114 @@
     </row>
     <row r="722">
       <c r="A722" s="6">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="C722" s="8">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" s="6">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B723" s="7">
-        <v>232</v>
+        <v>472</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" s="6">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="C724" s="8">
-        <v>313</v>
+        <v>117</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" s="6">
-        <v>313</v>
+        <v>117</v>
       </c>
       <c r="B725" s="7">
-        <v>232</v>
+        <v>472</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" s="6">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C726" s="8">
-        <v>90</v>
+        <v>2</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="B727" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" s="6">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C728" s="8">
-        <v>145</v>
+        <v>64</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" s="6">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="B729" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" s="6">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C730" s="8">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" s="6">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B731" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" s="6">
-        <v>472</v>
+        <v>231</v>
       </c>
       <c r="C732" s="8">
-        <v>79</v>
+        <v>126</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="6">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="B733" s="7">
-        <v>472</v>
+        <v>231</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" s="6">
-        <v>472</v>
+        <v>231</v>
       </c>
       <c r="C734" s="8">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" s="6">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B735" s="7">
-        <v>472</v>
+        <v>231</v>
       </c>
     </row>
     <row r="736">
@@ -5983,12 +5983,12 @@
         <v>231</v>
       </c>
       <c r="C736" s="8">
-        <v>2</v>
+        <v>313</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" s="6">
-        <v>2</v>
+        <v>313</v>
       </c>
       <c r="B737" s="7">
         <v>231</v>
@@ -5999,12 +5999,12 @@
         <v>231</v>
       </c>
       <c r="C738" s="8">
-        <v>64</v>
+        <v>135</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" s="6">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="B739" s="7">
         <v>231</v>
@@ -6012,242 +6012,946 @@
     </row>
     <row r="740">
       <c r="A740" s="6">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C740" s="8">
-        <v>59</v>
+        <v>473</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" s="6">
-        <v>59</v>
+        <v>473</v>
       </c>
       <c r="B741" s="7">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" s="6">
-        <v>231</v>
+        <v>473</v>
       </c>
       <c r="C742" s="8">
-        <v>126</v>
+        <v>474</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" s="6">
-        <v>126</v>
+        <v>474</v>
       </c>
       <c r="B743" s="7">
-        <v>231</v>
+        <v>473</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" s="6">
-        <v>231</v>
+        <v>60</v>
       </c>
       <c r="C744" s="8">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" s="6">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B745" s="7">
-        <v>231</v>
+        <v>60</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="6">
-        <v>231</v>
+        <v>60</v>
       </c>
       <c r="C746" s="8">
-        <v>313</v>
+        <v>90</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" s="6">
-        <v>313</v>
+        <v>90</v>
       </c>
       <c r="B747" s="7">
-        <v>231</v>
+        <v>60</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" s="6">
-        <v>231</v>
+        <v>60</v>
       </c>
       <c r="C748" s="8">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" s="6">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B749" s="7">
-        <v>231</v>
+        <v>60</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="6">
-        <v>221</v>
+        <v>60</v>
       </c>
       <c r="C750" s="8">
-        <v>473</v>
+        <v>59</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="6">
-        <v>473</v>
+        <v>59</v>
       </c>
       <c r="B751" s="7">
-        <v>221</v>
+        <v>60</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" s="6">
-        <v>473</v>
+        <v>90</v>
       </c>
       <c r="C752" s="8">
-        <v>474</v>
+        <v>79</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="6">
-        <v>474</v>
+        <v>79</v>
       </c>
       <c r="B753" s="7">
-        <v>473</v>
+        <v>90</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" s="6">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C754" s="8">
-        <v>119</v>
+        <v>145</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="6">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="B755" s="7">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" s="6">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C756" s="8">
-        <v>90</v>
+        <v>389</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" s="6">
+        <v>389</v>
+      </c>
+      <c r="B757" s="7">
         <v>90</v>
-      </c>
-      <c r="B757" s="7">
-        <v>60</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" s="6">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C758" s="8">
-        <v>117</v>
+        <v>57</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" s="6">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="B759" s="7">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" s="6">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="C760" s="8">
-        <v>59</v>
+        <v>363</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" s="6">
-        <v>59</v>
+        <v>363</v>
       </c>
       <c r="B761" s="7">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" s="6">
-        <v>90</v>
+        <v>362</v>
       </c>
       <c r="C762" s="8">
-        <v>79</v>
+        <v>476</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" s="6">
-        <v>79</v>
+        <v>476</v>
       </c>
       <c r="B763" s="7">
-        <v>90</v>
+        <v>362</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" s="6">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="C764" s="8">
-        <v>145</v>
+        <v>478</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" s="6">
-        <v>145</v>
+        <v>478</v>
       </c>
       <c r="B765" s="7">
-        <v>90</v>
+        <v>119</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" s="6">
-        <v>90</v>
+        <v>224</v>
       </c>
       <c r="C766" s="8">
-        <v>389</v>
+        <v>476</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" s="6">
-        <v>389</v>
+        <v>476</v>
       </c>
       <c r="B767" s="7">
-        <v>90</v>
+        <v>224</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" s="6">
-        <v>90</v>
+        <v>224</v>
       </c>
       <c r="C768" s="8">
-        <v>57</v>
+        <v>478</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" s="6">
-        <v>57</v>
+        <v>478</v>
       </c>
       <c r="B769" s="7">
-        <v>90</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="6">
+        <v>224</v>
+      </c>
+      <c r="C770" s="8">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="6">
+        <v>479</v>
+      </c>
+      <c r="B771" s="7">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="6">
+        <v>482</v>
+      </c>
+      <c r="C772" s="8">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="6">
+        <v>481</v>
+      </c>
+      <c r="B773" s="7">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="6">
+        <v>482</v>
+      </c>
+      <c r="C774" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="6">
+        <v>194</v>
+      </c>
+      <c r="B775" s="7">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="6">
+        <v>475</v>
+      </c>
+      <c r="C776" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="6">
+        <v>194</v>
+      </c>
+      <c r="B777" s="7">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="6">
+        <v>475</v>
+      </c>
+      <c r="C778" s="8">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="6">
+        <v>483</v>
+      </c>
+      <c r="B779" s="7">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="6">
+        <v>475</v>
+      </c>
+      <c r="C780" s="8">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="6">
+        <v>484</v>
+      </c>
+      <c r="B781" s="7">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="6">
+        <v>372</v>
+      </c>
+      <c r="C782" s="8">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="6">
+        <v>481</v>
+      </c>
+      <c r="B783" s="7">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="6">
+        <v>439</v>
+      </c>
+      <c r="C784" s="8">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="6">
+        <v>372</v>
+      </c>
+      <c r="B785" s="7">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="6">
+        <v>79</v>
+      </c>
+      <c r="C786" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="6">
+        <v>58</v>
+      </c>
+      <c r="B787" s="7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="6">
+        <v>79</v>
+      </c>
+      <c r="C788" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="6">
+        <v>25</v>
+      </c>
+      <c r="B789" s="7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="6">
+        <v>79</v>
+      </c>
+      <c r="C790" s="8">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="6">
+        <v>438</v>
+      </c>
+      <c r="B791" s="7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="6">
+        <v>1</v>
+      </c>
+      <c r="C792" s="8">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="6">
+        <v>179</v>
+      </c>
+      <c r="B793" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="6">
+        <v>1</v>
+      </c>
+      <c r="C794" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="6">
+        <v>64</v>
+      </c>
+      <c r="B795" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="6">
+        <v>4</v>
+      </c>
+      <c r="C796" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="6">
+        <v>79</v>
+      </c>
+      <c r="B797" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="6">
+        <v>4</v>
+      </c>
+      <c r="C798" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="6">
+        <v>19</v>
+      </c>
+      <c r="B799" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="6">
+        <v>4</v>
+      </c>
+      <c r="C800" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="6">
+        <v>20</v>
+      </c>
+      <c r="B801" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="6">
+        <v>4</v>
+      </c>
+      <c r="C802" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="6">
+        <v>59</v>
+      </c>
+      <c r="B803" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="6">
+        <v>10</v>
+      </c>
+      <c r="C804" s="8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="6">
+        <v>65</v>
+      </c>
+      <c r="B805" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="6">
+        <v>71</v>
+      </c>
+      <c r="C806" s="8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="6">
+        <v>72</v>
+      </c>
+      <c r="B807" s="7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="6">
+        <v>232</v>
+      </c>
+      <c r="C808" s="8">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="6">
+        <v>135</v>
+      </c>
+      <c r="B809" s="7">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="6">
+        <v>250</v>
+      </c>
+      <c r="C810" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="6">
+        <v>24</v>
+      </c>
+      <c r="B811" s="7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="6">
+        <v>49</v>
+      </c>
+      <c r="C812" s="8">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="6">
+        <v>358</v>
+      </c>
+      <c r="B813" s="7">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="6">
+        <v>322</v>
+      </c>
+      <c r="C814" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="6">
+        <v>47</v>
+      </c>
+      <c r="B815" s="7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="6">
+        <v>322</v>
+      </c>
+      <c r="C816" s="8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="6">
+        <v>96</v>
+      </c>
+      <c r="B817" s="7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="6">
+        <v>322</v>
+      </c>
+      <c r="C818" s="8">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="6">
+        <v>95</v>
+      </c>
+      <c r="B819" s="7">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="6">
+        <v>321</v>
+      </c>
+      <c r="C820" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="6">
+        <v>47</v>
+      </c>
+      <c r="B821" s="7">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="6">
+        <v>321</v>
+      </c>
+      <c r="C822" s="8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="6">
+        <v>96</v>
+      </c>
+      <c r="B823" s="7">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="6">
+        <v>53</v>
+      </c>
+      <c r="C824" s="8">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="6">
+        <v>214</v>
+      </c>
+      <c r="B825" s="7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="6">
+        <v>347</v>
+      </c>
+      <c r="C826" s="8">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="6">
+        <v>389</v>
+      </c>
+      <c r="B827" s="7">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="6">
+        <v>46</v>
+      </c>
+      <c r="C828" s="8">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="6">
+        <v>106</v>
+      </c>
+      <c r="B829" s="7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="6">
+        <v>46</v>
+      </c>
+      <c r="C830" s="8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="6">
+        <v>125</v>
+      </c>
+      <c r="B831" s="7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="6">
+        <v>360</v>
+      </c>
+      <c r="C832" s="8">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="6">
+        <v>483</v>
+      </c>
+      <c r="B833" s="7">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="6">
+        <v>360</v>
+      </c>
+      <c r="C834" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="6">
+        <v>58</v>
+      </c>
+      <c r="B835" s="7">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="6">
+        <v>360</v>
+      </c>
+      <c r="C836" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="6">
+        <v>79</v>
+      </c>
+      <c r="B837" s="7">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="6">
+        <v>360</v>
+      </c>
+      <c r="C838" s="8">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="6">
+        <v>367</v>
+      </c>
+      <c r="B839" s="7">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="6">
+        <v>368</v>
+      </c>
+      <c r="C840" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="6">
+        <v>1</v>
+      </c>
+      <c r="B841" s="7">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="6">
+        <v>368</v>
+      </c>
+      <c r="C842" s="8">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="6">
+        <v>130</v>
+      </c>
+      <c r="B843" s="7">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="6">
+        <v>368</v>
+      </c>
+      <c r="C844" s="8">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="6">
+        <v>483</v>
+      </c>
+      <c r="B845" s="7">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="6">
+        <v>368</v>
+      </c>
+      <c r="C846" s="8">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="6">
+        <v>106</v>
+      </c>
+      <c r="B847" s="7">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="6">
+        <v>368</v>
+      </c>
+      <c r="C848" s="8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="6">
+        <v>49</v>
+      </c>
+      <c r="B849" s="7">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="6">
+        <v>368</v>
+      </c>
+      <c r="C850" s="8">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="6">
+        <v>69</v>
+      </c>
+      <c r="B851" s="7">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="6">
+        <v>140</v>
+      </c>
+      <c r="C852" s="8">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="6">
+        <v>322</v>
+      </c>
+      <c r="B853" s="7">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="6">
+        <v>362</v>
+      </c>
+      <c r="C854" s="8">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="6">
+        <v>478</v>
+      </c>
+      <c r="B855" s="7">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="6">
+        <v>487</v>
+      </c>
+      <c r="C856" s="8">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="6">
+        <v>389</v>
+      </c>
+      <c r="B857" s="7">
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Concepthierarchy.xlsx
+++ b/raw/Concepthierarchy.xlsx
@@ -1436,23 +1436,23 @@
     </row>
     <row r="168">
       <c r="A168" s="6">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C168" s="8">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="B169" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C170" s="8">
         <v>48</v>
@@ -1463,39 +1463,39 @@
         <v>48</v>
       </c>
       <c r="B171" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="6">
+        <v>132</v>
+      </c>
+      <c r="C172" s="8">
         <v>131</v>
-      </c>
-      <c r="C172" s="8">
-        <v>48</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="B173" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="6">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C174" s="8">
-        <v>131</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="B175" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="176">
@@ -1503,12 +1503,12 @@
         <v>134</v>
       </c>
       <c r="C176" s="8">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B177" s="7">
         <v>134</v>
@@ -1519,12 +1519,12 @@
         <v>134</v>
       </c>
       <c r="C178" s="8">
-        <v>59</v>
+        <v>135</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="B179" s="7">
         <v>134</v>
@@ -1535,12 +1535,12 @@
         <v>134</v>
       </c>
       <c r="C180" s="8">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B181" s="7">
         <v>134</v>
@@ -1548,18 +1548,18 @@
     </row>
     <row r="182">
       <c r="A182" s="6">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C182" s="8">
-        <v>136</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="B183" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="184">
@@ -1567,12 +1567,12 @@
         <v>133</v>
       </c>
       <c r="C184" s="8">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B185" s="7">
         <v>133</v>
@@ -1583,12 +1583,12 @@
         <v>133</v>
       </c>
       <c r="C186" s="8">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="B187" s="7">
         <v>133</v>
@@ -1596,18 +1596,18 @@
     </row>
     <row r="188">
       <c r="A188" s="6">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C188" s="8">
-        <v>135</v>
+        <v>79</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6">
+        <v>79</v>
+      </c>
+      <c r="B189" s="7">
         <v>135</v>
-      </c>
-      <c r="B189" s="7">
-        <v>133</v>
       </c>
     </row>
     <row r="190">
@@ -1615,12 +1615,12 @@
         <v>135</v>
       </c>
       <c r="C190" s="8">
-        <v>79</v>
+        <v>125</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="B191" s="7">
         <v>135</v>
@@ -1631,12 +1631,12 @@
         <v>135</v>
       </c>
       <c r="C192" s="8">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B193" s="7">
         <v>135</v>
@@ -1647,12 +1647,12 @@
         <v>135</v>
       </c>
       <c r="C194" s="8">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="B195" s="7">
         <v>135</v>
@@ -1663,12 +1663,12 @@
         <v>135</v>
       </c>
       <c r="C196" s="8">
-        <v>106</v>
+        <v>48</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="B197" s="7">
         <v>135</v>
@@ -1676,18 +1676,18 @@
     </row>
     <row r="198">
       <c r="A198" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C198" s="8">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B199" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="200">
@@ -1695,12 +1695,12 @@
         <v>136</v>
       </c>
       <c r="C200" s="8">
-        <v>79</v>
+        <v>49</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="B201" s="7">
         <v>136</v>
@@ -1711,12 +1711,12 @@
         <v>136</v>
       </c>
       <c r="C202" s="8">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="B203" s="7">
         <v>136</v>
@@ -1727,12 +1727,12 @@
         <v>136</v>
       </c>
       <c r="C204" s="8">
-        <v>113</v>
+        <v>138</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="B205" s="7">
         <v>136</v>
@@ -1743,12 +1743,12 @@
         <v>136</v>
       </c>
       <c r="C206" s="8">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B207" s="7">
         <v>136</v>
@@ -1756,18 +1756,18 @@
     </row>
     <row r="208">
       <c r="A208" s="6">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C208" s="8">
-        <v>137</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="B209" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="210">
@@ -1775,12 +1775,12 @@
         <v>139</v>
       </c>
       <c r="C210" s="8">
-        <v>2</v>
+        <v>135</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="B211" s="7">
         <v>139</v>
@@ -1791,12 +1791,12 @@
         <v>139</v>
       </c>
       <c r="C212" s="8">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B213" s="7">
         <v>139</v>
@@ -1807,12 +1807,12 @@
         <v>139</v>
       </c>
       <c r="C214" s="8">
-        <v>136</v>
+        <v>59</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="B215" s="7">
         <v>139</v>
@@ -1820,34 +1820,34 @@
     </row>
     <row r="216">
       <c r="A216" s="6">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C216" s="8">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B217" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="6">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="C218" s="8">
-        <v>66</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="B219" s="7">
-        <v>141</v>
+        <v>43</v>
       </c>
     </row>
     <row r="220">
@@ -1855,12 +1855,12 @@
         <v>43</v>
       </c>
       <c r="C220" s="8">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B221" s="7">
         <v>43</v>
@@ -1868,50 +1868,50 @@
     </row>
     <row r="222">
       <c r="A222" s="6">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="C222" s="8">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B223" s="7">
-        <v>43</v>
+        <v>143</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="6">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C224" s="8">
-        <v>47</v>
+        <v>145</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="B225" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="6">
+        <v>143</v>
+      </c>
+      <c r="C226" s="8">
         <v>144</v>
-      </c>
-      <c r="C226" s="8">
-        <v>145</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B227" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="228">
@@ -1919,12 +1919,12 @@
         <v>143</v>
       </c>
       <c r="C228" s="8">
-        <v>144</v>
+        <v>106</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="B229" s="7">
         <v>143</v>
@@ -1935,12 +1935,12 @@
         <v>143</v>
       </c>
       <c r="C230" s="8">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B231" s="7">
         <v>143</v>
@@ -1948,18 +1948,18 @@
     </row>
     <row r="232">
       <c r="A232" s="6">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C232" s="8">
-        <v>49</v>
+        <v>112</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B233" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="234">
@@ -1967,12 +1967,12 @@
         <v>146</v>
       </c>
       <c r="C234" s="8">
-        <v>112</v>
+        <v>130</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B235" s="7">
         <v>146</v>
@@ -1983,12 +1983,12 @@
         <v>146</v>
       </c>
       <c r="C236" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B237" s="7">
         <v>146</v>
@@ -1996,18 +1996,18 @@
     </row>
     <row r="238">
       <c r="A238" s="6">
+        <v>148</v>
+      </c>
+      <c r="C238" s="8">
         <v>146</v>
-      </c>
-      <c r="C238" s="8">
-        <v>132</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B239" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="240">
@@ -2015,12 +2015,12 @@
         <v>148</v>
       </c>
       <c r="C240" s="8">
-        <v>146</v>
+        <v>106</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="B241" s="7">
         <v>148</v>
@@ -2031,12 +2031,12 @@
         <v>148</v>
       </c>
       <c r="C242" s="8">
-        <v>106</v>
+        <v>125</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B243" s="7">
         <v>148</v>
@@ -2047,12 +2047,12 @@
         <v>148</v>
       </c>
       <c r="C244" s="8">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B245" s="7">
         <v>148</v>
@@ -2063,12 +2063,12 @@
         <v>148</v>
       </c>
       <c r="C246" s="8">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B247" s="7">
         <v>148</v>
@@ -2076,18 +2076,18 @@
     </row>
     <row r="248">
       <c r="A248" s="6">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C248" s="8">
-        <v>130</v>
+        <v>49</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="6">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="B249" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="250">
@@ -2095,12 +2095,12 @@
         <v>149</v>
       </c>
       <c r="C250" s="8">
-        <v>49</v>
+        <v>125</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="B251" s="7">
         <v>149</v>
@@ -2111,12 +2111,12 @@
         <v>149</v>
       </c>
       <c r="C252" s="8">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="6">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B253" s="7">
         <v>149</v>
@@ -2127,12 +2127,12 @@
         <v>149</v>
       </c>
       <c r="C254" s="8">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B255" s="7">
         <v>149</v>
@@ -2140,18 +2140,18 @@
     </row>
     <row r="256">
       <c r="A256" s="6">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C256" s="8">
-        <v>132</v>
+        <v>19</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="B257" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="258">
@@ -2159,12 +2159,12 @@
         <v>150</v>
       </c>
       <c r="C258" s="8">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="B259" s="7">
         <v>150</v>
@@ -2175,12 +2175,12 @@
         <v>150</v>
       </c>
       <c r="C260" s="8">
-        <v>106</v>
+        <v>47</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B261" s="7">
         <v>150</v>
@@ -2188,18 +2188,18 @@
     </row>
     <row r="262">
       <c r="A262" s="6">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C262" s="8">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B263" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="264">
@@ -2207,12 +2207,12 @@
         <v>152</v>
       </c>
       <c r="C264" s="8">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B265" s="7">
         <v>152</v>
@@ -2220,18 +2220,18 @@
     </row>
     <row r="266">
       <c r="A266" s="6">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C266" s="8">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B267" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="268">
@@ -2239,12 +2239,12 @@
         <v>153</v>
       </c>
       <c r="C268" s="8">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B269" s="7">
         <v>153</v>
@@ -2255,12 +2255,12 @@
         <v>153</v>
       </c>
       <c r="C270" s="8">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="6">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="B271" s="7">
         <v>153</v>
@@ -2268,18 +2268,18 @@
     </row>
     <row r="272">
       <c r="A272" s="6">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C272" s="8">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="6">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B273" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="274">
@@ -2287,12 +2287,12 @@
         <v>155</v>
       </c>
       <c r="C274" s="8">
-        <v>57</v>
+        <v>135</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="6">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="B275" s="7">
         <v>155</v>
@@ -2300,23 +2300,23 @@
     </row>
     <row r="276">
       <c r="A276" s="6">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C276" s="8">
-        <v>135</v>
+        <v>79</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="6">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="B277" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="6">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C278" s="8">
         <v>79</v>
@@ -2327,23 +2327,23 @@
         <v>79</v>
       </c>
       <c r="B279" s="7">
-        <v>156</v>
+        <v>171</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="6">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C280" s="8">
-        <v>79</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="6">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="B281" s="7">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="282">
@@ -2351,12 +2351,12 @@
         <v>179</v>
       </c>
       <c r="C282" s="8">
-        <v>2</v>
+        <v>178</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="6">
-        <v>2</v>
+        <v>178</v>
       </c>
       <c r="B283" s="7">
         <v>179</v>
@@ -2367,12 +2367,12 @@
         <v>179</v>
       </c>
       <c r="C284" s="8">
-        <v>178</v>
+        <v>64</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="B285" s="7">
         <v>179</v>
@@ -2380,18 +2380,18 @@
     </row>
     <row r="286">
       <c r="A286" s="6">
+        <v>180</v>
+      </c>
+      <c r="C286" s="8">
         <v>179</v>
-      </c>
-      <c r="C286" s="8">
-        <v>64</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6">
-        <v>64</v>
+        <v>179</v>
       </c>
       <c r="B287" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="288">
@@ -2399,12 +2399,12 @@
         <v>180</v>
       </c>
       <c r="C288" s="8">
-        <v>179</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6">
-        <v>179</v>
+        <v>3</v>
       </c>
       <c r="B289" s="7">
         <v>180</v>
@@ -2412,18 +2412,18 @@
     </row>
     <row r="290">
       <c r="A290" s="6">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C290" s="8">
-        <v>3</v>
+        <v>179</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6">
-        <v>3</v>
+        <v>179</v>
       </c>
       <c r="B291" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="292">
@@ -2431,12 +2431,12 @@
         <v>181</v>
       </c>
       <c r="C292" s="8">
-        <v>179</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6">
-        <v>179</v>
+        <v>3</v>
       </c>
       <c r="B293" s="7">
         <v>181</v>
@@ -2444,18 +2444,18 @@
     </row>
     <row r="294">
       <c r="A294" s="6">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C294" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B295" s="7">
-        <v>181</v>
+        <v>199</v>
       </c>
     </row>
     <row r="296">
@@ -2463,12 +2463,12 @@
         <v>199</v>
       </c>
       <c r="C296" s="8">
-        <v>1</v>
+        <v>177</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="B297" s="7">
         <v>199</v>
@@ -2476,34 +2476,34 @@
     </row>
     <row r="298">
       <c r="A298" s="6">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C298" s="8">
-        <v>177</v>
+        <v>202</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="B299" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="6">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="C300" s="8">
-        <v>202</v>
+        <v>64</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="6">
-        <v>202</v>
+        <v>64</v>
       </c>
       <c r="B301" s="7">
-        <v>201</v>
+        <v>182</v>
       </c>
     </row>
     <row r="302">
@@ -2511,12 +2511,12 @@
         <v>182</v>
       </c>
       <c r="C302" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B303" s="7">
         <v>182</v>
@@ -2524,66 +2524,66 @@
     </row>
     <row r="304">
       <c r="A304" s="6">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C304" s="8">
-        <v>65</v>
+        <v>104</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="6">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B305" s="7">
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="6">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C306" s="8">
-        <v>104</v>
+        <v>145</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="6">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="B307" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="6">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C308" s="8">
-        <v>145</v>
+        <v>199</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="6">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="B309" s="7">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="6">
-        <v>195</v>
+        <v>73</v>
       </c>
       <c r="C310" s="8">
-        <v>199</v>
+        <v>157</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="6">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="B311" s="7">
-        <v>195</v>
+        <v>73</v>
       </c>
     </row>
     <row r="312">
@@ -2591,12 +2591,12 @@
         <v>73</v>
       </c>
       <c r="C312" s="8">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="6">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B313" s="7">
         <v>73</v>
@@ -2607,12 +2607,12 @@
         <v>73</v>
       </c>
       <c r="C314" s="8">
-        <v>173</v>
+        <v>211</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="6">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="B315" s="7">
         <v>73</v>
@@ -2620,18 +2620,18 @@
     </row>
     <row r="316">
       <c r="A316" s="6">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C316" s="8">
-        <v>211</v>
+        <v>34</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="6">
-        <v>211</v>
+        <v>34</v>
       </c>
       <c r="B317" s="7">
-        <v>73</v>
+        <v>88</v>
       </c>
     </row>
     <row r="318">
@@ -2639,12 +2639,12 @@
         <v>88</v>
       </c>
       <c r="C318" s="8">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="6">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B319" s="7">
         <v>88</v>
@@ -2652,34 +2652,34 @@
     </row>
     <row r="320">
       <c r="A320" s="6">
-        <v>88</v>
+        <v>226</v>
       </c>
       <c r="C320" s="8">
-        <v>47</v>
+        <v>227</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="6">
-        <v>47</v>
+        <v>227</v>
       </c>
       <c r="B321" s="7">
-        <v>88</v>
+        <v>226</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="6">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C322" s="8">
-        <v>227</v>
+        <v>47</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="6">
+        <v>47</v>
+      </c>
+      <c r="B323" s="7">
         <v>227</v>
-      </c>
-      <c r="B323" s="7">
-        <v>226</v>
       </c>
     </row>
     <row r="324">
@@ -2687,12 +2687,12 @@
         <v>227</v>
       </c>
       <c r="C324" s="8">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="6">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B325" s="7">
         <v>227</v>
@@ -2700,66 +2700,66 @@
     </row>
     <row r="326">
       <c r="A326" s="6">
-        <v>227</v>
+        <v>50</v>
       </c>
       <c r="C326" s="8">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B327" s="7">
-        <v>227</v>
+        <v>50</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="6">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C328" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="6">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B329" s="7">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="6">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="C330" s="8">
-        <v>68</v>
+        <v>227</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="6">
-        <v>68</v>
+        <v>227</v>
       </c>
       <c r="B331" s="7">
-        <v>20</v>
+        <v>234</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="6">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C332" s="8">
-        <v>227</v>
+        <v>95</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="6">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="B333" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="334">
@@ -2767,12 +2767,12 @@
         <v>235</v>
       </c>
       <c r="C334" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="6">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B335" s="7">
         <v>235</v>
@@ -2780,34 +2780,34 @@
     </row>
     <row r="336">
       <c r="A336" s="6">
-        <v>235</v>
+        <v>144</v>
       </c>
       <c r="C336" s="8">
-        <v>96</v>
+        <v>66</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="6">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="B337" s="7">
-        <v>235</v>
+        <v>144</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="6">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="C338" s="8">
-        <v>66</v>
+        <v>98</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="6">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="B339" s="7">
-        <v>144</v>
+        <v>241</v>
       </c>
     </row>
     <row r="340">
@@ -2815,12 +2815,12 @@
         <v>241</v>
       </c>
       <c r="C340" s="8">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="6">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B341" s="7">
         <v>241</v>
@@ -2831,12 +2831,12 @@
         <v>241</v>
       </c>
       <c r="C342" s="8">
-        <v>104</v>
+        <v>53</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="6">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="B343" s="7">
         <v>241</v>
@@ -2847,12 +2847,12 @@
         <v>241</v>
       </c>
       <c r="C344" s="8">
-        <v>53</v>
+        <v>143</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="6">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="B345" s="7">
         <v>241</v>
@@ -2863,12 +2863,12 @@
         <v>241</v>
       </c>
       <c r="C346" s="8">
-        <v>143</v>
+        <v>242</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="6">
-        <v>143</v>
+        <v>242</v>
       </c>
       <c r="B347" s="7">
         <v>241</v>
@@ -2876,18 +2876,18 @@
     </row>
     <row r="348">
       <c r="A348" s="6">
-        <v>241</v>
+        <v>97</v>
       </c>
       <c r="C348" s="8">
-        <v>242</v>
+        <v>64</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="6">
-        <v>242</v>
+        <v>64</v>
       </c>
       <c r="B349" s="7">
-        <v>241</v>
+        <v>97</v>
       </c>
     </row>
     <row r="350">
@@ -2895,12 +2895,12 @@
         <v>97</v>
       </c>
       <c r="C350" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B351" s="7">
         <v>97</v>
@@ -2908,39 +2908,39 @@
     </row>
     <row r="352">
       <c r="A352" s="6">
-        <v>97</v>
+        <v>250</v>
       </c>
       <c r="C352" s="8">
-        <v>65</v>
+        <v>251</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="6">
-        <v>65</v>
+        <v>251</v>
       </c>
       <c r="B353" s="7">
-        <v>97</v>
+        <v>250</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="6">
+        <v>162</v>
+      </c>
+      <c r="C354" s="8">
         <v>250</v>
-      </c>
-      <c r="C354" s="8">
-        <v>251</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="6">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B355" s="7">
-        <v>250</v>
+        <v>162</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="6">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C356" s="8">
         <v>250</v>
@@ -2951,39 +2951,39 @@
         <v>250</v>
       </c>
       <c r="B357" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="6">
-        <v>161</v>
+        <v>252</v>
       </c>
       <c r="C358" s="8">
-        <v>250</v>
+        <v>209</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="6">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="B359" s="7">
-        <v>161</v>
+        <v>252</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="6">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C360" s="8">
-        <v>209</v>
+        <v>79</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="6">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="B361" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="362">
@@ -2991,12 +2991,12 @@
         <v>259</v>
       </c>
       <c r="C362" s="8">
-        <v>79</v>
+        <v>260</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="6">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="B363" s="7">
         <v>259</v>
@@ -3007,12 +3007,12 @@
         <v>259</v>
       </c>
       <c r="C364" s="8">
-        <v>260</v>
+        <v>19</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="6">
-        <v>260</v>
+        <v>19</v>
       </c>
       <c r="B365" s="7">
         <v>259</v>
@@ -3023,12 +3023,12 @@
         <v>259</v>
       </c>
       <c r="C366" s="8">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="6">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="B367" s="7">
         <v>259</v>
@@ -3039,12 +3039,12 @@
         <v>259</v>
       </c>
       <c r="C368" s="8">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="6">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="B369" s="7">
         <v>259</v>
@@ -3055,12 +3055,12 @@
         <v>259</v>
       </c>
       <c r="C370" s="8">
-        <v>25</v>
+        <v>261</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="6">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="B371" s="7">
         <v>259</v>
@@ -3068,18 +3068,18 @@
     </row>
     <row r="372">
       <c r="A372" s="6">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C372" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="6">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B373" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="374">
@@ -3087,12 +3087,12 @@
         <v>262</v>
       </c>
       <c r="C374" s="8">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="6">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B375" s="7">
         <v>262</v>
@@ -3100,18 +3100,18 @@
     </row>
     <row r="376">
       <c r="A376" s="6">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C376" s="8">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="6">
+        <v>261</v>
+      </c>
+      <c r="B377" s="7">
         <v>264</v>
-      </c>
-      <c r="B377" s="7">
-        <v>262</v>
       </c>
     </row>
     <row r="378">
@@ -3119,12 +3119,12 @@
         <v>264</v>
       </c>
       <c r="C378" s="8">
-        <v>261</v>
+        <v>25</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="6">
-        <v>261</v>
+        <v>25</v>
       </c>
       <c r="B379" s="7">
         <v>264</v>
@@ -3135,12 +3135,12 @@
         <v>264</v>
       </c>
       <c r="C380" s="8">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="6">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B381" s="7">
         <v>264</v>
@@ -3148,18 +3148,18 @@
     </row>
     <row r="382">
       <c r="A382" s="6">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C382" s="8">
-        <v>78</v>
+        <v>266</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="6">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="B383" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="384">
@@ -3167,12 +3167,12 @@
         <v>265</v>
       </c>
       <c r="C384" s="8">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="6">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B385" s="7">
         <v>265</v>
@@ -3183,12 +3183,12 @@
         <v>265</v>
       </c>
       <c r="C386" s="8">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="6">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B387" s="7">
         <v>265</v>
@@ -3199,12 +3199,12 @@
         <v>265</v>
       </c>
       <c r="C388" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="6">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B389" s="7">
         <v>265</v>
@@ -3212,18 +3212,18 @@
     </row>
     <row r="390">
       <c r="A390" s="6">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C390" s="8">
-        <v>269</v>
+        <v>25</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="6">
-        <v>269</v>
+        <v>25</v>
       </c>
       <c r="B391" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="392">
@@ -3231,12 +3231,12 @@
         <v>270</v>
       </c>
       <c r="C392" s="8">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B393" s="7">
         <v>270</v>
@@ -3247,12 +3247,12 @@
         <v>270</v>
       </c>
       <c r="C394" s="8">
-        <v>19</v>
+        <v>263</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="6">
-        <v>19</v>
+        <v>263</v>
       </c>
       <c r="B395" s="7">
         <v>270</v>
@@ -3260,18 +3260,18 @@
     </row>
     <row r="396">
       <c r="A396" s="6">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C396" s="8">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="6">
+        <v>271</v>
+      </c>
+      <c r="B397" s="7">
         <v>263</v>
-      </c>
-      <c r="B397" s="7">
-        <v>270</v>
       </c>
     </row>
     <row r="398">
@@ -3279,12 +3279,12 @@
         <v>263</v>
       </c>
       <c r="C398" s="8">
-        <v>271</v>
+        <v>261</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="6">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B399" s="7">
         <v>263</v>
@@ -3295,12 +3295,12 @@
         <v>263</v>
       </c>
       <c r="C400" s="8">
-        <v>261</v>
+        <v>82</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="6">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="B401" s="7">
         <v>263</v>
@@ -3311,12 +3311,12 @@
         <v>263</v>
       </c>
       <c r="C402" s="8">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="6">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="B403" s="7">
         <v>263</v>
@@ -3327,12 +3327,12 @@
         <v>263</v>
       </c>
       <c r="C404" s="8">
-        <v>25</v>
+        <v>272</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="6">
-        <v>25</v>
+        <v>272</v>
       </c>
       <c r="B405" s="7">
         <v>263</v>
@@ -3340,23 +3340,23 @@
     </row>
     <row r="406">
       <c r="A406" s="6">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C406" s="8">
-        <v>272</v>
+        <v>179</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="6">
-        <v>272</v>
+        <v>179</v>
       </c>
       <c r="B407" s="7">
-        <v>263</v>
+        <v>275</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="6">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C408" s="8">
         <v>179</v>
@@ -3367,39 +3367,39 @@
         <v>179</v>
       </c>
       <c r="B409" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="6">
-        <v>276</v>
-      </c>
-      <c r="C410" s="8">
-        <v>179</v>
+        <v>277</v>
+      </c>
+      <c r="B410" s="7">
+        <v>241</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="6">
-        <v>179</v>
-      </c>
-      <c r="B411" s="7">
-        <v>276</v>
+        <v>241</v>
+      </c>
+      <c r="C411" s="8">
+        <v>277</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="6">
+        <v>278</v>
+      </c>
+      <c r="C412" s="8">
         <v>277</v>
-      </c>
-      <c r="B412" s="7">
-        <v>241</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="6">
-        <v>241</v>
-      </c>
-      <c r="C413" s="8">
         <v>277</v>
+      </c>
+      <c r="B413" s="7">
+        <v>278</v>
       </c>
     </row>
     <row r="414">
@@ -3407,12 +3407,12 @@
         <v>278</v>
       </c>
       <c r="C414" s="8">
-        <v>277</v>
+        <v>79</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="6">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="B415" s="7">
         <v>278</v>
@@ -3420,34 +3420,34 @@
     </row>
     <row r="416">
       <c r="A416" s="6">
+        <v>279</v>
+      </c>
+      <c r="C416" s="8">
         <v>278</v>
-      </c>
-      <c r="C416" s="8">
-        <v>79</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="6">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="B417" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="6">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C418" s="8">
-        <v>278</v>
+        <v>79</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="6">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="B419" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="420">
@@ -3455,12 +3455,12 @@
         <v>280</v>
       </c>
       <c r="C420" s="8">
-        <v>79</v>
+        <v>28</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="6">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B421" s="7">
         <v>280</v>
@@ -3471,12 +3471,12 @@
         <v>280</v>
       </c>
       <c r="C422" s="8">
-        <v>28</v>
+        <v>119</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="6">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="B423" s="7">
         <v>280</v>
@@ -3487,12 +3487,12 @@
         <v>280</v>
       </c>
       <c r="C424" s="8">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="6">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B425" s="7">
         <v>280</v>
@@ -3500,18 +3500,18 @@
     </row>
     <row r="426">
       <c r="A426" s="6">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C426" s="8">
-        <v>117</v>
+        <v>57</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="6">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="B427" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="428">
@@ -3519,12 +3519,12 @@
         <v>281</v>
       </c>
       <c r="C428" s="8">
-        <v>57</v>
+        <v>90</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="6">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="B429" s="7">
         <v>281</v>
@@ -3535,12 +3535,12 @@
         <v>281</v>
       </c>
       <c r="C430" s="8">
-        <v>90</v>
+        <v>145</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="6">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="B431" s="7">
         <v>281</v>
@@ -3551,12 +3551,12 @@
         <v>281</v>
       </c>
       <c r="C432" s="8">
-        <v>145</v>
+        <v>69</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="6">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="B433" s="7">
         <v>281</v>
@@ -3567,12 +3567,12 @@
         <v>281</v>
       </c>
       <c r="C434" s="8">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="6">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B435" s="7">
         <v>281</v>
@@ -3580,66 +3580,66 @@
     </row>
     <row r="436">
       <c r="A436" s="6">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C436" s="8">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="6">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B437" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="6">
+        <v>283</v>
+      </c>
+      <c r="C438" s="8">
         <v>282</v>
-      </c>
-      <c r="C438" s="8">
-        <v>66</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="6">
-        <v>66</v>
+        <v>282</v>
       </c>
       <c r="B439" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="6">
+        <v>282</v>
+      </c>
+      <c r="C440" s="8">
         <v>283</v>
-      </c>
-      <c r="C440" s="8">
-        <v>282</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="6">
+        <v>283</v>
+      </c>
+      <c r="B441" s="7">
         <v>282</v>
-      </c>
-      <c r="B441" s="7">
-        <v>283</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="6">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C442" s="8">
-        <v>283</v>
+        <v>178</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="6">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="B443" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="444">
@@ -3647,12 +3647,12 @@
         <v>284</v>
       </c>
       <c r="C444" s="8">
-        <v>178</v>
+        <v>68</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="6">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="B445" s="7">
         <v>284</v>
@@ -3663,12 +3663,12 @@
         <v>284</v>
       </c>
       <c r="C446" s="8">
-        <v>68</v>
+        <v>179</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="6">
-        <v>68</v>
+        <v>179</v>
       </c>
       <c r="B447" s="7">
         <v>284</v>
@@ -3679,12 +3679,12 @@
         <v>284</v>
       </c>
       <c r="C448" s="8">
-        <v>179</v>
+        <v>65</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="6">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="B449" s="7">
         <v>284</v>
@@ -3695,12 +3695,12 @@
         <v>284</v>
       </c>
       <c r="C450" s="8">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="6">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B451" s="7">
         <v>284</v>
@@ -3708,34 +3708,34 @@
     </row>
     <row r="452">
       <c r="A452" s="6">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C452" s="8">
-        <v>64</v>
+        <v>286</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="6">
-        <v>64</v>
+        <v>286</v>
       </c>
       <c r="B453" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="6">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C454" s="8">
-        <v>286</v>
+        <v>65</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="6">
+        <v>65</v>
+      </c>
+      <c r="B455" s="7">
         <v>286</v>
-      </c>
-      <c r="B455" s="7">
-        <v>285</v>
       </c>
     </row>
     <row r="456">
@@ -3743,12 +3743,12 @@
         <v>286</v>
       </c>
       <c r="C456" s="8">
-        <v>65</v>
+        <v>22</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="6">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="B457" s="7">
         <v>286</v>
@@ -3759,12 +3759,12 @@
         <v>286</v>
       </c>
       <c r="C458" s="8">
-        <v>22</v>
+        <v>287</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="6">
-        <v>22</v>
+        <v>287</v>
       </c>
       <c r="B459" s="7">
         <v>286</v>
@@ -3775,12 +3775,12 @@
         <v>286</v>
       </c>
       <c r="C460" s="8">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="6">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B461" s="7">
         <v>286</v>
@@ -3788,23 +3788,23 @@
     </row>
     <row r="462">
       <c r="A462" s="6">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C462" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="6">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B463" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="6">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="C464" s="8">
         <v>290</v>
@@ -3815,12 +3815,12 @@
         <v>290</v>
       </c>
       <c r="B465" s="7">
-        <v>289</v>
+        <v>116</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="6">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C466" s="8">
         <v>290</v>
@@ -3831,12 +3831,12 @@
         <v>290</v>
       </c>
       <c r="B467" s="7">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="6">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C468" s="8">
         <v>290</v>
@@ -3847,12 +3847,12 @@
         <v>290</v>
       </c>
       <c r="B469" s="7">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="6">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="C470" s="8">
         <v>290</v>
@@ -3863,12 +3863,12 @@
         <v>290</v>
       </c>
       <c r="B471" s="7">
-        <v>111</v>
+        <v>47</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="6">
-        <v>47</v>
+        <v>295</v>
       </c>
       <c r="C472" s="8">
         <v>290</v>
@@ -3879,55 +3879,55 @@
         <v>290</v>
       </c>
       <c r="B473" s="7">
-        <v>47</v>
+        <v>295</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="6">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C474" s="8">
-        <v>290</v>
+        <v>178</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="6">
-        <v>290</v>
+        <v>178</v>
       </c>
       <c r="B475" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="6">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C476" s="8">
-        <v>178</v>
+        <v>302</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="6">
-        <v>178</v>
+        <v>302</v>
       </c>
       <c r="B477" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="6">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C478" s="8">
-        <v>302</v>
+        <v>62</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="6">
-        <v>302</v>
+        <v>62</v>
       </c>
       <c r="B479" s="7">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="480">
@@ -3935,12 +3935,12 @@
         <v>311</v>
       </c>
       <c r="C480" s="8">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="6">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B481" s="7">
         <v>311</v>
@@ -3948,18 +3948,18 @@
     </row>
     <row r="482">
       <c r="A482" s="6">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="C482" s="8">
-        <v>53</v>
+        <v>106</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="6">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B483" s="7">
-        <v>311</v>
+        <v>84</v>
       </c>
     </row>
     <row r="484">
@@ -3967,12 +3967,12 @@
         <v>84</v>
       </c>
       <c r="C484" s="8">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="6">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="B485" s="7">
         <v>84</v>
@@ -3983,12 +3983,12 @@
         <v>84</v>
       </c>
       <c r="C486" s="8">
-        <v>49</v>
+        <v>125</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="6">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="B487" s="7">
         <v>84</v>
@@ -3999,12 +3999,12 @@
         <v>84</v>
       </c>
       <c r="C488" s="8">
-        <v>125</v>
+        <v>47</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="6">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="B489" s="7">
         <v>84</v>
@@ -4012,18 +4012,18 @@
     </row>
     <row r="490">
       <c r="A490" s="6">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="C490" s="8">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="6">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B491" s="7">
-        <v>84</v>
+        <v>312</v>
       </c>
     </row>
     <row r="492">
@@ -4031,12 +4031,12 @@
         <v>312</v>
       </c>
       <c r="C492" s="8">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="6">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B493" s="7">
         <v>312</v>
@@ -4044,34 +4044,34 @@
     </row>
     <row r="494">
       <c r="A494" s="6">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="C494" s="8">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="6">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B495" s="7">
-        <v>312</v>
+        <v>118</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="6">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C496" s="8">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B497" s="7">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="498">
@@ -4079,12 +4079,12 @@
         <v>97</v>
       </c>
       <c r="C498" s="8">
-        <v>70</v>
+        <v>322</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="6">
-        <v>70</v>
+        <v>322</v>
       </c>
       <c r="B499" s="7">
         <v>97</v>
@@ -4092,34 +4092,34 @@
     </row>
     <row r="500">
       <c r="A500" s="6">
-        <v>97</v>
+        <v>325</v>
       </c>
       <c r="C500" s="8">
-        <v>322</v>
+        <v>163</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="6">
-        <v>322</v>
+        <v>163</v>
       </c>
       <c r="B501" s="7">
-        <v>97</v>
+        <v>325</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="6">
-        <v>325</v>
+        <v>14</v>
       </c>
       <c r="C502" s="8">
-        <v>163</v>
+        <v>24</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="6">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="B503" s="7">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="504">
@@ -4127,12 +4127,12 @@
         <v>14</v>
       </c>
       <c r="C504" s="8">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="6">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="B505" s="7">
         <v>14</v>
@@ -4143,12 +4143,12 @@
         <v>14</v>
       </c>
       <c r="C506" s="8">
-        <v>63</v>
+        <v>260</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="6">
-        <v>63</v>
+        <v>260</v>
       </c>
       <c r="B507" s="7">
         <v>14</v>
@@ -4156,18 +4156,18 @@
     </row>
     <row r="508">
       <c r="A508" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C508" s="8">
-        <v>260</v>
+        <v>66</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="6">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="B509" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="510">
@@ -4175,12 +4175,12 @@
         <v>19</v>
       </c>
       <c r="C510" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="6">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B511" s="7">
         <v>19</v>
@@ -4188,39 +4188,39 @@
     </row>
     <row r="512">
       <c r="A512" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C512" s="8">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="6">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B513" s="7">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="6">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="C514" s="8">
-        <v>65</v>
+        <v>329</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="6">
-        <v>65</v>
+        <v>329</v>
       </c>
       <c r="B515" s="7">
-        <v>22</v>
+        <v>78</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="6">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="C516" s="8">
         <v>329</v>
@@ -4231,23 +4231,23 @@
         <v>329</v>
       </c>
       <c r="B517" s="7">
-        <v>78</v>
+        <v>22</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="6">
-        <v>22</v>
+        <v>223</v>
       </c>
       <c r="C518" s="8">
-        <v>329</v>
+        <v>59</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="6">
-        <v>329</v>
+        <v>59</v>
       </c>
       <c r="B519" s="7">
-        <v>22</v>
+        <v>223</v>
       </c>
     </row>
     <row r="520">
@@ -4255,12 +4255,12 @@
         <v>223</v>
       </c>
       <c r="C520" s="8">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="6">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="B521" s="7">
         <v>223</v>
@@ -4271,12 +4271,12 @@
         <v>223</v>
       </c>
       <c r="C522" s="8">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="6">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B523" s="7">
         <v>223</v>
@@ -4284,18 +4284,18 @@
     </row>
     <row r="524">
       <c r="A524" s="6">
-        <v>223</v>
+        <v>352</v>
       </c>
       <c r="C524" s="8">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="6">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B525" s="7">
-        <v>223</v>
+        <v>352</v>
       </c>
     </row>
     <row r="526">
@@ -4303,12 +4303,12 @@
         <v>352</v>
       </c>
       <c r="C526" s="8">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="6">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B527" s="7">
         <v>352</v>
@@ -4316,18 +4316,18 @@
     </row>
     <row r="528">
       <c r="A528" s="6">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C528" s="8">
-        <v>64</v>
+        <v>341</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="6">
-        <v>64</v>
+        <v>341</v>
       </c>
       <c r="B529" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="530">
@@ -4335,12 +4335,12 @@
         <v>354</v>
       </c>
       <c r="C530" s="8">
-        <v>341</v>
+        <v>19</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="6">
-        <v>341</v>
+        <v>19</v>
       </c>
       <c r="B531" s="7">
         <v>354</v>
@@ -4351,12 +4351,12 @@
         <v>354</v>
       </c>
       <c r="C532" s="8">
-        <v>19</v>
+        <v>355</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="6">
-        <v>19</v>
+        <v>355</v>
       </c>
       <c r="B533" s="7">
         <v>354</v>
@@ -4367,12 +4367,12 @@
         <v>354</v>
       </c>
       <c r="C534" s="8">
-        <v>355</v>
+        <v>135</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="6">
-        <v>355</v>
+        <v>135</v>
       </c>
       <c r="B535" s="7">
         <v>354</v>
@@ -4383,12 +4383,12 @@
         <v>354</v>
       </c>
       <c r="C536" s="8">
-        <v>135</v>
+        <v>164</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="6">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="B537" s="7">
         <v>354</v>
@@ -4396,34 +4396,34 @@
     </row>
     <row r="538">
       <c r="A538" s="6">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="C538" s="8">
-        <v>164</v>
+        <v>355</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="6">
-        <v>164</v>
+        <v>355</v>
       </c>
       <c r="B539" s="7">
-        <v>354</v>
+        <v>308</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="6">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="C540" s="8">
-        <v>355</v>
+        <v>164</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="6">
-        <v>355</v>
+        <v>164</v>
       </c>
       <c r="B541" s="7">
-        <v>308</v>
+        <v>166</v>
       </c>
     </row>
     <row r="542">
@@ -4431,12 +4431,12 @@
         <v>166</v>
       </c>
       <c r="C542" s="8">
-        <v>164</v>
+        <v>356</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="6">
-        <v>164</v>
+        <v>356</v>
       </c>
       <c r="B543" s="7">
         <v>166</v>
@@ -4447,12 +4447,12 @@
         <v>166</v>
       </c>
       <c r="C544" s="8">
-        <v>356</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="6">
-        <v>356</v>
+        <v>1</v>
       </c>
       <c r="B545" s="7">
         <v>166</v>
@@ -4460,18 +4460,18 @@
     </row>
     <row r="546">
       <c r="A546" s="6">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="C546" s="8">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="6">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="B547" s="7">
-        <v>166</v>
+        <v>137</v>
       </c>
     </row>
     <row r="548">
@@ -4479,12 +4479,12 @@
         <v>137</v>
       </c>
       <c r="C548" s="8">
-        <v>79</v>
+        <v>128</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="6">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="B549" s="7">
         <v>137</v>
@@ -4495,12 +4495,12 @@
         <v>137</v>
       </c>
       <c r="C550" s="8">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="6">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B551" s="7">
         <v>137</v>
@@ -4511,12 +4511,12 @@
         <v>137</v>
       </c>
       <c r="C552" s="8">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="6">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B553" s="7">
         <v>137</v>
@@ -4527,12 +4527,12 @@
         <v>137</v>
       </c>
       <c r="C554" s="8">
-        <v>115</v>
+        <v>58</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="6">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="B555" s="7">
         <v>137</v>
@@ -4543,12 +4543,12 @@
         <v>137</v>
       </c>
       <c r="C556" s="8">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="6">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="B557" s="7">
         <v>137</v>
@@ -4559,12 +4559,12 @@
         <v>137</v>
       </c>
       <c r="C558" s="8">
-        <v>99</v>
+        <v>357</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="6">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="B559" s="7">
         <v>137</v>
@@ -4572,23 +4572,23 @@
     </row>
     <row r="560">
       <c r="A560" s="6">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="C560" s="8">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="6">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B561" s="7">
-        <v>137</v>
+        <v>55</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="6">
-        <v>55</v>
+        <v>363</v>
       </c>
       <c r="C562" s="8">
         <v>362</v>
@@ -4599,12 +4599,12 @@
         <v>362</v>
       </c>
       <c r="B563" s="7">
-        <v>55</v>
+        <v>363</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="6">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C564" s="8">
         <v>362</v>
@@ -4615,23 +4615,23 @@
         <v>362</v>
       </c>
       <c r="B565" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="6">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C566" s="8">
-        <v>362</v>
+        <v>133</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="6">
-        <v>362</v>
+        <v>133</v>
       </c>
       <c r="B567" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="568">
@@ -4639,12 +4639,12 @@
         <v>367</v>
       </c>
       <c r="C568" s="8">
-        <v>133</v>
+        <v>368</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="6">
-        <v>133</v>
+        <v>368</v>
       </c>
       <c r="B569" s="7">
         <v>367</v>
@@ -4652,50 +4652,50 @@
     </row>
     <row r="570">
       <c r="A570" s="6">
-        <v>367</v>
+        <v>180</v>
       </c>
       <c r="C570" s="8">
-        <v>368</v>
+        <v>68</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="6">
-        <v>368</v>
+        <v>68</v>
       </c>
       <c r="B571" s="7">
-        <v>367</v>
+        <v>180</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="6">
-        <v>180</v>
+        <v>387</v>
       </c>
       <c r="C572" s="8">
-        <v>68</v>
+        <v>369</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="6">
-        <v>68</v>
+        <v>369</v>
       </c>
       <c r="B573" s="7">
-        <v>180</v>
+        <v>387</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="6">
-        <v>387</v>
+        <v>65</v>
       </c>
       <c r="C574" s="8">
-        <v>369</v>
+        <v>178</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="6">
-        <v>369</v>
+        <v>178</v>
       </c>
       <c r="B575" s="7">
-        <v>387</v>
+        <v>65</v>
       </c>
     </row>
     <row r="576">
@@ -4703,12 +4703,12 @@
         <v>65</v>
       </c>
       <c r="C576" s="8">
-        <v>178</v>
+        <v>68</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="6">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="B577" s="7">
         <v>65</v>
@@ -4716,34 +4716,34 @@
     </row>
     <row r="578">
       <c r="A578" s="6">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="C578" s="8">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="6">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B579" s="7">
-        <v>65</v>
+        <v>178</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="6">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="C580" s="8">
-        <v>66</v>
+        <v>400</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="6">
-        <v>66</v>
+        <v>400</v>
       </c>
       <c r="B581" s="7">
-        <v>178</v>
+        <v>65</v>
       </c>
     </row>
     <row r="582">
@@ -4751,12 +4751,12 @@
         <v>65</v>
       </c>
       <c r="C582" s="8">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="6">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B583" s="7">
         <v>65</v>
@@ -4767,12 +4767,12 @@
         <v>65</v>
       </c>
       <c r="C584" s="8">
-        <v>403</v>
+        <v>329</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="6">
-        <v>403</v>
+        <v>329</v>
       </c>
       <c r="B585" s="7">
         <v>65</v>
@@ -4780,23 +4780,23 @@
     </row>
     <row r="586">
       <c r="A586" s="6">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="C586" s="8">
-        <v>329</v>
+        <v>290</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="6">
-        <v>329</v>
+        <v>290</v>
       </c>
       <c r="B587" s="7">
-        <v>65</v>
+        <v>260</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="6">
-        <v>260</v>
+        <v>128</v>
       </c>
       <c r="C588" s="8">
         <v>290</v>
@@ -4807,44 +4807,44 @@
         <v>290</v>
       </c>
       <c r="B589" s="7">
-        <v>260</v>
+        <v>128</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="6">
-        <v>128</v>
+        <v>195</v>
       </c>
       <c r="C590" s="8">
-        <v>290</v>
+        <v>404</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="6">
-        <v>290</v>
+        <v>404</v>
       </c>
       <c r="B591" s="7">
-        <v>128</v>
+        <v>195</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="6">
-        <v>195</v>
+        <v>302</v>
       </c>
       <c r="C592" s="8">
-        <v>404</v>
+        <v>145</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="6">
-        <v>404</v>
+        <v>145</v>
       </c>
       <c r="B593" s="7">
-        <v>195</v>
+        <v>302</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="6">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="C594" s="8">
         <v>145</v>
@@ -4855,12 +4855,12 @@
         <v>145</v>
       </c>
       <c r="B595" s="7">
-        <v>302</v>
+        <v>405</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="6">
-        <v>405</v>
+        <v>207</v>
       </c>
       <c r="C596" s="8">
         <v>145</v>
@@ -4871,23 +4871,23 @@
         <v>145</v>
       </c>
       <c r="B597" s="7">
-        <v>405</v>
+        <v>207</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="6">
-        <v>207</v>
+        <v>410</v>
       </c>
       <c r="C598" s="8">
-        <v>145</v>
+        <v>306</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="6">
-        <v>145</v>
+        <v>306</v>
       </c>
       <c r="B599" s="7">
-        <v>207</v>
+        <v>410</v>
       </c>
     </row>
     <row r="600">
@@ -4895,12 +4895,12 @@
         <v>410</v>
       </c>
       <c r="C600" s="8">
-        <v>306</v>
+        <v>128</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="6">
-        <v>306</v>
+        <v>128</v>
       </c>
       <c r="B601" s="7">
         <v>410</v>
@@ -4908,23 +4908,23 @@
     </row>
     <row r="602">
       <c r="A602" s="6">
-        <v>410</v>
+        <v>337</v>
       </c>
       <c r="C602" s="8">
-        <v>128</v>
+        <v>290</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="6">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="B603" s="7">
-        <v>410</v>
+        <v>337</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="6">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C604" s="8">
         <v>290</v>
@@ -4935,12 +4935,12 @@
         <v>290</v>
       </c>
       <c r="B605" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="6">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C606" s="8">
         <v>290</v>
@@ -4951,12 +4951,12 @@
         <v>290</v>
       </c>
       <c r="B607" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="6">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="C608" s="8">
         <v>290</v>
@@ -4967,12 +4967,12 @@
         <v>290</v>
       </c>
       <c r="B609" s="7">
-        <v>340</v>
+        <v>357</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="6">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C610" s="8">
         <v>290</v>
@@ -4983,12 +4983,12 @@
         <v>290</v>
       </c>
       <c r="B611" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="6">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C612" s="8">
         <v>290</v>
@@ -4999,28 +4999,28 @@
         <v>290</v>
       </c>
       <c r="B613" s="7">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="6">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="C614" s="8">
-        <v>290</v>
+        <v>415</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="6">
-        <v>290</v>
+        <v>415</v>
       </c>
       <c r="B615" s="7">
-        <v>379</v>
+        <v>393</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="6">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="C616" s="8">
         <v>415</v>
@@ -5031,12 +5031,12 @@
         <v>415</v>
       </c>
       <c r="B617" s="7">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="6">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C618" s="8">
         <v>415</v>
@@ -5047,12 +5047,12 @@
         <v>415</v>
       </c>
       <c r="B619" s="7">
-        <v>406</v>
+        <v>416</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="6">
-        <v>416</v>
+        <v>218</v>
       </c>
       <c r="C620" s="8">
         <v>415</v>
@@ -5063,7 +5063,7 @@
         <v>415</v>
       </c>
       <c r="B621" s="7">
-        <v>416</v>
+        <v>218</v>
       </c>
     </row>
     <row r="622">
@@ -5071,12 +5071,12 @@
         <v>218</v>
       </c>
       <c r="C622" s="8">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="6">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B623" s="7">
         <v>218</v>
@@ -5084,23 +5084,23 @@
     </row>
     <row r="624">
       <c r="A624" s="6">
-        <v>218</v>
+        <v>421</v>
       </c>
       <c r="C624" s="8">
-        <v>419</v>
+        <v>306</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="6">
-        <v>419</v>
+        <v>306</v>
       </c>
       <c r="B625" s="7">
-        <v>218</v>
+        <v>421</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="6">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C626" s="8">
         <v>306</v>
@@ -5111,12 +5111,12 @@
         <v>306</v>
       </c>
       <c r="B627" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="6">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C628" s="8">
         <v>306</v>
@@ -5127,12 +5127,12 @@
         <v>306</v>
       </c>
       <c r="B629" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="6">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C630" s="8">
         <v>306</v>
@@ -5143,7 +5143,7 @@
         <v>306</v>
       </c>
       <c r="B631" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="632">
@@ -5151,12 +5151,12 @@
         <v>424</v>
       </c>
       <c r="C632" s="8">
-        <v>306</v>
+        <v>425</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="6">
-        <v>306</v>
+        <v>425</v>
       </c>
       <c r="B633" s="7">
         <v>424</v>
@@ -5164,7 +5164,7 @@
     </row>
     <row r="634">
       <c r="A634" s="6">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C634" s="8">
         <v>425</v>
@@ -5175,12 +5175,12 @@
         <v>425</v>
       </c>
       <c r="B635" s="7">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="6">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C636" s="8">
         <v>425</v>
@@ -5191,7 +5191,7 @@
         <v>425</v>
       </c>
       <c r="B637" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="638">
@@ -5199,12 +5199,12 @@
         <v>426</v>
       </c>
       <c r="C638" s="8">
-        <v>425</v>
+        <v>306</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="6">
-        <v>425</v>
+        <v>306</v>
       </c>
       <c r="B639" s="7">
         <v>426</v>
@@ -5215,12 +5215,12 @@
         <v>426</v>
       </c>
       <c r="C640" s="8">
-        <v>306</v>
+        <v>422</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="6">
-        <v>306</v>
+        <v>422</v>
       </c>
       <c r="B641" s="7">
         <v>426</v>
@@ -5228,18 +5228,18 @@
     </row>
     <row r="642">
       <c r="A642" s="6">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C642" s="8">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="6">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B643" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="644">
@@ -5247,12 +5247,12 @@
         <v>427</v>
       </c>
       <c r="C644" s="8">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" s="6">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B645" s="7">
         <v>427</v>
@@ -5260,66 +5260,66 @@
     </row>
     <row r="646">
       <c r="A646" s="6">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C646" s="8">
-        <v>422</v>
+        <v>224</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" s="6">
-        <v>422</v>
+        <v>224</v>
       </c>
       <c r="B647" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" s="6">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C648" s="8">
-        <v>224</v>
+        <v>135</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" s="6">
-        <v>224</v>
+        <v>135</v>
       </c>
       <c r="B649" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" s="6">
-        <v>429</v>
+        <v>63</v>
       </c>
       <c r="C650" s="8">
-        <v>17</v>
+        <v>437</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" s="6">
-        <v>17</v>
+        <v>437</v>
       </c>
       <c r="B651" s="7">
-        <v>429</v>
+        <v>63</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" s="6">
-        <v>430</v>
+        <v>63</v>
       </c>
       <c r="C652" s="8">
-        <v>135</v>
+        <v>438</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="6">
-        <v>135</v>
+        <v>438</v>
       </c>
       <c r="B653" s="7">
-        <v>430</v>
+        <v>63</v>
       </c>
     </row>
     <row r="654">
@@ -5327,12 +5327,12 @@
         <v>63</v>
       </c>
       <c r="C654" s="8">
-        <v>437</v>
+        <v>62</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" s="6">
-        <v>437</v>
+        <v>62</v>
       </c>
       <c r="B655" s="7">
         <v>63</v>
@@ -5340,162 +5340,162 @@
     </row>
     <row r="656">
       <c r="A656" s="6">
-        <v>63</v>
+        <v>425</v>
       </c>
       <c r="C656" s="8">
-        <v>438</v>
+        <v>306</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" s="6">
-        <v>438</v>
+        <v>306</v>
       </c>
       <c r="B657" s="7">
-        <v>63</v>
+        <v>425</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" s="6">
-        <v>63</v>
+        <v>444</v>
       </c>
       <c r="C658" s="8">
-        <v>62</v>
+        <v>392</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" s="6">
-        <v>62</v>
+        <v>392</v>
       </c>
       <c r="B659" s="7">
-        <v>63</v>
+        <v>444</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" s="6">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="C660" s="8">
-        <v>306</v>
+        <v>64</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" s="6">
-        <v>306</v>
+        <v>64</v>
       </c>
       <c r="B661" s="7">
-        <v>425</v>
+        <v>444</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" s="6">
-        <v>444</v>
+        <v>59</v>
       </c>
       <c r="C662" s="8">
-        <v>392</v>
+        <v>65</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" s="6">
-        <v>392</v>
+        <v>65</v>
       </c>
       <c r="B663" s="7">
-        <v>444</v>
+        <v>59</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" s="6">
-        <v>444</v>
+        <v>59</v>
       </c>
       <c r="C664" s="8">
-        <v>64</v>
+        <v>400</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="6">
-        <v>64</v>
+        <v>400</v>
       </c>
       <c r="B665" s="7">
-        <v>444</v>
+        <v>59</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" s="6">
-        <v>59</v>
+        <v>450</v>
       </c>
       <c r="C666" s="8">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" s="6">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B667" s="7">
-        <v>59</v>
+        <v>450</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" s="6">
-        <v>59</v>
+        <v>388</v>
       </c>
       <c r="C668" s="8">
-        <v>400</v>
+        <v>363</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" s="6">
-        <v>400</v>
+        <v>363</v>
       </c>
       <c r="B669" s="7">
-        <v>59</v>
+        <v>388</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" s="6">
-        <v>450</v>
+        <v>201</v>
       </c>
       <c r="C670" s="8">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="6">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B671" s="7">
-        <v>450</v>
+        <v>201</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" s="6">
-        <v>388</v>
+        <v>96</v>
       </c>
       <c r="C672" s="8">
-        <v>363</v>
+        <v>1</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" s="6">
-        <v>363</v>
+        <v>1</v>
       </c>
       <c r="B673" s="7">
-        <v>388</v>
+        <v>96</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" s="6">
-        <v>201</v>
+        <v>96</v>
       </c>
       <c r="C674" s="8">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" s="6">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B675" s="7">
-        <v>201</v>
+        <v>96</v>
       </c>
     </row>
     <row r="676">
@@ -5503,12 +5503,12 @@
         <v>96</v>
       </c>
       <c r="C676" s="8">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="6">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="B677" s="7">
         <v>96</v>
@@ -5516,82 +5516,82 @@
     </row>
     <row r="678">
       <c r="A678" s="6">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C678" s="8">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" s="6">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="B679" s="7">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" s="6">
-        <v>96</v>
+        <v>457</v>
       </c>
       <c r="C680" s="8">
-        <v>90</v>
+        <v>355</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" s="6">
-        <v>90</v>
+        <v>355</v>
       </c>
       <c r="B681" s="7">
-        <v>96</v>
+        <v>457</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" s="6">
-        <v>95</v>
+        <v>457</v>
       </c>
       <c r="C682" s="8">
-        <v>1</v>
+        <v>209</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" s="6">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="B683" s="7">
-        <v>95</v>
+        <v>457</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" s="6">
-        <v>457</v>
+        <v>394</v>
       </c>
       <c r="C684" s="8">
-        <v>355</v>
+        <v>63</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" s="6">
-        <v>355</v>
+        <v>63</v>
       </c>
       <c r="B685" s="7">
-        <v>457</v>
+        <v>394</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" s="6">
-        <v>457</v>
+        <v>394</v>
       </c>
       <c r="C686" s="8">
-        <v>209</v>
+        <v>438</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" s="6">
-        <v>209</v>
+        <v>438</v>
       </c>
       <c r="B687" s="7">
-        <v>457</v>
+        <v>394</v>
       </c>
     </row>
     <row r="688">
@@ -5599,12 +5599,12 @@
         <v>394</v>
       </c>
       <c r="C688" s="8">
-        <v>63</v>
+        <v>458</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="6">
-        <v>63</v>
+        <v>458</v>
       </c>
       <c r="B689" s="7">
         <v>394</v>
@@ -5612,50 +5612,50 @@
     </row>
     <row r="690">
       <c r="A690" s="6">
-        <v>394</v>
+        <v>286</v>
       </c>
       <c r="C690" s="8">
-        <v>438</v>
+        <v>458</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" s="6">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="B691" s="7">
-        <v>394</v>
+        <v>286</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" s="6">
-        <v>394</v>
+        <v>466</v>
       </c>
       <c r="C692" s="8">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" s="6">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B693" s="7">
-        <v>394</v>
+        <v>466</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" s="6">
-        <v>286</v>
+        <v>467</v>
       </c>
       <c r="C694" s="8">
-        <v>458</v>
+        <v>55</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" s="6">
-        <v>458</v>
+        <v>55</v>
       </c>
       <c r="B695" s="7">
-        <v>286</v>
+        <v>467</v>
       </c>
     </row>
     <row r="696">
@@ -5663,12 +5663,12 @@
         <v>466</v>
       </c>
       <c r="C696" s="8">
-        <v>467</v>
+        <v>178</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" s="6">
-        <v>467</v>
+        <v>178</v>
       </c>
       <c r="B697" s="7">
         <v>466</v>
@@ -5676,34 +5676,34 @@
     </row>
     <row r="698">
       <c r="A698" s="6">
-        <v>467</v>
+        <v>140</v>
       </c>
       <c r="C698" s="8">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" s="6">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B699" s="7">
-        <v>467</v>
+        <v>140</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" s="6">
-        <v>466</v>
+        <v>140</v>
       </c>
       <c r="C700" s="8">
-        <v>178</v>
+        <v>59</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" s="6">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="B701" s="7">
-        <v>466</v>
+        <v>140</v>
       </c>
     </row>
     <row r="702">
@@ -5711,12 +5711,12 @@
         <v>140</v>
       </c>
       <c r="C702" s="8">
-        <v>79</v>
+        <v>334</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" s="6">
-        <v>79</v>
+        <v>334</v>
       </c>
       <c r="B703" s="7">
         <v>140</v>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="704">
       <c r="A704" s="6">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="C704" s="8">
         <v>59</v>
@@ -5735,23 +5735,23 @@
         <v>59</v>
       </c>
       <c r="B705" s="7">
-        <v>140</v>
+        <v>232</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" s="6">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="C706" s="8">
-        <v>334</v>
+        <v>352</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" s="6">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B707" s="7">
-        <v>140</v>
+        <v>232</v>
       </c>
     </row>
     <row r="708">
@@ -5759,12 +5759,12 @@
         <v>232</v>
       </c>
       <c r="C708" s="8">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" s="6">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B709" s="7">
         <v>232</v>
@@ -5775,12 +5775,12 @@
         <v>232</v>
       </c>
       <c r="C710" s="8">
-        <v>352</v>
+        <v>313</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" s="6">
-        <v>352</v>
+        <v>313</v>
       </c>
       <c r="B711" s="7">
         <v>232</v>
@@ -5791,12 +5791,12 @@
         <v>232</v>
       </c>
       <c r="C712" s="8">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" s="6">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B713" s="7">
         <v>232</v>
@@ -5807,12 +5807,12 @@
         <v>232</v>
       </c>
       <c r="C714" s="8">
-        <v>313</v>
+        <v>145</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" s="6">
-        <v>313</v>
+        <v>145</v>
       </c>
       <c r="B715" s="7">
         <v>232</v>
@@ -5823,12 +5823,12 @@
         <v>232</v>
       </c>
       <c r="C716" s="8">
-        <v>90</v>
+        <v>57</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" s="6">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="B717" s="7">
         <v>232</v>
@@ -5836,66 +5836,66 @@
     </row>
     <row r="718">
       <c r="A718" s="6">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="C718" s="8">
-        <v>145</v>
+        <v>79</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" s="6">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="B719" s="7">
-        <v>232</v>
+        <v>472</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" s="6">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="C720" s="8">
-        <v>57</v>
+        <v>117</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" s="6">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="B721" s="7">
-        <v>232</v>
+        <v>472</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" s="6">
-        <v>472</v>
+        <v>231</v>
       </c>
       <c r="C722" s="8">
-        <v>79</v>
+        <v>2</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" s="6">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="B723" s="7">
-        <v>472</v>
+        <v>231</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" s="6">
-        <v>472</v>
+        <v>231</v>
       </c>
       <c r="C724" s="8">
-        <v>117</v>
+        <v>64</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" s="6">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="B725" s="7">
-        <v>472</v>
+        <v>231</v>
       </c>
     </row>
     <row r="726">
@@ -5903,12 +5903,12 @@
         <v>231</v>
       </c>
       <c r="C726" s="8">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" s="6">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="B727" s="7">
         <v>231</v>
@@ -5919,12 +5919,12 @@
         <v>231</v>
       </c>
       <c r="C728" s="8">
-        <v>64</v>
+        <v>126</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" s="6">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="B729" s="7">
         <v>231</v>
@@ -5935,12 +5935,12 @@
         <v>231</v>
       </c>
       <c r="C730" s="8">
-        <v>59</v>
+        <v>127</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" s="6">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="B731" s="7">
         <v>231</v>
@@ -5951,12 +5951,12 @@
         <v>231</v>
       </c>
       <c r="C732" s="8">
-        <v>126</v>
+        <v>313</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="6">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="B733" s="7">
         <v>231</v>
@@ -5967,12 +5967,12 @@
         <v>231</v>
       </c>
       <c r="C734" s="8">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" s="6">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B735" s="7">
         <v>231</v>
@@ -5980,66 +5980,66 @@
     </row>
     <row r="736">
       <c r="A736" s="6">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C736" s="8">
-        <v>313</v>
+        <v>473</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" s="6">
-        <v>313</v>
+        <v>473</v>
       </c>
       <c r="B737" s="7">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" s="6">
-        <v>231</v>
+        <v>473</v>
       </c>
       <c r="C738" s="8">
-        <v>135</v>
+        <v>474</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" s="6">
-        <v>135</v>
+        <v>474</v>
       </c>
       <c r="B739" s="7">
-        <v>231</v>
+        <v>473</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" s="6">
-        <v>221</v>
+        <v>60</v>
       </c>
       <c r="C740" s="8">
-        <v>473</v>
+        <v>119</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" s="6">
-        <v>473</v>
+        <v>119</v>
       </c>
       <c r="B741" s="7">
-        <v>221</v>
+        <v>60</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" s="6">
-        <v>473</v>
+        <v>60</v>
       </c>
       <c r="C742" s="8">
-        <v>474</v>
+        <v>90</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" s="6">
-        <v>474</v>
+        <v>90</v>
       </c>
       <c r="B743" s="7">
-        <v>473</v>
+        <v>60</v>
       </c>
     </row>
     <row r="744">
@@ -6047,12 +6047,12 @@
         <v>60</v>
       </c>
       <c r="C744" s="8">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" s="6">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B745" s="7">
         <v>60</v>
@@ -6063,12 +6063,12 @@
         <v>60</v>
       </c>
       <c r="C746" s="8">
-        <v>90</v>
+        <v>59</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" s="6">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="B747" s="7">
         <v>60</v>
@@ -6076,34 +6076,34 @@
     </row>
     <row r="748">
       <c r="A748" s="6">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C748" s="8">
-        <v>117</v>
+        <v>79</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" s="6">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="B749" s="7">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="6">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C750" s="8">
-        <v>59</v>
+        <v>145</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="6">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="B751" s="7">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="752">
@@ -6111,12 +6111,12 @@
         <v>90</v>
       </c>
       <c r="C752" s="8">
-        <v>79</v>
+        <v>389</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="6">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="B753" s="7">
         <v>90</v>
@@ -6127,12 +6127,12 @@
         <v>90</v>
       </c>
       <c r="C754" s="8">
-        <v>145</v>
+        <v>57</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="6">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="B755" s="7">
         <v>90</v>
@@ -6140,55 +6140,55 @@
     </row>
     <row r="756">
       <c r="A756" s="6">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C756" s="8">
-        <v>389</v>
+        <v>363</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" s="6">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="B757" s="7">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" s="6">
-        <v>90</v>
+        <v>362</v>
       </c>
       <c r="C758" s="8">
-        <v>57</v>
+        <v>476</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" s="6">
-        <v>57</v>
+        <v>476</v>
       </c>
       <c r="B759" s="7">
-        <v>90</v>
+        <v>362</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" s="6">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C760" s="8">
-        <v>363</v>
+        <v>478</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" s="6">
-        <v>363</v>
+        <v>478</v>
       </c>
       <c r="B761" s="7">
-        <v>104</v>
+        <v>119</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" s="6">
-        <v>362</v>
+        <v>224</v>
       </c>
       <c r="C762" s="8">
         <v>476</v>
@@ -6199,12 +6199,12 @@
         <v>476</v>
       </c>
       <c r="B763" s="7">
-        <v>362</v>
+        <v>224</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" s="6">
-        <v>119</v>
+        <v>224</v>
       </c>
       <c r="C764" s="8">
         <v>478</v>
@@ -6215,7 +6215,7 @@
         <v>478</v>
       </c>
       <c r="B765" s="7">
-        <v>119</v>
+        <v>224</v>
       </c>
     </row>
     <row r="766">
@@ -6223,12 +6223,12 @@
         <v>224</v>
       </c>
       <c r="C766" s="8">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" s="6">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B767" s="7">
         <v>224</v>
@@ -6236,66 +6236,66 @@
     </row>
     <row r="768">
       <c r="A768" s="6">
-        <v>224</v>
+        <v>482</v>
       </c>
       <c r="C768" s="8">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" s="6">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B769" s="7">
-        <v>224</v>
+        <v>482</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" s="6">
-        <v>224</v>
+        <v>482</v>
       </c>
       <c r="C770" s="8">
-        <v>479</v>
+        <v>194</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" s="6">
-        <v>479</v>
+        <v>194</v>
       </c>
       <c r="B771" s="7">
-        <v>224</v>
+        <v>482</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" s="6">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C772" s="8">
-        <v>481</v>
+        <v>194</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" s="6">
-        <v>481</v>
+        <v>194</v>
       </c>
       <c r="B773" s="7">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" s="6">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C774" s="8">
-        <v>194</v>
+        <v>483</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" s="6">
-        <v>194</v>
+        <v>483</v>
       </c>
       <c r="B775" s="7">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="776">
@@ -6303,12 +6303,12 @@
         <v>475</v>
       </c>
       <c r="C776" s="8">
-        <v>194</v>
+        <v>484</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="6">
-        <v>194</v>
+        <v>484</v>
       </c>
       <c r="B777" s="7">
         <v>475</v>
@@ -6316,66 +6316,66 @@
     </row>
     <row r="778">
       <c r="A778" s="6">
-        <v>475</v>
+        <v>372</v>
       </c>
       <c r="C778" s="8">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" s="6">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B779" s="7">
-        <v>475</v>
+        <v>372</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" s="6">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="C780" s="8">
-        <v>484</v>
+        <v>372</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" s="6">
-        <v>484</v>
+        <v>372</v>
       </c>
       <c r="B781" s="7">
-        <v>475</v>
+        <v>439</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" s="6">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="C782" s="8">
-        <v>481</v>
+        <v>58</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" s="6">
-        <v>481</v>
+        <v>58</v>
       </c>
       <c r="B783" s="7">
-        <v>372</v>
+        <v>79</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" s="6">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="C784" s="8">
-        <v>372</v>
+        <v>25</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" s="6">
-        <v>372</v>
+        <v>25</v>
       </c>
       <c r="B785" s="7">
-        <v>439</v>
+        <v>79</v>
       </c>
     </row>
     <row r="786">
@@ -6383,12 +6383,12 @@
         <v>79</v>
       </c>
       <c r="C786" s="8">
-        <v>58</v>
+        <v>438</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" s="6">
-        <v>58</v>
+        <v>438</v>
       </c>
       <c r="B787" s="7">
         <v>79</v>
@@ -6396,66 +6396,66 @@
     </row>
     <row r="788">
       <c r="A788" s="6">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="C788" s="8">
-        <v>25</v>
+        <v>179</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" s="6">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="B789" s="7">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" s="6">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="C790" s="8">
-        <v>438</v>
+        <v>64</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" s="6">
-        <v>438</v>
+        <v>64</v>
       </c>
       <c r="B791" s="7">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C792" s="8">
-        <v>179</v>
+        <v>79</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" s="6">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="B793" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C794" s="8">
-        <v>64</v>
+        <v>19</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" s="6">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="B795" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="796">
@@ -6463,12 +6463,12 @@
         <v>4</v>
       </c>
       <c r="C796" s="8">
-        <v>79</v>
+        <v>20</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" s="6">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="B797" s="7">
         <v>4</v>
@@ -6479,12 +6479,12 @@
         <v>4</v>
       </c>
       <c r="C798" s="8">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" s="6">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="B799" s="7">
         <v>4</v>
@@ -6492,114 +6492,114 @@
     </row>
     <row r="800">
       <c r="A800" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C800" s="8">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="6">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="B801" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" s="6">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="C802" s="8">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" s="6">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B803" s="7">
-        <v>4</v>
+        <v>71</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" s="6">
-        <v>10</v>
+        <v>232</v>
       </c>
       <c r="C804" s="8">
-        <v>65</v>
+        <v>135</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" s="6">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="B805" s="7">
-        <v>10</v>
+        <v>232</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" s="6">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="C806" s="8">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" s="6">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="B807" s="7">
-        <v>71</v>
+        <v>250</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" s="6">
-        <v>232</v>
+        <v>49</v>
       </c>
       <c r="C808" s="8">
-        <v>135</v>
+        <v>358</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" s="6">
-        <v>135</v>
+        <v>358</v>
       </c>
       <c r="B809" s="7">
-        <v>232</v>
+        <v>49</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" s="6">
-        <v>250</v>
+        <v>322</v>
       </c>
       <c r="C810" s="8">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" s="6">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="B811" s="7">
-        <v>250</v>
+        <v>322</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" s="6">
-        <v>49</v>
+        <v>322</v>
       </c>
       <c r="C812" s="8">
-        <v>358</v>
+        <v>96</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" s="6">
-        <v>358</v>
+        <v>96</v>
       </c>
       <c r="B813" s="7">
-        <v>49</v>
+        <v>322</v>
       </c>
     </row>
     <row r="814">
@@ -6607,12 +6607,12 @@
         <v>322</v>
       </c>
       <c r="C814" s="8">
-        <v>47</v>
+        <v>95</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" s="6">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="B815" s="7">
         <v>322</v>
@@ -6620,130 +6620,130 @@
     </row>
     <row r="816">
       <c r="A816" s="6">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C816" s="8">
-        <v>96</v>
+        <v>47</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" s="6">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="B817" s="7">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" s="6">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C818" s="8">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" s="6">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B819" s="7">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" s="6">
-        <v>321</v>
+        <v>53</v>
       </c>
       <c r="C820" s="8">
-        <v>47</v>
+        <v>214</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" s="6">
-        <v>47</v>
+        <v>214</v>
       </c>
       <c r="B821" s="7">
-        <v>321</v>
+        <v>53</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" s="6">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="C822" s="8">
-        <v>96</v>
+        <v>389</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" s="6">
-        <v>96</v>
+        <v>389</v>
       </c>
       <c r="B823" s="7">
-        <v>321</v>
+        <v>347</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" s="6">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C824" s="8">
-        <v>214</v>
+        <v>106</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" s="6">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="B825" s="7">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" s="6">
-        <v>347</v>
+        <v>46</v>
       </c>
       <c r="C826" s="8">
-        <v>389</v>
+        <v>125</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" s="6">
-        <v>389</v>
+        <v>125</v>
       </c>
       <c r="B827" s="7">
-        <v>347</v>
+        <v>46</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" s="6">
-        <v>46</v>
+        <v>360</v>
       </c>
       <c r="C828" s="8">
-        <v>106</v>
+        <v>483</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" s="6">
-        <v>106</v>
+        <v>483</v>
       </c>
       <c r="B829" s="7">
-        <v>46</v>
+        <v>360</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" s="6">
-        <v>46</v>
+        <v>360</v>
       </c>
       <c r="C830" s="8">
-        <v>125</v>
+        <v>58</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" s="6">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="B831" s="7">
-        <v>46</v>
+        <v>360</v>
       </c>
     </row>
     <row r="832">
@@ -6751,12 +6751,12 @@
         <v>360</v>
       </c>
       <c r="C832" s="8">
-        <v>483</v>
+        <v>79</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" s="6">
-        <v>483</v>
+        <v>79</v>
       </c>
       <c r="B833" s="7">
         <v>360</v>
@@ -6767,12 +6767,12 @@
         <v>360</v>
       </c>
       <c r="C834" s="8">
-        <v>58</v>
+        <v>367</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" s="6">
-        <v>58</v>
+        <v>367</v>
       </c>
       <c r="B835" s="7">
         <v>360</v>
@@ -6780,34 +6780,34 @@
     </row>
     <row r="836">
       <c r="A836" s="6">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C836" s="8">
-        <v>79</v>
+        <v>130</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" s="6">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="B837" s="7">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" s="6">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C838" s="8">
-        <v>367</v>
+        <v>483</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" s="6">
-        <v>367</v>
+        <v>483</v>
       </c>
       <c r="B839" s="7">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="840">
@@ -6815,12 +6815,12 @@
         <v>368</v>
       </c>
       <c r="C840" s="8">
-        <v>1</v>
+        <v>106</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" s="6">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="B841" s="7">
         <v>368</v>
@@ -6831,12 +6831,12 @@
         <v>368</v>
       </c>
       <c r="C842" s="8">
-        <v>130</v>
+        <v>49</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" s="6">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="B843" s="7">
         <v>368</v>
@@ -6847,12 +6847,12 @@
         <v>368</v>
       </c>
       <c r="C844" s="8">
-        <v>483</v>
+        <v>69</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" s="6">
-        <v>483</v>
+        <v>69</v>
       </c>
       <c r="B845" s="7">
         <v>368</v>
@@ -6860,98 +6860,2066 @@
     </row>
     <row r="846">
       <c r="A846" s="6">
-        <v>368</v>
+        <v>140</v>
       </c>
       <c r="C846" s="8">
-        <v>106</v>
+        <v>322</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" s="6">
-        <v>106</v>
+        <v>322</v>
       </c>
       <c r="B847" s="7">
-        <v>368</v>
+        <v>140</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" s="6">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C848" s="8">
-        <v>49</v>
+        <v>478</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" s="6">
-        <v>49</v>
+        <v>478</v>
       </c>
       <c r="B849" s="7">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" s="6">
-        <v>368</v>
+        <v>487</v>
       </c>
       <c r="C850" s="8">
-        <v>69</v>
+        <v>389</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" s="6">
-        <v>69</v>
+        <v>389</v>
       </c>
       <c r="B851" s="7">
-        <v>368</v>
+        <v>487</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" s="6">
-        <v>140</v>
+        <v>366</v>
       </c>
       <c r="C852" s="8">
-        <v>322</v>
+        <v>19</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" s="6">
-        <v>322</v>
+        <v>19</v>
       </c>
       <c r="B853" s="7">
-        <v>140</v>
+        <v>366</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" s="6">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C854" s="8">
-        <v>478</v>
+        <v>1</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" s="6">
-        <v>478</v>
+        <v>1</v>
       </c>
       <c r="B855" s="7">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" s="6">
-        <v>487</v>
+        <v>97</v>
       </c>
       <c r="C856" s="8">
-        <v>389</v>
+        <v>2</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" s="6">
+        <v>2</v>
+      </c>
+      <c r="B857" s="7">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="6">
+        <v>97</v>
+      </c>
+      <c r="C858" s="8">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="6">
+        <v>178</v>
+      </c>
+      <c r="B859" s="7">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="6">
+        <v>488</v>
+      </c>
+      <c r="C860" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="6">
+        <v>290</v>
+      </c>
+      <c r="B861" s="7">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="6">
+        <v>183</v>
+      </c>
+      <c r="C862" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="6">
+        <v>64</v>
+      </c>
+      <c r="B863" s="7">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="6">
+        <v>183</v>
+      </c>
+      <c r="C864" s="8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="6">
+        <v>65</v>
+      </c>
+      <c r="B865" s="7">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="6">
+        <v>64</v>
+      </c>
+      <c r="C866" s="8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="6">
+        <v>68</v>
+      </c>
+      <c r="B867" s="7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="6">
+        <v>277</v>
+      </c>
+      <c r="C868" s="8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="6">
+        <v>117</v>
+      </c>
+      <c r="B869" s="7">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="6">
+        <v>194</v>
+      </c>
+      <c r="C870" s="8">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="6">
+        <v>483</v>
+      </c>
+      <c r="B871" s="7">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="6">
+        <v>429</v>
+      </c>
+      <c r="C872" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="6">
+        <v>1</v>
+      </c>
+      <c r="B873" s="7">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="6">
+        <v>429</v>
+      </c>
+      <c r="C874" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="6">
+        <v>79</v>
+      </c>
+      <c r="B875" s="7">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="6">
+        <v>429</v>
+      </c>
+      <c r="C876" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="6">
+        <v>59</v>
+      </c>
+      <c r="B877" s="7">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="6">
+        <v>489</v>
+      </c>
+      <c r="C878" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="6">
+        <v>59</v>
+      </c>
+      <c r="B879" s="7">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="6">
+        <v>489</v>
+      </c>
+      <c r="C880" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="6">
+        <v>1</v>
+      </c>
+      <c r="B881" s="7">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="6">
+        <v>489</v>
+      </c>
+      <c r="C882" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="6">
+        <v>79</v>
+      </c>
+      <c r="B883" s="7">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="6">
+        <v>489</v>
+      </c>
+      <c r="C884" s="8">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="6">
+        <v>224</v>
+      </c>
+      <c r="B885" s="7">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="6">
+        <v>489</v>
+      </c>
+      <c r="C886" s="8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="6">
+        <v>117</v>
+      </c>
+      <c r="B887" s="7">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="6">
+        <v>373</v>
+      </c>
+      <c r="C888" s="8">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="6">
+        <v>308</v>
+      </c>
+      <c r="B889" s="7">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="6">
+        <v>145</v>
+      </c>
+      <c r="C890" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="6">
+        <v>79</v>
+      </c>
+      <c r="B891" s="7">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="6">
+        <v>145</v>
+      </c>
+      <c r="C892" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="6">
+        <v>19</v>
+      </c>
+      <c r="B893" s="7">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="6">
+        <v>145</v>
+      </c>
+      <c r="C894" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="6">
+        <v>290</v>
+      </c>
+      <c r="B895" s="7">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="6">
+        <v>145</v>
+      </c>
+      <c r="C896" s="8">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="6">
+        <v>102</v>
+      </c>
+      <c r="B897" s="7">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="6">
+        <v>155</v>
+      </c>
+      <c r="C898" s="8">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="6">
+        <v>194</v>
+      </c>
+      <c r="B899" s="7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="6">
+        <v>155</v>
+      </c>
+      <c r="C900" s="8">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="6">
+        <v>176</v>
+      </c>
+      <c r="B901" s="7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="6">
+        <v>236</v>
+      </c>
+      <c r="C902" s="8">
         <v>389</v>
       </c>
-      <c r="B857" s="7">
-        <v>487</v>
+    </row>
+    <row r="903">
+      <c r="A903" s="6">
+        <v>389</v>
+      </c>
+      <c r="B903" s="7">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="6">
+        <v>236</v>
+      </c>
+      <c r="C904" s="8">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="6">
+        <v>96</v>
+      </c>
+      <c r="B905" s="7">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="6">
+        <v>62</v>
+      </c>
+      <c r="C906" s="8">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="6">
+        <v>342</v>
+      </c>
+      <c r="B907" s="7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="6">
+        <v>62</v>
+      </c>
+      <c r="C908" s="8">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="6">
+        <v>63</v>
+      </c>
+      <c r="B909" s="7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="6">
+        <v>394</v>
+      </c>
+      <c r="C910" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="6">
+        <v>10</v>
+      </c>
+      <c r="B911" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="6">
+        <v>394</v>
+      </c>
+      <c r="C912" s="8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="6">
+        <v>62</v>
+      </c>
+      <c r="B913" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="6">
+        <v>394</v>
+      </c>
+      <c r="C914" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="6">
+        <v>59</v>
+      </c>
+      <c r="B915" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="6">
+        <v>394</v>
+      </c>
+      <c r="C916" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="6">
+        <v>58</v>
+      </c>
+      <c r="B917" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="6">
+        <v>394</v>
+      </c>
+      <c r="C918" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="6">
+        <v>22</v>
+      </c>
+      <c r="B919" s="7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="6">
+        <v>251</v>
+      </c>
+      <c r="C920" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="6">
+        <v>64</v>
+      </c>
+      <c r="B921" s="7">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="6">
+        <v>251</v>
+      </c>
+      <c r="C922" s="8">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="6">
+        <v>403</v>
+      </c>
+      <c r="B923" s="7">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="6">
+        <v>493</v>
+      </c>
+      <c r="C924" s="8">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="6">
+        <v>196</v>
+      </c>
+      <c r="B925" s="7">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="6">
+        <v>499</v>
+      </c>
+      <c r="C926" s="8">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="6">
+        <v>382</v>
+      </c>
+      <c r="B927" s="7">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="6">
+        <v>500</v>
+      </c>
+      <c r="C928" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="6">
+        <v>19</v>
+      </c>
+      <c r="B929" s="7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="6">
+        <v>500</v>
+      </c>
+      <c r="C930" s="8">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="6">
+        <v>226</v>
+      </c>
+      <c r="B931" s="7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="6">
+        <v>500</v>
+      </c>
+      <c r="C932" s="8">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="6">
+        <v>234</v>
+      </c>
+      <c r="B933" s="7">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="6">
+        <v>506</v>
+      </c>
+      <c r="C934" s="8">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="6">
+        <v>428</v>
+      </c>
+      <c r="B935" s="7">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="6">
+        <v>508</v>
+      </c>
+      <c r="C936" s="8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="6">
+        <v>117</v>
+      </c>
+      <c r="B937" s="7">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="6">
+        <v>278</v>
+      </c>
+      <c r="C938" s="8">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="6">
+        <v>508</v>
+      </c>
+      <c r="B939" s="7">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="6">
+        <v>512</v>
+      </c>
+      <c r="C940" s="8">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="6">
+        <v>392</v>
+      </c>
+      <c r="B941" s="7">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="6">
+        <v>512</v>
+      </c>
+      <c r="C942" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="6">
+        <v>64</v>
+      </c>
+      <c r="B943" s="7">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="6">
+        <v>512</v>
+      </c>
+      <c r="C944" s="8">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="6">
+        <v>320</v>
+      </c>
+      <c r="B945" s="7">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="6">
+        <v>449</v>
+      </c>
+      <c r="C946" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="6">
+        <v>444</v>
+      </c>
+      <c r="B947" s="7">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="6">
+        <v>449</v>
+      </c>
+      <c r="C948" s="8">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="6">
+        <v>120</v>
+      </c>
+      <c r="B949" s="7">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="6">
+        <v>513</v>
+      </c>
+      <c r="C950" s="8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="6">
+        <v>65</v>
+      </c>
+      <c r="B951" s="7">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="6">
+        <v>513</v>
+      </c>
+      <c r="C952" s="8">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="6">
+        <v>285</v>
+      </c>
+      <c r="B953" s="7">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="6">
+        <v>513</v>
+      </c>
+      <c r="C954" s="8">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="6">
+        <v>512</v>
+      </c>
+      <c r="B955" s="7">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="6">
+        <v>513</v>
+      </c>
+      <c r="C956" s="8">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="6">
+        <v>444</v>
+      </c>
+      <c r="B957" s="7">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="6">
+        <v>514</v>
+      </c>
+      <c r="C958" s="8">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="6">
+        <v>286</v>
+      </c>
+      <c r="B959" s="7">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="6">
+        <v>514</v>
+      </c>
+      <c r="C960" s="8">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="6">
+        <v>512</v>
+      </c>
+      <c r="B961" s="7">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="6">
+        <v>515</v>
+      </c>
+      <c r="C962" s="8">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="6">
+        <v>282</v>
+      </c>
+      <c r="B963" s="7">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="6">
+        <v>515</v>
+      </c>
+      <c r="C964" s="8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="6">
+        <v>66</v>
+      </c>
+      <c r="B965" s="7">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="6">
+        <v>445</v>
+      </c>
+      <c r="C966" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="6">
+        <v>64</v>
+      </c>
+      <c r="B967" s="7">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="6">
+        <v>354</v>
+      </c>
+      <c r="C968" s="8">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="6">
+        <v>516</v>
+      </c>
+      <c r="B969" s="7">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="6">
+        <v>507</v>
+      </c>
+      <c r="C970" s="8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="6">
+        <v>27</v>
+      </c>
+      <c r="B971" s="7">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="6">
+        <v>507</v>
+      </c>
+      <c r="C972" s="8">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="6">
+        <v>117</v>
+      </c>
+      <c r="B973" s="7">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="6">
+        <v>517</v>
+      </c>
+      <c r="C974" s="8">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="6">
+        <v>266</v>
+      </c>
+      <c r="B975" s="7">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="6">
+        <v>517</v>
+      </c>
+      <c r="C976" s="8">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="6">
+        <v>267</v>
+      </c>
+      <c r="B977" s="7">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="6">
+        <v>517</v>
+      </c>
+      <c r="C978" s="8">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="6">
+        <v>269</v>
+      </c>
+      <c r="B979" s="7">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="6">
+        <v>517</v>
+      </c>
+      <c r="C980" s="8">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="6">
+        <v>268</v>
+      </c>
+      <c r="B981" s="7">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="6">
+        <v>518</v>
+      </c>
+      <c r="C982" s="8">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="6">
+        <v>261</v>
+      </c>
+      <c r="B983" s="7">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="6">
+        <v>267</v>
+      </c>
+      <c r="C984" s="8">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="6">
+        <v>261</v>
+      </c>
+      <c r="B985" s="7">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="6">
+        <v>462</v>
+      </c>
+      <c r="C986" s="8">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="6">
+        <v>145</v>
+      </c>
+      <c r="B987" s="7">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="6">
+        <v>299</v>
+      </c>
+      <c r="C988" s="8">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="6">
+        <v>55</v>
+      </c>
+      <c r="B989" s="7">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="6">
+        <v>299</v>
+      </c>
+      <c r="C990" s="8">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="6">
+        <v>466</v>
+      </c>
+      <c r="B991" s="7">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="6">
+        <v>247</v>
+      </c>
+      <c r="C992" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="6">
+        <v>21</v>
+      </c>
+      <c r="B993" s="7">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="6">
+        <v>474</v>
+      </c>
+      <c r="C994" s="8">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="6">
+        <v>519</v>
+      </c>
+      <c r="B995" s="7">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="6">
+        <v>519</v>
+      </c>
+      <c r="C996" s="8">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="6">
+        <v>112</v>
+      </c>
+      <c r="B997" s="7">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="6">
+        <v>519</v>
+      </c>
+      <c r="C998" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="6">
+        <v>58</v>
+      </c>
+      <c r="B999" s="7">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="6">
+        <v>220</v>
+      </c>
+      <c r="C1000" s="8">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="6">
+        <v>382</v>
+      </c>
+      <c r="B1001" s="7">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="6">
+        <v>221</v>
+      </c>
+      <c r="C1002" s="8">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="6">
+        <v>382</v>
+      </c>
+      <c r="B1003" s="7">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="6">
+        <v>520</v>
+      </c>
+      <c r="C1004" s="8">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="6">
+        <v>474</v>
+      </c>
+      <c r="B1005" s="7">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="6">
+        <v>520</v>
+      </c>
+      <c r="C1006" s="8">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="6">
+        <v>106</v>
+      </c>
+      <c r="B1007" s="7">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="6">
+        <v>520</v>
+      </c>
+      <c r="C1008" s="8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="6">
+        <v>49</v>
+      </c>
+      <c r="B1009" s="7">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="6">
+        <v>499</v>
+      </c>
+      <c r="C1010" s="8">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="6">
+        <v>520</v>
+      </c>
+      <c r="B1011" s="7">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="6">
+        <v>26</v>
+      </c>
+      <c r="C1012" s="8">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="6">
+        <v>266</v>
+      </c>
+      <c r="B1013" s="7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="6">
+        <v>26</v>
+      </c>
+      <c r="C1014" s="8">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="6">
+        <v>262</v>
+      </c>
+      <c r="B1015" s="7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="6">
+        <v>26</v>
+      </c>
+      <c r="C1016" s="8">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="6">
+        <v>323</v>
+      </c>
+      <c r="B1017" s="7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="6">
+        <v>36</v>
+      </c>
+      <c r="C1018" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="6">
+        <v>64</v>
+      </c>
+      <c r="B1019" s="7">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="6">
+        <v>102</v>
+      </c>
+      <c r="C1020" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1021" s="7">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="6">
+        <v>102</v>
+      </c>
+      <c r="C1022" s="8">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="6">
+        <v>125</v>
+      </c>
+      <c r="B1023" s="7">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="6">
+        <v>102</v>
+      </c>
+      <c r="C1024" s="8">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="6">
+        <v>106</v>
+      </c>
+      <c r="B1025" s="7">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="6">
+        <v>102</v>
+      </c>
+      <c r="C1026" s="8">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="6">
+        <v>113</v>
+      </c>
+      <c r="B1027" s="7">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="6">
+        <v>102</v>
+      </c>
+      <c r="C1028" s="8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="6">
+        <v>49</v>
+      </c>
+      <c r="B1029" s="7">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="6">
+        <v>102</v>
+      </c>
+      <c r="C1030" s="8">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="6">
+        <v>138</v>
+      </c>
+      <c r="B1031" s="7">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="6">
+        <v>165</v>
+      </c>
+      <c r="C1032" s="8">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="6">
+        <v>469</v>
+      </c>
+      <c r="B1033" s="7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="6">
+        <v>165</v>
+      </c>
+      <c r="C1034" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="6">
+        <v>1</v>
+      </c>
+      <c r="B1035" s="7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="6">
+        <v>165</v>
+      </c>
+      <c r="C1036" s="8">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="6">
+        <v>164</v>
+      </c>
+      <c r="B1037" s="7">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="6">
+        <v>256</v>
+      </c>
+      <c r="C1038" s="8">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="6">
+        <v>352</v>
+      </c>
+      <c r="B1039" s="7">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="6">
+        <v>256</v>
+      </c>
+      <c r="C1040" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="6">
+        <v>59</v>
+      </c>
+      <c r="B1041" s="7">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="6">
+        <v>256</v>
+      </c>
+      <c r="C1042" s="8">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="6">
+        <v>521</v>
+      </c>
+      <c r="B1043" s="7">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="6">
+        <v>521</v>
+      </c>
+      <c r="C1044" s="8">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="6">
+        <v>144</v>
+      </c>
+      <c r="B1045" s="7">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="6">
+        <v>521</v>
+      </c>
+      <c r="C1046" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="6">
+        <v>64</v>
+      </c>
+      <c r="B1047" s="7">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="6">
+        <v>521</v>
+      </c>
+      <c r="C1048" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="6">
+        <v>59</v>
+      </c>
+      <c r="B1049" s="7">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="6">
+        <v>523</v>
+      </c>
+      <c r="C1050" s="8">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="6">
+        <v>171</v>
+      </c>
+      <c r="B1051" s="7">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="6">
+        <v>523</v>
+      </c>
+      <c r="C1052" s="8">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="6">
+        <v>505</v>
+      </c>
+      <c r="B1053" s="7">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="6">
+        <v>523</v>
+      </c>
+      <c r="C1054" s="8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="6">
+        <v>90</v>
+      </c>
+      <c r="B1055" s="7">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="6">
+        <v>112</v>
+      </c>
+      <c r="C1056" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="6">
+        <v>59</v>
+      </c>
+      <c r="B1057" s="7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="6">
+        <v>112</v>
+      </c>
+      <c r="C1058" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="6">
+        <v>58</v>
+      </c>
+      <c r="B1059" s="7">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="6">
+        <v>114</v>
+      </c>
+      <c r="C1060" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="6">
+        <v>59</v>
+      </c>
+      <c r="B1061" s="7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="6">
+        <v>115</v>
+      </c>
+      <c r="C1062" s="8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="6">
+        <v>73</v>
+      </c>
+      <c r="B1063" s="7">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="6">
+        <v>114</v>
+      </c>
+      <c r="C1064" s="8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="6">
+        <v>73</v>
+      </c>
+      <c r="B1065" s="7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="6">
+        <v>118</v>
+      </c>
+      <c r="C1066" s="8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="6">
+        <v>27</v>
+      </c>
+      <c r="B1067" s="7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="6">
+        <v>119</v>
+      </c>
+      <c r="C1068" s="8">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="6">
+        <v>171</v>
+      </c>
+      <c r="B1069" s="7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="6">
+        <v>128</v>
+      </c>
+      <c r="C1070" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="6">
+        <v>58</v>
+      </c>
+      <c r="B1071" s="7">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="6">
+        <v>128</v>
+      </c>
+      <c r="C1072" s="8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="6">
+        <v>400</v>
+      </c>
+      <c r="B1073" s="7">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="6">
+        <v>129</v>
+      </c>
+      <c r="C1074" s="8">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="6">
+        <v>132</v>
+      </c>
+      <c r="B1075" s="7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="6">
+        <v>129</v>
+      </c>
+      <c r="C1076" s="8">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="6">
+        <v>130</v>
+      </c>
+      <c r="B1077" s="7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="6">
+        <v>129</v>
+      </c>
+      <c r="C1078" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="6">
+        <v>64</v>
+      </c>
+      <c r="B1079" s="7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="6">
+        <v>129</v>
+      </c>
+      <c r="C1080" s="8">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="6">
+        <v>352</v>
+      </c>
+      <c r="B1081" s="7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="6">
+        <v>130</v>
+      </c>
+      <c r="C1082" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="6">
+        <v>59</v>
+      </c>
+      <c r="B1083" s="7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="6">
+        <v>131</v>
+      </c>
+      <c r="C1084" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="6">
+        <v>79</v>
+      </c>
+      <c r="B1085" s="7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="6">
+        <v>131</v>
+      </c>
+      <c r="C1086" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="6">
+        <v>58</v>
+      </c>
+      <c r="B1087" s="7">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="6">
+        <v>132</v>
+      </c>
+      <c r="C1088" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="6">
+        <v>59</v>
+      </c>
+      <c r="B1089" s="7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="6">
+        <v>149</v>
+      </c>
+      <c r="C1090" s="8">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="6">
+        <v>519</v>
+      </c>
+      <c r="B1091" s="7">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="6">
+        <v>510</v>
+      </c>
+      <c r="C1092" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="6">
+        <v>10</v>
+      </c>
+      <c r="B1093" s="7">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="6">
+        <v>502</v>
+      </c>
+      <c r="C1094" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="6">
+        <v>290</v>
+      </c>
+      <c r="B1095" s="7">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="6">
+        <v>498</v>
+      </c>
+      <c r="C1096" s="8">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="6">
+        <v>95</v>
+      </c>
+      <c r="B1097" s="7">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="6">
+        <v>496</v>
+      </c>
+      <c r="C1098" s="8">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="6">
+        <v>290</v>
+      </c>
+      <c r="B1099" s="7">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="6">
+        <v>491</v>
+      </c>
+      <c r="C1100" s="8">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="6">
+        <v>369</v>
+      </c>
+      <c r="B1101" s="7">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="6">
+        <v>490</v>
+      </c>
+      <c r="C1102" s="8">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="6">
+        <v>519</v>
+      </c>
+      <c r="B1103" s="7">
+        <v>490</v>
       </c>
     </row>
   </sheetData>

--- a/raw/Concepthierarchy.xlsx
+++ b/raw/Concepthierarchy.xlsx
@@ -12554,6 +12554,38 @@
         <v>581</v>
       </c>
     </row>
+    <row r="1558">
+      <c r="A1558" s="6">
+        <v>101</v>
+      </c>
+      <c r="C1558" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1559" s="7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="6">
+        <v>101</v>
+      </c>
+      <c r="C1560" s="8">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="6">
+        <v>483</v>
+      </c>
+      <c r="B1561" s="7">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/raw/Concepthierarchy.xlsx
+++ b/raw/Concepthierarchy.xlsx
@@ -12586,6 +12586,1030 @@
         <v>101</v>
       </c>
     </row>
+    <row r="1562">
+      <c r="A1562" s="6">
+        <v>19</v>
+      </c>
+      <c r="C1562" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="6">
+        <v>14</v>
+      </c>
+      <c r="B1563" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="6">
+        <v>19</v>
+      </c>
+      <c r="C1564" s="8">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="6">
+        <v>537</v>
+      </c>
+      <c r="B1565" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="6">
+        <v>39</v>
+      </c>
+      <c r="C1566" s="8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="6">
+        <v>400</v>
+      </c>
+      <c r="B1567" s="7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="6">
+        <v>39</v>
+      </c>
+      <c r="C1568" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="6">
+        <v>59</v>
+      </c>
+      <c r="B1569" s="7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="6">
+        <v>39</v>
+      </c>
+      <c r="C1570" s="8">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="6">
+        <v>284</v>
+      </c>
+      <c r="B1571" s="7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="6">
+        <v>40</v>
+      </c>
+      <c r="C1572" s="8">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="6">
+        <v>400</v>
+      </c>
+      <c r="B1573" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="6">
+        <v>40</v>
+      </c>
+      <c r="C1574" s="8">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="6">
+        <v>284</v>
+      </c>
+      <c r="B1575" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="6">
+        <v>51</v>
+      </c>
+      <c r="C1576" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1577" s="7">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="6">
+        <v>52</v>
+      </c>
+      <c r="C1578" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1579" s="7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="6">
+        <v>82</v>
+      </c>
+      <c r="C1580" s="8">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="6">
+        <v>372</v>
+      </c>
+      <c r="B1581" s="7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="6">
+        <v>82</v>
+      </c>
+      <c r="C1582" s="8">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="6">
+        <v>386</v>
+      </c>
+      <c r="B1583" s="7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="6">
+        <v>238</v>
+      </c>
+      <c r="C1584" s="8">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="6">
+        <v>284</v>
+      </c>
+      <c r="B1585" s="7">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="6">
+        <v>238</v>
+      </c>
+      <c r="C1586" s="8">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="6">
+        <v>536</v>
+      </c>
+      <c r="B1587" s="7">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="6">
+        <v>287</v>
+      </c>
+      <c r="C1588" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1589" s="7">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="6">
+        <v>287</v>
+      </c>
+      <c r="C1590" s="8">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="6">
+        <v>241</v>
+      </c>
+      <c r="B1591" s="7">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="6">
+        <v>384</v>
+      </c>
+      <c r="C1592" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1593" s="7">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="6">
+        <v>390</v>
+      </c>
+      <c r="C1594" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1595" s="7">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="6">
+        <v>461</v>
+      </c>
+      <c r="C1596" s="8">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="6">
+        <v>536</v>
+      </c>
+      <c r="B1597" s="7">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="6">
+        <v>461</v>
+      </c>
+      <c r="C1598" s="8">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="6">
+        <v>314</v>
+      </c>
+      <c r="B1599" s="7">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="6">
+        <v>461</v>
+      </c>
+      <c r="C1600" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1601" s="7">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="6">
+        <v>461</v>
+      </c>
+      <c r="C1602" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="6">
+        <v>59</v>
+      </c>
+      <c r="B1603" s="7">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="6">
+        <v>461</v>
+      </c>
+      <c r="C1604" s="8">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="6">
+        <v>282</v>
+      </c>
+      <c r="B1605" s="7">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="6">
+        <v>201</v>
+      </c>
+      <c r="C1606" s="8">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="6">
+        <v>209</v>
+      </c>
+      <c r="B1607" s="7">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="6">
+        <v>204</v>
+      </c>
+      <c r="C1608" s="8">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="6">
+        <v>342</v>
+      </c>
+      <c r="B1609" s="7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="6">
+        <v>226</v>
+      </c>
+      <c r="C1610" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1611" s="7">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="6">
+        <v>275</v>
+      </c>
+      <c r="C1612" s="8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="6">
+        <v>68</v>
+      </c>
+      <c r="B1613" s="7">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="6">
+        <v>276</v>
+      </c>
+      <c r="C1614" s="8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="6">
+        <v>68</v>
+      </c>
+      <c r="B1615" s="7">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="6">
+        <v>277</v>
+      </c>
+      <c r="C1616" s="8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="6">
+        <v>29</v>
+      </c>
+      <c r="B1617" s="7">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="6">
+        <v>277</v>
+      </c>
+      <c r="C1618" s="8">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="6">
+        <v>79</v>
+      </c>
+      <c r="B1619" s="7">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="6">
+        <v>277</v>
+      </c>
+      <c r="C1620" s="8">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="6">
+        <v>242</v>
+      </c>
+      <c r="B1621" s="7">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="6">
+        <v>298</v>
+      </c>
+      <c r="C1622" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="6">
+        <v>25</v>
+      </c>
+      <c r="B1623" s="7">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="6">
+        <v>298</v>
+      </c>
+      <c r="C1624" s="8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="6">
+        <v>57</v>
+      </c>
+      <c r="B1625" s="7">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="6">
+        <v>152</v>
+      </c>
+      <c r="C1626" s="8">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="6">
+        <v>583</v>
+      </c>
+      <c r="B1627" s="7">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="6">
+        <v>83</v>
+      </c>
+      <c r="C1628" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1629" s="7">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="6">
+        <v>85</v>
+      </c>
+      <c r="C1630" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1631" s="7">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="6">
+        <v>86</v>
+      </c>
+      <c r="C1632" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1633" s="7">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" s="6">
+        <v>86</v>
+      </c>
+      <c r="C1634" s="8">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="6">
+        <v>411</v>
+      </c>
+      <c r="B1635" s="7">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="6">
+        <v>86</v>
+      </c>
+      <c r="C1636" s="8">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="6">
+        <v>289</v>
+      </c>
+      <c r="B1637" s="7">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="6">
+        <v>87</v>
+      </c>
+      <c r="C1638" s="8">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="6">
+        <v>339</v>
+      </c>
+      <c r="B1639" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="6">
+        <v>87</v>
+      </c>
+      <c r="C1640" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1641" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="6">
+        <v>89</v>
+      </c>
+      <c r="C1642" s="8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="6">
+        <v>49</v>
+      </c>
+      <c r="B1643" s="7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="6">
+        <v>89</v>
+      </c>
+      <c r="C1644" s="8">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="6">
+        <v>115</v>
+      </c>
+      <c r="B1645" s="7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="6">
+        <v>89</v>
+      </c>
+      <c r="C1646" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="6">
+        <v>19</v>
+      </c>
+      <c r="B1647" s="7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="6">
+        <v>186</v>
+      </c>
+      <c r="C1648" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1649" s="7">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="6">
+        <v>186</v>
+      </c>
+      <c r="C1650" s="8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="6">
+        <v>72</v>
+      </c>
+      <c r="B1651" s="7">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="6">
+        <v>187</v>
+      </c>
+      <c r="C1652" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1653" s="7">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="6">
+        <v>187</v>
+      </c>
+      <c r="C1654" s="8">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="6">
+        <v>451</v>
+      </c>
+      <c r="B1655" s="7">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="6">
+        <v>188</v>
+      </c>
+      <c r="C1656" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="6">
+        <v>58</v>
+      </c>
+      <c r="B1657" s="7">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="6">
+        <v>314</v>
+      </c>
+      <c r="C1658" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1659" s="7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="6">
+        <v>331</v>
+      </c>
+      <c r="C1660" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1661" s="7">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="6">
+        <v>332</v>
+      </c>
+      <c r="C1662" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1663" s="7">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="6">
+        <v>333</v>
+      </c>
+      <c r="C1664" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="6">
+        <v>47</v>
+      </c>
+      <c r="B1665" s="7">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="6">
+        <v>443</v>
+      </c>
+      <c r="C1666" s="8">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="6">
+        <v>411</v>
+      </c>
+      <c r="B1667" s="7">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="6">
+        <v>506</v>
+      </c>
+      <c r="C1668" s="8">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="6">
+        <v>314</v>
+      </c>
+      <c r="B1669" s="7">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="6">
+        <v>378</v>
+      </c>
+      <c r="C1670" s="8">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="6">
+        <v>343</v>
+      </c>
+      <c r="B1671" s="7">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="6">
+        <v>475</v>
+      </c>
+      <c r="C1672" s="8">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="6">
+        <v>241</v>
+      </c>
+      <c r="B1673" s="7">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="6">
+        <v>480</v>
+      </c>
+      <c r="C1674" s="8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="6">
+        <v>59</v>
+      </c>
+      <c r="B1675" s="7">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="6">
+        <v>480</v>
+      </c>
+      <c r="C1676" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="6">
+        <v>1</v>
+      </c>
+      <c r="B1677" s="7">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="6">
+        <v>481</v>
+      </c>
+      <c r="C1678" s="8">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="6">
+        <v>483</v>
+      </c>
+      <c r="B1679" s="7">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="6">
+        <v>484</v>
+      </c>
+      <c r="C1680" s="8">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="6">
+        <v>58</v>
+      </c>
+      <c r="B1681" s="7">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="6">
+        <v>584</v>
+      </c>
+      <c r="C1682" s="8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="6">
+        <v>66</v>
+      </c>
+      <c r="B1683" s="7">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="6">
+        <v>584</v>
+      </c>
+      <c r="C1684" s="8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="6">
+        <v>90</v>
+      </c>
+      <c r="B1685" s="7">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="6">
+        <v>584</v>
+      </c>
+      <c r="C1686" s="8">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="6">
+        <v>156</v>
+      </c>
+      <c r="B1687" s="7">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="6">
+        <v>484</v>
+      </c>
+      <c r="C1688" s="8">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="6">
+        <v>584</v>
+      </c>
+      <c r="B1689" s="7">
+        <v>484</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>